--- a/vagas_gupy_inhire.xlsx
+++ b/vagas_gupy_inhire.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\busca-vagas-gupy-inhire-empregare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C87E83B-BF9F-4773-9D4D-DDD408721ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42F3B9AB-F05B-408D-8843-417773AD7F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8AA89335-F1D0-4CC5-A6EE-80670CE0F603}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BC4FFBB-7E4A-4A6A-9F25-1656EC745DF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Vagas" sheetId="3" r:id="rId1"/>
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'InHire novas (fora da lista)'!$A$1:$C$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Presenca por Empresa'!$A$1:$F$252</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vagas!$A$1:$M$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Presenca por Empresa'!$A$1:$F$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vagas!$A$1:$M$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="711">
   <si>
     <t>Empresa</t>
   </si>
@@ -211,6 +211,12 @@
     <t>[Expert] Assistente de Operações Financeiras (Notas Fiscais)</t>
   </si>
   <si>
+    <t>KPMG</t>
+  </si>
+  <si>
+    <t>Consultor Júnior de Finance Transformation</t>
+  </si>
+  <si>
     <t>Aché</t>
   </si>
   <si>
@@ -946,9 +952,6 @@
     <t>Kovi</t>
   </si>
   <si>
-    <t>KPMG</t>
-  </si>
-  <si>
     <t>Labi Exames</t>
   </si>
   <si>
@@ -1108,9 +1111,6 @@
     <t>Pravaler</t>
   </si>
   <si>
-    <t>Qexpert</t>
-  </si>
-  <si>
     <t>Radix</t>
   </si>
   <si>
@@ -1294,21 +1294,21 @@
     <t>Grupo Comolatti</t>
   </si>
   <si>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Deloitte</t>
+  </si>
+  <si>
+    <t>Saúde do TEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo Protege </t>
+  </si>
+  <si>
     <t>Priner</t>
   </si>
   <si>
-    <t>Demo</t>
-  </si>
-  <si>
-    <t>Deloitte</t>
-  </si>
-  <si>
-    <t>Saúde do TEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupo Protege </t>
-  </si>
-  <si>
     <t>Essencial Nutrição</t>
   </si>
   <si>
@@ -1327,12 +1327,12 @@
     <t>Ninecon</t>
   </si>
   <si>
+    <t>ICON Solutions do Brasil</t>
+  </si>
+  <si>
     <t>Mottu</t>
   </si>
   <si>
-    <t>ICON Solutions do Brasil</t>
-  </si>
-  <si>
     <t>Gogroup</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>AGROSearch</t>
   </si>
   <si>
+    <t>vocedm</t>
+  </si>
+  <si>
     <t>Pedra Agroindustrial</t>
   </si>
   <si>
-    <t>vocedm</t>
-  </si>
-  <si>
     <t>Sympla</t>
   </si>
   <si>
@@ -1366,67 +1366,70 @@
     <t>Framework</t>
   </si>
   <si>
+    <t>Premiersoft</t>
+  </si>
+  <si>
     <t>DUX Company</t>
   </si>
   <si>
+    <t>Westwing Brasil</t>
+  </si>
+  <si>
+    <t>ASA</t>
+  </si>
+  <si>
     <t>MENA</t>
   </si>
   <si>
-    <t>Premiersoft</t>
-  </si>
-  <si>
-    <t>Westwing Brasil</t>
-  </si>
-  <si>
-    <t>ASA</t>
+    <t>Poliedro Educação</t>
   </si>
   <si>
     <t>Qeevo</t>
   </si>
   <si>
+    <t>QI Tech</t>
+  </si>
+  <si>
+    <t>Bequest Academy</t>
+  </si>
+  <si>
+    <t>EQI</t>
+  </si>
+  <si>
+    <t>Asper</t>
+  </si>
+  <si>
+    <t>Grupo AG Capital</t>
+  </si>
+  <si>
     <t>Lyncas</t>
   </si>
   <si>
-    <t>Poliedro Educação</t>
-  </si>
-  <si>
-    <t>QI Tech</t>
-  </si>
-  <si>
-    <t>Bequest Academy</t>
-  </si>
-  <si>
-    <t>EQI</t>
-  </si>
-  <si>
-    <t>Asper</t>
-  </si>
-  <si>
-    <t>Grupo AG Capital</t>
-  </si>
-  <si>
     <t>Oliveira &amp; Antunes Advogados Associados</t>
   </si>
   <si>
+    <t>FiberHome Brasil</t>
+  </si>
+  <si>
     <t>Grupo LOS</t>
   </si>
   <si>
-    <t>FiberHome Brasil</t>
+    <t>Schulze</t>
   </si>
   <si>
     <t>SRM</t>
   </si>
   <si>
+    <t>Sylvamo</t>
+  </si>
+  <si>
+    <t>GVC</t>
+  </si>
+  <si>
     <t>Sanar</t>
   </si>
   <si>
-    <t>Schulze</t>
-  </si>
-  <si>
-    <t>Sylvamo</t>
-  </si>
-  <si>
-    <t>GVC</t>
+    <t>Appmax</t>
   </si>
   <si>
     <t>Seu Estágio</t>
@@ -1435,36 +1438,33 @@
     <t>TalentX Digital</t>
   </si>
   <si>
-    <t>Appmax</t>
+    <t>Paytrack</t>
+  </si>
+  <si>
+    <t>tecer</t>
   </si>
   <si>
     <t>LiveMode</t>
   </si>
   <si>
-    <t>tecer</t>
-  </si>
-  <si>
     <t>Magazord</t>
   </si>
   <si>
     <t>Melnick</t>
   </si>
   <si>
-    <t>Paytrack</t>
-  </si>
-  <si>
     <t>Luby</t>
   </si>
   <si>
+    <t>Trinnus RH</t>
+  </si>
+  <si>
+    <t>iHunters</t>
+  </si>
+  <si>
     <t>Solfácil</t>
   </si>
   <si>
-    <t>Trinnus RH</t>
-  </si>
-  <si>
-    <t>iHunters</t>
-  </si>
-  <si>
     <t>Anhembi</t>
   </si>
   <si>
@@ -1498,6 +1498,9 @@
     <t>ASCAS</t>
   </si>
   <si>
+    <t>Construtora Elevação</t>
+  </si>
+  <si>
     <t>Ligga</t>
   </si>
   <si>
@@ -1522,45 +1525,51 @@
     <t>Cescon Barrieu</t>
   </si>
   <si>
+    <t>GCB</t>
+  </si>
+  <si>
+    <t>Grupo Autoglass</t>
+  </si>
+  <si>
+    <t>Guaracamp</t>
+  </si>
+  <si>
+    <t>MK Solutions</t>
+  </si>
+  <si>
+    <t>Turbo</t>
+  </si>
+  <si>
+    <t>CTC</t>
+  </si>
+  <si>
+    <t>Eclipseworks</t>
+  </si>
+  <si>
+    <t>FIAP</t>
+  </si>
+  <si>
+    <t>IDG</t>
+  </si>
+  <si>
+    <t>Octafy</t>
+  </si>
+  <si>
+    <t>Vórtx</t>
+  </si>
+  <si>
+    <t>Yandeh</t>
+  </si>
+  <si>
+    <t>CashMe</t>
+  </si>
+  <si>
+    <t>CRMBonus</t>
+  </si>
+  <si>
     <t>Fitting</t>
   </si>
   <si>
-    <t>GCB</t>
-  </si>
-  <si>
-    <t>Grupo Autoglass</t>
-  </si>
-  <si>
-    <t>Guaracamp</t>
-  </si>
-  <si>
-    <t>Turbo</t>
-  </si>
-  <si>
-    <t>CRMBonus</t>
-  </si>
-  <si>
-    <t>Eclipseworks</t>
-  </si>
-  <si>
-    <t>FIAP</t>
-  </si>
-  <si>
-    <t>IDG</t>
-  </si>
-  <si>
-    <t>MK Solutions</t>
-  </si>
-  <si>
-    <t>Octafy</t>
-  </si>
-  <si>
-    <t>Yandeh</t>
-  </si>
-  <si>
-    <t>CashMe</t>
-  </si>
-  <si>
     <t>Flutter Brazil</t>
   </si>
   <si>
@@ -1570,15 +1579,12 @@
     <t>Leader &amp; Talent</t>
   </si>
   <si>
+    <t>LWSA</t>
+  </si>
+  <si>
     <t>Segura®</t>
   </si>
   <si>
-    <t>Vórtx</t>
-  </si>
-  <si>
-    <t>CTC</t>
-  </si>
-  <si>
     <t>Infleet</t>
   </si>
   <si>
@@ -1588,45 +1594,45 @@
     <t>Yolo Recruit</t>
   </si>
   <si>
-    <t>Construtora Elevação</t>
-  </si>
-  <si>
     <t>Essence</t>
   </si>
   <si>
+    <t>J.Assy</t>
+  </si>
+  <si>
+    <t>Pottencial</t>
+  </si>
+  <si>
+    <t>Procfit</t>
+  </si>
+  <si>
+    <t>Qive</t>
+  </si>
+  <si>
+    <t>Zig</t>
+  </si>
+  <si>
+    <t>BR MotorSport</t>
+  </si>
+  <si>
+    <t>Conx</t>
+  </si>
+  <si>
     <t>Grupo GCB</t>
   </si>
   <si>
-    <t>J.Assy</t>
-  </si>
-  <si>
-    <t>LWSA</t>
-  </si>
-  <si>
-    <t>Pottencial</t>
-  </si>
-  <si>
-    <t>Procfit</t>
-  </si>
-  <si>
-    <t>Qive</t>
-  </si>
-  <si>
-    <t>Zig</t>
-  </si>
-  <si>
-    <t>BR MotorSport</t>
-  </si>
-  <si>
-    <t>Conx</t>
-  </si>
-  <si>
     <t>Heads</t>
   </si>
   <si>
+    <t>Petit.RH</t>
+  </si>
+  <si>
     <t>Portofino Multi    Family Office</t>
   </si>
   <si>
+    <t>RIOgaleão</t>
+  </si>
+  <si>
     <t>TPGROUP</t>
   </si>
   <si>
@@ -1639,9 +1645,6 @@
     <t>Movecta</t>
   </si>
   <si>
-    <t>RIOgaleão</t>
-  </si>
-  <si>
     <t>Think IT</t>
   </si>
   <si>
@@ -1681,9 +1684,6 @@
     <t>M7 Soluções Financeiras</t>
   </si>
   <si>
-    <t>Petit.RH</t>
-  </si>
-  <si>
     <t>Praso</t>
   </si>
   <si>
@@ -1696,6 +1696,9 @@
     <t>Seguros SURA</t>
   </si>
   <si>
+    <t>Vem ser GX2</t>
+  </si>
+  <si>
     <t>Vertigo Tecnologia</t>
   </si>
   <si>
@@ -1720,66 +1723,75 @@
     <t>FacilitaPay</t>
   </si>
   <si>
+    <t>FRICON Brasil</t>
+  </si>
+  <si>
+    <t>GuiaInvest</t>
+  </si>
+  <si>
+    <t>Kanastra</t>
+  </si>
+  <si>
+    <t>Koopere</t>
+  </si>
+  <si>
+    <t>Luzandreya Consultoria e Assessoria de RH</t>
+  </si>
+  <si>
+    <t>Medway</t>
+  </si>
+  <si>
+    <t>NTS Brasil</t>
+  </si>
+  <si>
+    <t>Pier Seguradora</t>
+  </si>
+  <si>
+    <t>Seventh</t>
+  </si>
+  <si>
+    <t>Ume</t>
+  </si>
+  <si>
+    <t>Unitech</t>
+  </si>
+  <si>
+    <t>V360</t>
+  </si>
+  <si>
+    <t>wehandle</t>
+  </si>
+  <si>
+    <t>2Future</t>
+  </si>
+  <si>
+    <t>Atlas</t>
+  </si>
+  <si>
+    <t>Autopass</t>
+  </si>
+  <si>
+    <t>Bankme.</t>
+  </si>
+  <si>
+    <t>CAF</t>
+  </si>
+  <si>
+    <t>Carbigdata</t>
+  </si>
+  <si>
+    <t>Construtora Patriani</t>
+  </si>
+  <si>
+    <t>EDGE</t>
+  </si>
+  <si>
+    <t>erural</t>
+  </si>
+  <si>
     <t>Farmtech</t>
   </si>
   <si>
-    <t>FRICON Brasil</t>
-  </si>
-  <si>
-    <t>GuiaInvest</t>
-  </si>
-  <si>
-    <t>Kanastra</t>
-  </si>
-  <si>
-    <t>Luzandreya Consultoria e Assessoria de RH</t>
-  </si>
-  <si>
-    <t>Medway</t>
-  </si>
-  <si>
-    <t>NTS Brasil</t>
-  </si>
-  <si>
-    <t>Seventh</t>
-  </si>
-  <si>
-    <t>Ume</t>
-  </si>
-  <si>
-    <t>Unitech</t>
-  </si>
-  <si>
-    <t>V360</t>
-  </si>
-  <si>
-    <t>Vem ser GX2</t>
-  </si>
-  <si>
-    <t>wehandle</t>
-  </si>
-  <si>
-    <t>2Future</t>
-  </si>
-  <si>
-    <t>Autopass</t>
-  </si>
-  <si>
-    <t>Bankme.</t>
-  </si>
-  <si>
-    <t>CAF</t>
-  </si>
-  <si>
-    <t>Construtora Patriani</t>
-  </si>
-  <si>
-    <t>EDGE</t>
-  </si>
-  <si>
-    <t>erural</t>
-  </si>
-  <si>
     <t>Fleming Educação</t>
   </si>
   <si>
@@ -1795,48 +1807,39 @@
     <t>Indicium</t>
   </si>
   <si>
+    <t>Miner Tecnologia</t>
+  </si>
+  <si>
+    <t>Pipo Saúde</t>
+  </si>
+  <si>
+    <t>Rentbrella</t>
+  </si>
+  <si>
+    <t>Sancor Seguros</t>
+  </si>
+  <si>
+    <t>Sotran</t>
+  </si>
+  <si>
+    <t>TownSq</t>
+  </si>
+  <si>
+    <t>UPDA</t>
+  </si>
+  <si>
+    <t>Wevy</t>
+  </si>
+  <si>
+    <t>Azos</t>
+  </si>
+  <si>
+    <t>Grupo Food Nation</t>
+  </si>
+  <si>
     <t>IORQ</t>
   </si>
   <si>
-    <t>Koopere</t>
-  </si>
-  <si>
-    <t>Miner Tecnologia</t>
-  </si>
-  <si>
-    <t>Pier Seguradora</t>
-  </si>
-  <si>
-    <t>Pipo Saúde</t>
-  </si>
-  <si>
-    <t>Rentbrella</t>
-  </si>
-  <si>
-    <t>Sancor Seguros</t>
-  </si>
-  <si>
-    <t>Sotran</t>
-  </si>
-  <si>
-    <t>TownSq</t>
-  </si>
-  <si>
-    <t>Wevy</t>
-  </si>
-  <si>
-    <t>Atlas</t>
-  </si>
-  <si>
-    <t>Azos</t>
-  </si>
-  <si>
-    <t>Carbigdata</t>
-  </si>
-  <si>
-    <t>Grupo Food Nation</t>
-  </si>
-  <si>
     <t>Lumine</t>
   </si>
   <si>
@@ -1858,9 +1861,6 @@
     <t>Ubots</t>
   </si>
   <si>
-    <t>UPDA</t>
-  </si>
-  <si>
     <t>VerticalRH</t>
   </si>
   <si>
@@ -2023,6 +2023,9 @@
     <t>Cactus Gaming</t>
   </si>
   <si>
+    <t>CAPEF</t>
+  </si>
+  <si>
     <t>Celero</t>
   </si>
   <si>
@@ -2114,9 +2117,6 @@
   </si>
   <si>
     <t>Breezy Seguros</t>
-  </si>
-  <si>
-    <t>CAPEF</t>
   </si>
   <si>
     <t>ChatGuru</t>
@@ -2553,8 +2553,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B6589D-7C6A-4B04-BBC1-628A7FB471FB}">
-  <dimension ref="A1:M46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFB8138-8CC8-4B2C-8FA8-D565C8D081BB}">
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.77734375" customWidth="1"/>
@@ -2922,27 +2922,27 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>59</v>
       </c>
       <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
@@ -2956,40 +2956,37 @@
       <c r="K10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="M10" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
         <v>67</v>
       </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="H11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
         <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
-        <v>67</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>56</v>
@@ -2998,7 +2995,7 @@
         <v>56</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>24</v>
@@ -3009,22 +3006,22 @@
         <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>20</v>
@@ -3039,7 +3036,7 @@
         <v>56</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>24</v>
@@ -3047,31 +3044,31 @@
     </row>
     <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" t="s">
         <v>74</v>
       </c>
-      <c r="F13" t="s">
-        <v>72</v>
-      </c>
       <c r="G13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>56</v>
@@ -3080,7 +3077,7 @@
         <v>56</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>24</v>
@@ -3091,22 +3088,22 @@
         <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>76</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>20</v>
@@ -3121,7 +3118,7 @@
         <v>56</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>24</v>
@@ -3132,22 +3129,22 @@
         <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>20</v>
@@ -3162,7 +3159,7 @@
         <v>56</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>24</v>
@@ -3173,22 +3170,22 @@
         <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>20</v>
@@ -3203,7 +3200,7 @@
         <v>56</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>24</v>
@@ -3214,22 +3211,22 @@
         <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>20</v>
@@ -3244,7 +3241,7 @@
         <v>56</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>24</v>
@@ -3255,22 +3252,22 @@
         <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>20</v>
@@ -3285,33 +3282,33 @@
         <v>56</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>85</v>
       </c>
       <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>20</v>
@@ -3325,37 +3322,40 @@
       <c r="K19" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="L19" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="M19" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" t="s">
         <v>90</v>
       </c>
-      <c r="F20" t="s">
-        <v>88</v>
-      </c>
       <c r="G20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>56</v>
@@ -3369,31 +3369,31 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
         <v>52</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" t="s">
         <v>90</v>
       </c>
-      <c r="F21" t="s">
-        <v>88</v>
-      </c>
       <c r="G21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>56</v>
@@ -3410,22 +3410,22 @@
         <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
         <v>52</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>20</v>
@@ -3445,31 +3445,31 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
         <v>52</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>56</v>
@@ -3486,10 +3486,10 @@
         <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
         <v>52</v>
@@ -3498,10 +3498,10 @@
         <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>20</v>
@@ -3524,10 +3524,10 @@
         <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>52</v>
@@ -3536,10 +3536,10 @@
         <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>20</v>
@@ -3562,22 +3562,22 @@
         <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>20</v>
@@ -3597,31 +3597,31 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
         <v>52</v>
       </c>
       <c r="E27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
         <v>101</v>
-      </c>
-      <c r="F27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" t="s">
-        <v>102</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27" t="s">
-        <v>100</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>56</v>
@@ -3635,31 +3635,31 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
         <v>52</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" t="s">
         <v>104</v>
       </c>
-      <c r="F28" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" t="s">
-        <v>89</v>
-      </c>
       <c r="H28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>56</v>
@@ -3671,27 +3671,27 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>106</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>20</v>
@@ -3700,36 +3700,33 @@
         <v>105</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G30" t="s">
         <v>19</v>
@@ -3738,16 +3735,16 @@
         <v>20</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>24</v>
@@ -3755,22 +3752,22 @@
     </row>
     <row r="31" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E31" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" t="s">
         <v>113</v>
-      </c>
-      <c r="F31" t="s">
-        <v>111</v>
       </c>
       <c r="G31" t="s">
         <v>19</v>
@@ -3779,13 +3776,13 @@
         <v>20</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>23</v>
@@ -3796,13 +3793,13 @@
     </row>
     <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s">
         <v>31</v>
@@ -3811,7 +3808,7 @@
         <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G32" t="s">
         <v>19</v>
@@ -3820,13 +3817,13 @@
         <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>23</v>
@@ -3837,22 +3834,22 @@
     </row>
     <row r="33" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G33" t="s">
         <v>19</v>
@@ -3861,13 +3858,13 @@
         <v>20</v>
       </c>
       <c r="I33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>40</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>23</v>
@@ -3878,22 +3875,22 @@
     </row>
     <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F34" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G34" t="s">
         <v>19</v>
@@ -3902,13 +3899,13 @@
         <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>40</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>23</v>
@@ -3917,24 +3914,24 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>119</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
         <v>19</v>
@@ -3943,16 +3940,16 @@
         <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>24</v>
@@ -3960,22 +3957,22 @@
     </row>
     <row r="36" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
@@ -3984,39 +3981,39 @@
         <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G37" t="s">
         <v>19</v>
@@ -4025,16 +4022,16 @@
         <v>20</v>
       </c>
       <c r="I37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>24</v>
@@ -4042,78 +4039,81 @@
     </row>
     <row r="38" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s">
+        <v>123</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" t="s">
-        <v>130</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" t="s">
-        <v>128</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>132</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s">
+        <v>130</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" s="6" t="s">
+      <c r="L39" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="F39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" t="s">
-        <v>134</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>24</v>
@@ -4121,19 +4121,19 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F40" t="s">
         <v>37</v>
@@ -4145,33 +4145,33 @@
         <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F41" t="s">
         <v>37</v>
@@ -4183,33 +4183,33 @@
         <v>20</v>
       </c>
       <c r="I41" t="s">
+        <v>139</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="M41" s="1" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F42" t="s">
         <v>37</v>
@@ -4221,13 +4221,13 @@
         <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>24</v>
@@ -4235,113 +4235,113 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E43" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F43" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" t="s">
+        <v>38</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>148</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="F43" t="s">
-        <v>151</v>
-      </c>
-      <c r="G43" t="s">
-        <v>152</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I43" t="s">
-        <v>149</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
         <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F44" t="s">
+        <v>153</v>
+      </c>
+      <c r="G44" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>151</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="F44" t="s">
-        <v>151</v>
-      </c>
-      <c r="G44" t="s">
-        <v>156</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" t="s">
-        <v>154</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
         <v>52</v>
       </c>
       <c r="E45" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45" t="s">
+        <v>153</v>
+      </c>
+      <c r="G45" t="s">
+        <v>158</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>156</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
-      <c r="G45" t="s">
-        <v>55</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I45" t="s">
-        <v>158</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>24</v>
@@ -4355,7 +4355,7 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
         <v>52</v>
@@ -4385,62 +4385,101 @@
         <v>24</v>
       </c>
     </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" t="s">
+        <v>54</v>
+      </c>
+      <c r="G47" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s">
+        <v>162</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M46" xr:uid="{43B6589D-7C6A-4B04-BBC1-628A7FB471FB}"/>
+  <autoFilter ref="A1:M47" xr:uid="{9FFB8138-8CC8-4B2C-8FA8-D565C8D081BB}"/>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" tooltip="Abrir" xr:uid="{ADF683A8-A3E4-4E5C-BB2D-AD562D4DB0B8}"/>
-    <hyperlink ref="H3" r:id="rId2" tooltip="Abrir" xr:uid="{5697239A-3220-416E-84BE-50931133981E}"/>
-    <hyperlink ref="H4" r:id="rId3" tooltip="Abrir" xr:uid="{2FC582D1-2F83-49A7-B765-35FAEBFA9FBD}"/>
-    <hyperlink ref="H5" r:id="rId4" tooltip="Abrir" xr:uid="{991D77E5-33E2-4BD8-90E3-9CB435EB89B3}"/>
-    <hyperlink ref="H6" r:id="rId5" tooltip="Abrir" xr:uid="{55B437C1-BBD1-44E0-A1EE-D5EA1FFA583B}"/>
-    <hyperlink ref="H7" r:id="rId6" tooltip="Abrir" xr:uid="{3DD55D22-5F14-4389-BE60-D80D9757A540}"/>
-    <hyperlink ref="H8" r:id="rId7" tooltip="Abrir" xr:uid="{44643FDC-5A3E-4A0E-A762-183A8AEF95DE}"/>
-    <hyperlink ref="H9" r:id="rId8" tooltip="Abrir" xr:uid="{6192D735-D9AA-45CF-87D3-E7704F550BAF}"/>
-    <hyperlink ref="H10" r:id="rId9" location="/login/candidacy-registration/3111" tooltip="Abrir" xr:uid="{62CA9B1D-E723-42C8-BA96-75D2A6DD399C}"/>
-    <hyperlink ref="H11" r:id="rId10" location="/login/candidacy-registration/3023" tooltip="Abrir" xr:uid="{C6C02F78-A478-40A0-BF2B-24D0EB7BF3F7}"/>
-    <hyperlink ref="H12" r:id="rId11" location="/login/candidacy-registration/3157" tooltip="Abrir" xr:uid="{FA72A2D4-DED7-4C67-93B9-CF4B6BCA88DB}"/>
-    <hyperlink ref="H13" r:id="rId12" location="/login/candidacy-registration/3145" tooltip="Abrir" xr:uid="{C43C3235-9167-4121-A121-35ECEC13CA8C}"/>
-    <hyperlink ref="H14" r:id="rId13" location="/login/candidacy-registration/3155" tooltip="Abrir" xr:uid="{6741AD24-2E11-4F24-ACDC-1F2AAA0E1671}"/>
-    <hyperlink ref="H15" r:id="rId14" location="/login/candidacy-registration/3125" tooltip="Abrir" xr:uid="{7AD39F42-E099-4B48-92B2-9BA1F4362AAA}"/>
-    <hyperlink ref="H16" r:id="rId15" location="/login/candidacy-registration/3120" tooltip="Abrir" xr:uid="{487802FB-4D04-43A3-BA57-BAF3B2FCBFCE}"/>
-    <hyperlink ref="H17" r:id="rId16" location="/login/candidacy-registration/3133" tooltip="Abrir" xr:uid="{7C7C43E6-17F8-41B7-A247-803B0A113586}"/>
-    <hyperlink ref="H18" r:id="rId17" location="/login/candidacy-registration/3117" tooltip="Abrir" xr:uid="{887465AB-0EA2-45EB-A93B-D1354745175E}"/>
-    <hyperlink ref="H19" r:id="rId18" tooltip="Abrir" xr:uid="{B167BDEE-04EA-47FB-8737-D72FE14A5CE5}"/>
-    <hyperlink ref="H20" r:id="rId19" tooltip="Abrir" xr:uid="{3EA02939-B07D-4616-9755-6BF2B149636F}"/>
-    <hyperlink ref="H21" r:id="rId20" tooltip="Abrir" xr:uid="{E1090B50-3324-408A-8C4B-7556BA31905C}"/>
-    <hyperlink ref="H22" r:id="rId21" tooltip="Abrir" xr:uid="{B2A24277-1E84-4D68-BD74-82D583940460}"/>
-    <hyperlink ref="H23" r:id="rId22" tooltip="Abrir" xr:uid="{1462B168-A49C-41A3-A26D-F908BF2E3678}"/>
-    <hyperlink ref="H24" r:id="rId23" tooltip="Abrir" xr:uid="{62EC44E7-E065-4793-A613-DD21E9DAC22F}"/>
-    <hyperlink ref="H25" r:id="rId24" tooltip="Abrir" xr:uid="{C0E062B3-ADFC-4C18-9E5A-5E2E74F82286}"/>
-    <hyperlink ref="H26" r:id="rId25" tooltip="Abrir" xr:uid="{25E910C7-45AA-438D-96BC-145265399EC9}"/>
-    <hyperlink ref="H27" r:id="rId26" tooltip="Abrir" xr:uid="{E04D6BF6-8062-4D8F-949D-4CC8E892D8BA}"/>
-    <hyperlink ref="H28" r:id="rId27" tooltip="Abrir" xr:uid="{72ABBC8C-4AF7-4358-A2DC-604459F02F11}"/>
-    <hyperlink ref="H29" r:id="rId28" tooltip="Abrir" xr:uid="{C5836141-FC9B-4CC2-8E45-3880562C9573}"/>
-    <hyperlink ref="H30" r:id="rId29" tooltip="Abrir" xr:uid="{17936973-84D7-4169-9BDA-156E9B43F1EC}"/>
-    <hyperlink ref="H31" r:id="rId30" tooltip="Abrir" xr:uid="{948F41A2-C089-4720-9483-13B25630ACF8}"/>
-    <hyperlink ref="H32" r:id="rId31" tooltip="Abrir" xr:uid="{454E5E97-8CAE-4728-A63D-21EF40CD968F}"/>
-    <hyperlink ref="H33" r:id="rId32" tooltip="Abrir" xr:uid="{3B722C99-E810-47CF-BC7B-AE1CCB3D70A3}"/>
-    <hyperlink ref="H34" r:id="rId33" tooltip="Abrir" xr:uid="{7055EFE8-F57F-49C3-A515-C6C819053593}"/>
-    <hyperlink ref="H35" r:id="rId34" tooltip="Abrir" xr:uid="{C6E5B776-D370-44CE-8B64-E961386EEF3A}"/>
-    <hyperlink ref="H36" r:id="rId35" tooltip="Abrir" xr:uid="{D392B5D8-9974-4322-B2DA-17EACE981B87}"/>
-    <hyperlink ref="H37" r:id="rId36" tooltip="Abrir" xr:uid="{0363BFBB-F0B5-4993-B2D3-614BB345AE4D}"/>
-    <hyperlink ref="H38" r:id="rId37" tooltip="Abrir" xr:uid="{5E4B744F-F58B-43BD-A45E-4CD99012098F}"/>
-    <hyperlink ref="H39" r:id="rId38" tooltip="Abrir" xr:uid="{A8A86DE9-2B6E-4CD4-88B2-55D4D98BDC6E}"/>
-    <hyperlink ref="H40" r:id="rId39" tooltip="Abrir" xr:uid="{3BA332E3-61E6-4649-9D29-4B35BFE67EC4}"/>
-    <hyperlink ref="H41" r:id="rId40" tooltip="Abrir" xr:uid="{9090E6D0-C447-41AA-9E96-CE36CA73CE89}"/>
-    <hyperlink ref="H42" r:id="rId41" tooltip="Abrir" xr:uid="{26F24602-1ECB-46B3-8533-B14548AEA49A}"/>
-    <hyperlink ref="H43" r:id="rId42" tooltip="Abrir" xr:uid="{850D54E1-F52C-46DD-B458-EA95DD9D30DD}"/>
-    <hyperlink ref="H44" r:id="rId43" tooltip="Abrir" xr:uid="{1286AFE7-5944-4C82-8B17-7F9E08E51CF1}"/>
-    <hyperlink ref="H45" r:id="rId44" tooltip="Abrir" xr:uid="{EFA06F96-5FF7-4D46-B1CB-27D51FFBD831}"/>
-    <hyperlink ref="H46" r:id="rId45" tooltip="Abrir" xr:uid="{4BC7387A-F850-4D11-9823-A7D5946D636A}"/>
+    <hyperlink ref="H2" r:id="rId1" tooltip="Abrir" xr:uid="{5DCF3D93-48A8-4CB5-AE33-48A10774E310}"/>
+    <hyperlink ref="H3" r:id="rId2" tooltip="Abrir" xr:uid="{367665D3-BF10-48D2-B798-5218CAF4E3EA}"/>
+    <hyperlink ref="H4" r:id="rId3" tooltip="Abrir" xr:uid="{6971EC2C-2EDA-4142-A44E-63A98DD16AFB}"/>
+    <hyperlink ref="H5" r:id="rId4" tooltip="Abrir" xr:uid="{298FB276-ADCD-4D62-B75B-A4A2EB742FBB}"/>
+    <hyperlink ref="H6" r:id="rId5" tooltip="Abrir" xr:uid="{0434A962-7C53-4270-A1CA-4CE55CDF7386}"/>
+    <hyperlink ref="H7" r:id="rId6" tooltip="Abrir" xr:uid="{65CBE52C-13F2-4078-B8C5-FF40CC6CCD84}"/>
+    <hyperlink ref="H8" r:id="rId7" tooltip="Abrir" xr:uid="{B2FBB2A6-2712-4BB6-B8B5-713731637953}"/>
+    <hyperlink ref="H9" r:id="rId8" tooltip="Abrir" xr:uid="{F0173F87-B699-4792-BE4E-FF21F92A31EE}"/>
+    <hyperlink ref="H10" r:id="rId9" tooltip="Abrir" xr:uid="{0DAB2537-6597-4440-BFEF-E127ECD57D04}"/>
+    <hyperlink ref="H11" r:id="rId10" location="/login/candidacy-registration/3111" tooltip="Abrir" xr:uid="{969FB092-6539-49B3-BDEB-6DBAB127F7C9}"/>
+    <hyperlink ref="H12" r:id="rId11" location="/login/candidacy-registration/3023" tooltip="Abrir" xr:uid="{7E588A98-4980-47CD-BA04-913A8F230467}"/>
+    <hyperlink ref="H13" r:id="rId12" location="/login/candidacy-registration/3157" tooltip="Abrir" xr:uid="{7E96071C-38B0-4ED4-9AAB-BF47E5522198}"/>
+    <hyperlink ref="H14" r:id="rId13" location="/login/candidacy-registration/3145" tooltip="Abrir" xr:uid="{DFE5A4D6-65D0-4AD7-8A1E-07E107C63F7C}"/>
+    <hyperlink ref="H15" r:id="rId14" location="/login/candidacy-registration/3155" tooltip="Abrir" xr:uid="{E5169422-BE8D-4E11-8B79-897C63EA3F8E}"/>
+    <hyperlink ref="H16" r:id="rId15" location="/login/candidacy-registration/3125" tooltip="Abrir" xr:uid="{3077A213-11E8-4763-875E-FDE903D9F75C}"/>
+    <hyperlink ref="H17" r:id="rId16" location="/login/candidacy-registration/3120" tooltip="Abrir" xr:uid="{DA94B6F6-C515-4A22-A349-959DFA921367}"/>
+    <hyperlink ref="H18" r:id="rId17" location="/login/candidacy-registration/3133" tooltip="Abrir" xr:uid="{D24EB57F-B318-4EA4-B5D5-CBC995803506}"/>
+    <hyperlink ref="H19" r:id="rId18" location="/login/candidacy-registration/3117" tooltip="Abrir" xr:uid="{D89BEE4D-0BE3-4B1E-AA9A-66C12E286CC2}"/>
+    <hyperlink ref="H20" r:id="rId19" tooltip="Abrir" xr:uid="{AD767D7B-CC5C-4B9A-968C-37462AAC119D}"/>
+    <hyperlink ref="H21" r:id="rId20" tooltip="Abrir" xr:uid="{E6010BF5-71D2-4B06-AA2A-21214A5B596C}"/>
+    <hyperlink ref="H22" r:id="rId21" tooltip="Abrir" xr:uid="{CCCB5BD8-B3D6-41D8-AAF6-5F21DDA0CE37}"/>
+    <hyperlink ref="H23" r:id="rId22" tooltip="Abrir" xr:uid="{C3005568-1464-48A4-B0DA-DF0B014A65F3}"/>
+    <hyperlink ref="H24" r:id="rId23" tooltip="Abrir" xr:uid="{A8EECC95-456F-4C18-B7B4-9B9BCC3D20FC}"/>
+    <hyperlink ref="H25" r:id="rId24" tooltip="Abrir" xr:uid="{465C4DD4-4A0E-4570-BECF-B876531778DC}"/>
+    <hyperlink ref="H26" r:id="rId25" tooltip="Abrir" xr:uid="{8CDB4960-D978-46EB-9C43-9983A60C0769}"/>
+    <hyperlink ref="H27" r:id="rId26" tooltip="Abrir" xr:uid="{38F0624B-E7AE-49B9-B727-D405C80F9F49}"/>
+    <hyperlink ref="H28" r:id="rId27" tooltip="Abrir" xr:uid="{0482FD63-8C0D-4C1C-8911-87253B5B556E}"/>
+    <hyperlink ref="H29" r:id="rId28" tooltip="Abrir" xr:uid="{C09E22F5-193B-45A3-8C02-80BEBC1ED357}"/>
+    <hyperlink ref="H30" r:id="rId29" tooltip="Abrir" xr:uid="{2F16C58F-DFC8-4BFA-B583-3D554309E586}"/>
+    <hyperlink ref="H31" r:id="rId30" tooltip="Abrir" xr:uid="{EF0954B4-A87B-4D79-8030-3EE46B348C6F}"/>
+    <hyperlink ref="H32" r:id="rId31" tooltip="Abrir" xr:uid="{4D8CF1FD-A599-49BD-A36E-D79A2AF29194}"/>
+    <hyperlink ref="H33" r:id="rId32" tooltip="Abrir" xr:uid="{CD9F30BF-157F-46DE-8958-1D1691888B2D}"/>
+    <hyperlink ref="H34" r:id="rId33" tooltip="Abrir" xr:uid="{167E5BDC-3B83-479E-9FD0-6116DE8E9F4C}"/>
+    <hyperlink ref="H35" r:id="rId34" tooltip="Abrir" xr:uid="{7CD19CC8-A448-4E1B-927C-B031054234EE}"/>
+    <hyperlink ref="H36" r:id="rId35" tooltip="Abrir" xr:uid="{CA68797A-5769-4083-93EF-169022D03A8A}"/>
+    <hyperlink ref="H37" r:id="rId36" tooltip="Abrir" xr:uid="{083933F1-C5AD-4765-AF1E-77E2102C12D1}"/>
+    <hyperlink ref="H38" r:id="rId37" tooltip="Abrir" xr:uid="{8A1F1644-9FA6-4AA8-992F-A16334CE9E7D}"/>
+    <hyperlink ref="H39" r:id="rId38" tooltip="Abrir" xr:uid="{578D4DE4-CED4-4FA9-8430-873E585A70B5}"/>
+    <hyperlink ref="H40" r:id="rId39" tooltip="Abrir" xr:uid="{75C35FA2-8AEF-4BC6-8106-67B0CBBD092F}"/>
+    <hyperlink ref="H41" r:id="rId40" tooltip="Abrir" xr:uid="{498619C9-BACA-4F90-9919-BFF889C6F786}"/>
+    <hyperlink ref="H42" r:id="rId41" tooltip="Abrir" xr:uid="{6DAFE86D-1BF7-44D7-B63D-E5305BBC1CC5}"/>
+    <hyperlink ref="H43" r:id="rId42" tooltip="Abrir" xr:uid="{E4068DEE-235C-481F-BD1C-3BF578A13210}"/>
+    <hyperlink ref="H44" r:id="rId43" tooltip="Abrir" xr:uid="{0DB123C9-24D9-44A3-B3B7-58823D19683C}"/>
+    <hyperlink ref="H45" r:id="rId44" tooltip="Abrir" xr:uid="{03036064-F51F-4035-9A90-D90A62162D4D}"/>
+    <hyperlink ref="H46" r:id="rId45" tooltip="Abrir" xr:uid="{2D6D0D21-6CB5-4E64-B927-D246AB3F7784}"/>
+    <hyperlink ref="H47" r:id="rId46" tooltip="Abrir" xr:uid="{7AB3B6F2-3136-4506-A750-91C6CAA53F04}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93AF6C5A-5107-4357-A17D-F1849FA3F4BD}">
-  <dimension ref="A1:F252"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1093B08-8A5D-4393-94E5-EBA568F55529}">
+  <dimension ref="A1:F251"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.77734375" customWidth="1"/>
@@ -4456,24 +4495,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -4487,7 +4526,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -4498,7 +4537,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -4512,7 +4551,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -4523,7 +4562,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -4534,7 +4573,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -4545,7 +4584,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -4556,7 +4595,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
@@ -4570,7 +4609,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -4581,7 +4620,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -4592,7 +4631,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -4603,7 +4642,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -4617,7 +4656,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -4637,7 +4676,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -4646,12 +4685,12 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -4662,7 +4701,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -4673,7 +4712,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -4682,12 +4721,12 @@
         <v>20</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -4701,7 +4740,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
@@ -4712,7 +4751,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
@@ -4721,12 +4760,12 @@
         <v>20</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
@@ -4737,7 +4776,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
@@ -4748,7 +4787,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -4762,7 +4801,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
@@ -4776,7 +4815,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
@@ -4787,7 +4826,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -4798,7 +4837,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
@@ -4809,7 +4848,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
@@ -4823,7 +4862,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D30" t="s">
         <v>15</v>
@@ -4837,7 +4876,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
@@ -4851,7 +4890,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -4865,7 +4904,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
@@ -4876,7 +4915,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
@@ -4890,7 +4929,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
@@ -4901,7 +4940,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
@@ -4912,7 +4951,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
@@ -4926,7 +4965,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
@@ -4937,7 +4976,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
@@ -4948,7 +4987,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B40" t="s">
         <v>15</v>
@@ -4959,7 +4998,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
@@ -4973,7 +5012,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s">
         <v>15</v>
@@ -4993,7 +5032,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
@@ -5007,7 +5046,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
@@ -5032,7 +5071,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
         <v>15</v>
@@ -5043,7 +5082,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -5057,7 +5096,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
@@ -5068,7 +5107,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D49" t="s">
         <v>15</v>
@@ -5082,7 +5121,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
@@ -5104,7 +5143,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -5118,7 +5157,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
@@ -5129,7 +5168,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
@@ -5138,12 +5177,12 @@
         <v>20</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -5157,7 +5196,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
         <v>15</v>
@@ -5168,7 +5207,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B57" t="s">
         <v>15</v>
@@ -5179,7 +5218,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D58" t="s">
         <v>15</v>
@@ -5193,7 +5232,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
@@ -5204,7 +5243,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B60" t="s">
         <v>15</v>
@@ -5215,7 +5254,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B61" t="s">
         <v>15</v>
@@ -5235,7 +5274,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
@@ -5249,7 +5288,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
@@ -5269,7 +5308,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
@@ -5280,7 +5319,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
@@ -5291,7 +5330,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
@@ -5302,7 +5341,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
@@ -5313,7 +5352,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D68" t="s">
         <v>15</v>
@@ -5341,7 +5380,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B70" t="s">
         <v>15</v>
@@ -5361,7 +5400,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D71" t="s">
         <v>15</v>
@@ -5375,7 +5414,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
         <v>15</v>
@@ -5386,7 +5425,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s">
         <v>15</v>
@@ -5397,7 +5436,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B74" t="s">
         <v>15</v>
@@ -5417,7 +5456,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B75" t="s">
         <v>15</v>
@@ -5428,7 +5467,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D76" t="s">
         <v>15</v>
@@ -5442,7 +5481,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
         <v>15</v>
@@ -5457,12 +5496,12 @@
         <v>20</v>
       </c>
       <c r="F77">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D78" t="s">
         <v>15</v>
@@ -5476,7 +5515,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B79" t="s">
         <v>15</v>
@@ -5487,7 +5526,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B80" t="s">
         <v>15</v>
@@ -5507,7 +5546,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D81" t="s">
         <v>15</v>
@@ -5521,7 +5560,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D82" t="s">
         <v>15</v>
@@ -5530,12 +5569,12 @@
         <v>20</v>
       </c>
       <c r="F82">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D83" t="s">
         <v>15</v>
@@ -5549,7 +5588,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B84" t="s">
         <v>15</v>
@@ -5560,7 +5599,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B85" t="s">
         <v>15</v>
@@ -5571,7 +5610,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D86" t="s">
         <v>15</v>
@@ -5585,7 +5624,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
@@ -5605,7 +5644,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B88" t="s">
         <v>15</v>
@@ -5616,7 +5655,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D89" t="s">
         <v>15</v>
@@ -5630,7 +5669,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B90" t="s">
         <v>15</v>
@@ -5641,7 +5680,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D91" t="s">
         <v>15</v>
@@ -5655,7 +5694,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D92" t="s">
         <v>15</v>
@@ -5669,7 +5708,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D93" t="s">
         <v>15</v>
@@ -5683,7 +5722,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
@@ -5694,7 +5733,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
@@ -5708,7 +5747,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D96" t="s">
         <v>15</v>
@@ -5722,7 +5761,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D97" t="s">
         <v>15</v>
@@ -5736,7 +5775,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D98" t="s">
         <v>15</v>
@@ -5750,7 +5789,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
@@ -5761,7 +5800,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D100" t="s">
         <v>15</v>
@@ -5775,7 +5814,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
@@ -5789,7 +5828,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
@@ -5803,7 +5842,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
@@ -5814,7 +5853,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D104" t="s">
         <v>15</v>
@@ -5828,7 +5867,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B105" t="s">
         <v>15</v>
@@ -5848,7 +5887,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B106" t="s">
         <v>15</v>
@@ -5859,7 +5898,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D107" t="s">
         <v>15</v>
@@ -5873,7 +5912,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
@@ -5884,7 +5923,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
@@ -5904,7 +5943,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>
@@ -5918,7 +5957,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
@@ -5929,7 +5968,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B112" t="s">
         <v>15</v>
@@ -5940,7 +5979,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
@@ -5954,7 +5993,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B114" t="s">
         <v>15</v>
@@ -5965,7 +6004,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B115" t="s">
         <v>15</v>
@@ -5976,7 +6015,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B116" t="s">
         <v>15</v>
@@ -5996,7 +6035,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B117" t="s">
         <v>15</v>
@@ -6007,7 +6046,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B118" t="s">
         <v>15</v>
@@ -6018,7 +6057,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
@@ -6032,7 +6071,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
@@ -6043,7 +6082,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
@@ -6054,7 +6093,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B122" t="s">
         <v>15</v>
@@ -6065,7 +6104,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D123" t="s">
         <v>15</v>
@@ -6079,7 +6118,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D124" t="s">
         <v>15</v>
@@ -6088,12 +6127,12 @@
         <v>20</v>
       </c>
       <c r="F124">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D125" t="s">
         <v>15</v>
@@ -6107,7 +6146,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D126" t="s">
         <v>15</v>
@@ -6121,7 +6160,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D127" t="s">
         <v>15</v>
@@ -6135,7 +6174,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D128" t="s">
         <v>15</v>
@@ -6149,7 +6188,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
@@ -6160,7 +6199,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D130" t="s">
         <v>15</v>
@@ -6174,7 +6213,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D131" t="s">
         <v>15</v>
@@ -6188,7 +6227,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B132" t="s">
         <v>15</v>
@@ -6199,7 +6238,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D133" t="s">
         <v>15</v>
@@ -6208,12 +6247,12 @@
         <v>20</v>
       </c>
       <c r="F133">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B134" t="s">
         <v>15</v>
@@ -6224,7 +6263,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D135" t="s">
         <v>15</v>
@@ -6238,7 +6277,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B136" t="s">
         <v>15</v>
@@ -6249,7 +6288,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D137" t="s">
         <v>15</v>
@@ -6263,7 +6302,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D138" t="s">
         <v>15</v>
@@ -6277,7 +6316,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D139" t="s">
         <v>15</v>
@@ -6291,7 +6330,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B140" t="s">
         <v>15</v>
@@ -6302,7 +6341,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
@@ -6313,7 +6352,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>304</v>
+        <v>59</v>
       </c>
       <c r="D142" t="s">
         <v>15</v>
@@ -6327,7 +6366,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D143" t="s">
         <v>15</v>
@@ -6341,7 +6380,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D144" t="s">
         <v>15</v>
@@ -6355,7 +6394,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B145" t="s">
         <v>15</v>
@@ -6366,7 +6405,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D146" t="s">
         <v>15</v>
@@ -6380,7 +6419,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D147" t="s">
         <v>15</v>
@@ -6394,7 +6433,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D148" t="s">
         <v>15</v>
@@ -6408,7 +6447,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D149" t="s">
         <v>15</v>
@@ -6422,7 +6461,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B150" t="s">
         <v>15</v>
@@ -6433,7 +6472,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D151" t="s">
         <v>15</v>
@@ -6447,7 +6486,7 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D152" t="s">
         <v>15</v>
@@ -6461,7 +6500,7 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B153" t="s">
         <v>15</v>
@@ -6472,7 +6511,7 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B154" t="s">
         <v>15</v>
@@ -6483,7 +6522,7 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B155" t="s">
         <v>15</v>
@@ -6494,7 +6533,7 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D156" t="s">
         <v>15</v>
@@ -6508,7 +6547,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D157" t="s">
         <v>15</v>
@@ -6522,7 +6561,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B158" t="s">
         <v>15</v>
@@ -6533,7 +6572,7 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D159" t="s">
         <v>15</v>
@@ -6547,7 +6586,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D160" t="s">
         <v>15</v>
@@ -6556,12 +6595,12 @@
         <v>20</v>
       </c>
       <c r="F160">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B161" t="s">
         <v>15</v>
@@ -6581,7 +6620,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D162" t="s">
         <v>15</v>
@@ -6595,7 +6634,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B163" t="s">
         <v>15</v>
@@ -6606,7 +6645,7 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B164" t="s">
         <v>15</v>
@@ -6617,7 +6656,7 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B165" t="s">
         <v>15</v>
@@ -6628,7 +6667,7 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B166" t="s">
         <v>15</v>
@@ -6639,7 +6678,7 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B167" t="s">
         <v>15</v>
@@ -6659,7 +6698,7 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B168" t="s">
         <v>15</v>
@@ -6670,7 +6709,7 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D169" t="s">
         <v>15</v>
@@ -6684,7 +6723,7 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D170" t="s">
         <v>15</v>
@@ -6698,7 +6737,7 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D171" t="s">
         <v>15</v>
@@ -6712,7 +6751,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D172" t="s">
         <v>15</v>
@@ -6726,7 +6765,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
@@ -6737,7 +6776,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D174" t="s">
         <v>15</v>
@@ -6751,7 +6790,7 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
@@ -6762,7 +6801,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B176" t="s">
         <v>15</v>
@@ -6782,7 +6821,7 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D177" t="s">
         <v>15</v>
@@ -6796,7 +6835,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D178" t="s">
         <v>15</v>
@@ -6810,7 +6849,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D179" t="s">
         <v>15</v>
@@ -6819,12 +6858,12 @@
         <v>20</v>
       </c>
       <c r="F179">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D180" t="s">
         <v>15</v>
@@ -6838,7 +6877,7 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D181" t="s">
         <v>15</v>
@@ -6852,7 +6891,7 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B182" t="s">
         <v>15</v>
@@ -6863,7 +6902,7 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D183" t="s">
         <v>15</v>
@@ -6877,7 +6916,7 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B184" t="s">
         <v>15</v>
@@ -6897,7 +6936,7 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B185" t="s">
         <v>15</v>
@@ -6908,7 +6947,7 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B186" t="s">
         <v>15</v>
@@ -6919,7 +6958,7 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B187" t="s">
         <v>15</v>
@@ -6930,7 +6969,7 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D188" t="s">
         <v>15</v>
@@ -6944,7 +6983,7 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B189" t="s">
         <v>15</v>
@@ -6955,7 +6994,7 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B190" t="s">
         <v>15</v>
@@ -6966,7 +7005,7 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D191" t="s">
         <v>15</v>
@@ -6975,12 +7014,12 @@
         <v>20</v>
       </c>
       <c r="F191">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B192" t="s">
         <v>15</v>
@@ -6991,7 +7030,7 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B193" t="s">
         <v>15</v>
@@ -7002,7 +7041,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B194" t="s">
         <v>15</v>
@@ -7013,7 +7052,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D195" t="s">
         <v>15</v>
@@ -7027,18 +7066,21 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>358</v>
-      </c>
-      <c r="B196" t="s">
-        <v>15</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>20</v>
+        <v>359</v>
+      </c>
+      <c r="D196" t="s">
+        <v>15</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F196">
+        <v>109</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D197" t="s">
         <v>15</v>
@@ -7047,12 +7089,12 @@
         <v>20</v>
       </c>
       <c r="F197">
-        <v>108</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D198" t="s">
         <v>15</v>
@@ -7061,12 +7103,12 @@
         <v>20</v>
       </c>
       <c r="F198">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -7075,12 +7117,12 @@
         <v>20</v>
       </c>
       <c r="F199">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -7089,26 +7131,23 @@
         <v>20</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>363</v>
-      </c>
-      <c r="D201" t="s">
-        <v>15</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F201">
-        <v>5</v>
+        <v>364</v>
+      </c>
+      <c r="B201" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B202" t="s">
         <v>15</v>
@@ -7119,74 +7158,77 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B203" t="s">
         <v>15</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="D203" t="s">
+        <v>15</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F203">
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B204" t="s">
         <v>15</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D204" t="s">
-        <v>15</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F204">
-        <v>9</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>367</v>
-      </c>
-      <c r="B205" t="s">
-        <v>15</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>20</v>
+        <v>368</v>
+      </c>
+      <c r="D205" t="s">
+        <v>15</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205">
+        <v>72</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>368</v>
-      </c>
-      <c r="D206" t="s">
-        <v>15</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F206">
-        <v>72</v>
+        <v>369</v>
+      </c>
+      <c r="B206" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>369</v>
-      </c>
-      <c r="B207" t="s">
-        <v>15</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>20</v>
+        <v>370</v>
+      </c>
+      <c r="D207" t="s">
+        <v>15</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D208" t="s">
         <v>15</v>
@@ -7195,12 +7237,18 @@
         <v>20</v>
       </c>
       <c r="F208">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>371</v>
+        <v>372</v>
+      </c>
+      <c r="B209" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D209" t="s">
         <v>15</v>
@@ -7209,57 +7257,48 @@
         <v>20</v>
       </c>
       <c r="F209">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B210" t="s">
         <v>15</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D210" t="s">
-        <v>15</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F210">
-        <v>13</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>373</v>
-      </c>
-      <c r="B211" t="s">
-        <v>15</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>20</v>
+        <v>374</v>
+      </c>
+      <c r="D211" t="s">
+        <v>15</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F211">
+        <v>16</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>374</v>
-      </c>
-      <c r="D212" t="s">
-        <v>15</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F212">
-        <v>16</v>
+        <v>375</v>
+      </c>
+      <c r="B212" t="s">
+        <v>15</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B213" t="s">
         <v>15</v>
@@ -7270,24 +7309,27 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B214" t="s">
         <v>15</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="D214" t="s">
+        <v>15</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F214">
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>377</v>
-      </c>
-      <c r="B215" t="s">
-        <v>15</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>20</v>
+        <v>378</v>
       </c>
       <c r="D215" t="s">
         <v>15</v>
@@ -7296,12 +7338,12 @@
         <v>20</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D216" t="s">
         <v>15</v>
@@ -7310,26 +7352,23 @@
         <v>20</v>
       </c>
       <c r="F216">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>379</v>
-      </c>
-      <c r="D217" t="s">
-        <v>15</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F217">
-        <v>0</v>
+        <v>380</v>
+      </c>
+      <c r="B217" t="s">
+        <v>15</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B218" t="s">
         <v>15</v>
@@ -7340,43 +7379,46 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>381</v>
-      </c>
-      <c r="B219" t="s">
-        <v>15</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>20</v>
+        <v>382</v>
+      </c>
+      <c r="D219" t="s">
+        <v>15</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F219">
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>382</v>
-      </c>
-      <c r="D220" t="s">
-        <v>15</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F220">
-        <v>3</v>
+        <v>383</v>
+      </c>
+      <c r="B220" t="s">
+        <v>15</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>383</v>
-      </c>
-      <c r="B221" t="s">
-        <v>15</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>20</v>
+        <v>384</v>
+      </c>
+      <c r="D221" t="s">
+        <v>15</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F221">
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D222" t="s">
         <v>15</v>
@@ -7385,62 +7427,62 @@
         <v>20</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>385</v>
-      </c>
-      <c r="D223" t="s">
-        <v>15</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F223">
-        <v>8</v>
+        <v>386</v>
+      </c>
+      <c r="B223" t="s">
+        <v>15</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>386</v>
-      </c>
-      <c r="B224" t="s">
-        <v>15</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>20</v>
+        <v>387</v>
+      </c>
+      <c r="D224" t="s">
+        <v>15</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F224">
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>387</v>
-      </c>
-      <c r="D225" t="s">
-        <v>15</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F225">
-        <v>5</v>
+        <v>388</v>
+      </c>
+      <c r="B225" t="s">
+        <v>15</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>388</v>
-      </c>
-      <c r="B226" t="s">
-        <v>15</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>20</v>
+        <v>389</v>
+      </c>
+      <c r="D226" t="s">
+        <v>15</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F226">
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D227" t="s">
         <v>15</v>
@@ -7449,12 +7491,12 @@
         <v>20</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D228" t="s">
         <v>15</v>
@@ -7463,12 +7505,12 @@
         <v>20</v>
       </c>
       <c r="F228">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D229" t="s">
         <v>15</v>
@@ -7477,12 +7519,12 @@
         <v>20</v>
       </c>
       <c r="F229">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D230" t="s">
         <v>15</v>
@@ -7491,37 +7533,43 @@
         <v>20</v>
       </c>
       <c r="F230">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>393</v>
-      </c>
-      <c r="D231" t="s">
-        <v>15</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F231">
-        <v>2</v>
+        <v>394</v>
+      </c>
+      <c r="B231" t="s">
+        <v>15</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>394</v>
-      </c>
-      <c r="B232" t="s">
-        <v>15</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>20</v>
+        <v>395</v>
+      </c>
+      <c r="D232" t="s">
+        <v>15</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F232">
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>395</v>
+        <v>396</v>
+      </c>
+      <c r="B233" t="s">
+        <v>15</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D233" t="s">
         <v>15</v>
@@ -7530,18 +7578,12 @@
         <v>20</v>
       </c>
       <c r="F233">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>396</v>
-      </c>
-      <c r="B234" t="s">
-        <v>15</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>20</v>
+        <v>397</v>
       </c>
       <c r="D234" t="s">
         <v>15</v>
@@ -7550,26 +7592,23 @@
         <v>20</v>
       </c>
       <c r="F234">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>397</v>
-      </c>
-      <c r="D235" t="s">
-        <v>15</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F235">
-        <v>9</v>
+        <v>398</v>
+      </c>
+      <c r="B235" t="s">
+        <v>15</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B236" t="s">
         <v>15</v>
@@ -7580,18 +7619,21 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>399</v>
-      </c>
-      <c r="B237" t="s">
-        <v>15</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>20</v>
+        <v>400</v>
+      </c>
+      <c r="D237" t="s">
+        <v>15</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F237">
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D238" t="s">
         <v>15</v>
@@ -7600,68 +7642,68 @@
         <v>20</v>
       </c>
       <c r="F238">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>401</v>
-      </c>
-      <c r="D239" t="s">
-        <v>15</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F239">
-        <v>25</v>
+        <v>402</v>
+      </c>
+      <c r="B239" t="s">
+        <v>15</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>402</v>
-      </c>
-      <c r="B240" t="s">
-        <v>15</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>20</v>
+        <v>403</v>
+      </c>
+      <c r="D240" t="s">
+        <v>15</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F240">
+        <v>10</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>403</v>
-      </c>
-      <c r="D241" t="s">
-        <v>15</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F241">
-        <v>10</v>
+        <v>404</v>
+      </c>
+      <c r="B241" t="s">
+        <v>15</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B242" t="s">
         <v>15</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="D242" t="s">
+        <v>15</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F242">
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>405</v>
-      </c>
-      <c r="B243" t="s">
-        <v>15</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="D243" t="s">
         <v>15</v>
@@ -7670,26 +7712,23 @@
         <v>20</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>406</v>
-      </c>
-      <c r="D244" t="s">
-        <v>15</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F244">
-        <v>3</v>
+        <v>407</v>
+      </c>
+      <c r="B244" t="s">
+        <v>15</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B245" t="s">
         <v>15</v>
@@ -7700,57 +7739,57 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>408</v>
-      </c>
-      <c r="B246" t="s">
-        <v>15</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>20</v>
+        <v>409</v>
+      </c>
+      <c r="D246" t="s">
+        <v>15</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F246">
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>409</v>
-      </c>
-      <c r="D247" t="s">
-        <v>15</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F247">
-        <v>5</v>
+        <v>410</v>
+      </c>
+      <c r="B247" t="s">
+        <v>15</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>410</v>
-      </c>
-      <c r="B248" t="s">
-        <v>15</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>20</v>
+        <v>411</v>
+      </c>
+      <c r="D248" t="s">
+        <v>15</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F248">
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>411</v>
-      </c>
-      <c r="D249" t="s">
-        <v>15</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F249">
-        <v>1</v>
+        <v>412</v>
+      </c>
+      <c r="B249" t="s">
+        <v>15</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B250" t="s">
         <v>15</v>
@@ -7761,311 +7800,299 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>413</v>
-      </c>
-      <c r="B251" t="s">
-        <v>15</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
         <v>414</v>
       </c>
-      <c r="D252" t="s">
-        <v>15</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F252">
+      <c r="D251" t="s">
+        <v>15</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F251">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F252" xr:uid="{93AF6C5A-5107-4357-A17D-F1849FA3F4BD}"/>
+  <autoFilter ref="A1:F251" xr:uid="{F1093B08-8A5D-4393-94E5-EBA568F55529}"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" tooltip="Abrir" xr:uid="{DF29C045-8FA3-4A52-A27C-5AE0AFBEE705}"/>
-    <hyperlink ref="C3" r:id="rId2" tooltip="Abrir" xr:uid="{9027AB59-086C-4A34-A042-035C3098D944}"/>
-    <hyperlink ref="E4" r:id="rId3" tooltip="Abrir" xr:uid="{1D36D31E-85E5-4FD9-B293-6C65C1833AC3}"/>
-    <hyperlink ref="C5" r:id="rId4" tooltip="Abrir" xr:uid="{AB2FF7A8-1FA8-48D8-BBBE-1EAAF2C46E56}"/>
-    <hyperlink ref="C6" r:id="rId5" tooltip="Abrir" xr:uid="{C4F1ECD5-587B-4E81-BF2B-7FCFA9DFC520}"/>
-    <hyperlink ref="C7" r:id="rId6" tooltip="Abrir" xr:uid="{30FC30AE-CCDF-478D-B3A0-7536BD7B25BA}"/>
-    <hyperlink ref="C8" r:id="rId7" tooltip="Abrir" xr:uid="{2684AE25-09A2-4625-BECF-67184F0E437A}"/>
-    <hyperlink ref="E9" r:id="rId8" tooltip="Abrir" xr:uid="{4559CC6C-E8E4-499A-9FA7-F9F5BDB37E68}"/>
-    <hyperlink ref="C10" r:id="rId9" tooltip="Abrir" xr:uid="{7B7D2841-8735-4AAA-AE72-A76173D455C4}"/>
-    <hyperlink ref="C11" r:id="rId10" tooltip="Abrir" xr:uid="{77AEB8E2-A117-4F8F-A835-0CBCCDFFF503}"/>
-    <hyperlink ref="C12" r:id="rId11" tooltip="Abrir" xr:uid="{C6205B67-538B-4CE9-A5BE-7A416A302A01}"/>
-    <hyperlink ref="E13" r:id="rId12" tooltip="Abrir" xr:uid="{97C62456-5AD3-4B8F-BE31-8E9599768E5F}"/>
-    <hyperlink ref="C14" r:id="rId13" tooltip="Abrir" xr:uid="{40F124E1-C3F9-4866-A686-6DD1D43F36DD}"/>
-    <hyperlink ref="E14" r:id="rId14" tooltip="Abrir" xr:uid="{59FD2383-DF1E-4F52-9D92-F525D0A1422C}"/>
-    <hyperlink ref="E15" r:id="rId15" tooltip="Abrir" xr:uid="{E1F7DC31-DC00-4C86-9EF3-9C9A54EFEC6B}"/>
-    <hyperlink ref="C16" r:id="rId16" tooltip="Abrir" xr:uid="{5B101AA3-9140-4BCF-B299-F9F8FEE8E528}"/>
-    <hyperlink ref="C17" r:id="rId17" tooltip="Abrir" xr:uid="{0EE8686B-BF68-43A9-B0A0-D6C5764F51AD}"/>
-    <hyperlink ref="E18" r:id="rId18" tooltip="Abrir" xr:uid="{5D302D08-E6F5-42A6-AA59-8ACFADBAEC95}"/>
-    <hyperlink ref="E19" r:id="rId19" tooltip="Abrir" xr:uid="{F0089C3C-E9B0-4E42-BE70-F108CA6801D2}"/>
-    <hyperlink ref="C20" r:id="rId20" tooltip="Abrir" xr:uid="{58DD679C-D78E-49B0-B270-C36CF96EB4C3}"/>
-    <hyperlink ref="E21" r:id="rId21" tooltip="Abrir" xr:uid="{AAF41CB8-981E-469F-B221-0DE90052665B}"/>
-    <hyperlink ref="C22" r:id="rId22" tooltip="Abrir" xr:uid="{D69E2EFF-245D-4F65-9401-3C03037D05C9}"/>
-    <hyperlink ref="C23" r:id="rId23" tooltip="Abrir" xr:uid="{7C3B76CC-5C78-4F93-8E78-00D42D7C18E1}"/>
-    <hyperlink ref="E24" r:id="rId24" tooltip="Abrir" xr:uid="{BFF601E0-6D57-4FF5-BA1E-C11FA73D327F}"/>
-    <hyperlink ref="E25" r:id="rId25" tooltip="Abrir" xr:uid="{892FBB53-532E-467A-B606-FB7ECC39BB6D}"/>
-    <hyperlink ref="C26" r:id="rId26" tooltip="Abrir" xr:uid="{BB507FC5-311C-4A6A-9A6A-A28B3EDACC67}"/>
-    <hyperlink ref="C27" r:id="rId27" tooltip="Abrir" xr:uid="{2DB68B52-5780-4CE2-957F-79B3A0E7C733}"/>
-    <hyperlink ref="C28" r:id="rId28" tooltip="Abrir" xr:uid="{48FA7A2F-AFAB-4DDC-B73F-426D22F42109}"/>
-    <hyperlink ref="E29" r:id="rId29" tooltip="Abrir" xr:uid="{F5C03C07-0211-4B86-A489-772ED5CFFB3C}"/>
-    <hyperlink ref="E30" r:id="rId30" tooltip="Abrir" xr:uid="{C806AE60-10D2-441B-BB21-D2C456FB8033}"/>
-    <hyperlink ref="E31" r:id="rId31" tooltip="Abrir" xr:uid="{E5DD35E6-C169-4BAD-99AD-D3BA3E388461}"/>
-    <hyperlink ref="E32" r:id="rId32" tooltip="Abrir" xr:uid="{12615919-C0EB-4B20-8CF3-CC09D71007F6}"/>
-    <hyperlink ref="C33" r:id="rId33" tooltip="Abrir" xr:uid="{05547A22-C1BA-45BD-8E8D-CBCDF9208DB6}"/>
-    <hyperlink ref="E34" r:id="rId34" tooltip="Abrir" xr:uid="{2A6F1DA9-B7AF-404C-B5FA-C851430D99FA}"/>
-    <hyperlink ref="C35" r:id="rId35" tooltip="Abrir" xr:uid="{3E80ACBF-94B7-488D-854F-2B74A006D821}"/>
-    <hyperlink ref="C36" r:id="rId36" tooltip="Abrir" xr:uid="{71ECCFE9-A6DF-43D4-8682-BF3A57F59346}"/>
-    <hyperlink ref="E37" r:id="rId37" tooltip="Abrir" xr:uid="{57040D25-4900-4DE9-A2D3-E7D7FC69086A}"/>
-    <hyperlink ref="C38" r:id="rId38" tooltip="Abrir" xr:uid="{3237158C-9FEA-4826-84D1-30A2D8944F33}"/>
-    <hyperlink ref="C39" r:id="rId39" tooltip="Abrir" xr:uid="{B1350FFE-0EA1-4530-9A52-93A7DC88AC40}"/>
-    <hyperlink ref="C40" r:id="rId40" tooltip="Abrir" xr:uid="{240959A7-9818-4631-9570-8FDDB40105F7}"/>
-    <hyperlink ref="E41" r:id="rId41" tooltip="Abrir" xr:uid="{6BB7AA9B-8B76-4FA2-B29A-C9F2F332D298}"/>
-    <hyperlink ref="C42" r:id="rId42" tooltip="Abrir" xr:uid="{6237C3FF-FCD4-445D-8F3B-1AD049D0343E}"/>
-    <hyperlink ref="E42" r:id="rId43" tooltip="Abrir" xr:uid="{AEAF9242-F076-4C01-A181-D607EDB2DFF5}"/>
-    <hyperlink ref="E43" r:id="rId44" tooltip="Abrir" xr:uid="{E602098A-69E0-4F99-AF1E-90F686C2BA56}"/>
-    <hyperlink ref="C44" r:id="rId45" tooltip="Abrir" xr:uid="{BD8CE647-D4C4-4F32-B9F3-E701F1050749}"/>
-    <hyperlink ref="E45" r:id="rId46" tooltip="Abrir" xr:uid="{93B6BDF3-7633-4610-BF81-E7BD4DDD5083}"/>
-    <hyperlink ref="C46" r:id="rId47" tooltip="Abrir" xr:uid="{C02E777E-A2F4-4E5D-BB55-F94A55C027D4}"/>
-    <hyperlink ref="E47" r:id="rId48" tooltip="Abrir" xr:uid="{F0928B0D-5FF5-4C6B-8CE3-D02C6D52334C}"/>
-    <hyperlink ref="C48" r:id="rId49" tooltip="Abrir" xr:uid="{37D68B58-07EF-404C-ABCF-4F7F00269533}"/>
-    <hyperlink ref="E49" r:id="rId50" tooltip="Abrir" xr:uid="{FC7AECA3-1173-48DC-826D-6238B7F3DCF4}"/>
-    <hyperlink ref="C50" r:id="rId51" tooltip="Abrir" xr:uid="{1CE8D489-132E-4216-B933-1BA00C7CD704}"/>
-    <hyperlink ref="C51" r:id="rId52" tooltip="Abrir" xr:uid="{14639DA0-7C08-4580-9E14-564EBE466CFE}"/>
-    <hyperlink ref="E52" r:id="rId53" tooltip="Abrir" xr:uid="{3FBEA3B3-273F-42D6-83BC-D0A412B6B3D9}"/>
-    <hyperlink ref="C53" r:id="rId54" tooltip="Abrir" xr:uid="{50C2E370-3926-4AA1-88CB-CDA311661F83}"/>
-    <hyperlink ref="E54" r:id="rId55" tooltip="Abrir" xr:uid="{62BA32DE-B9B1-4B80-95E0-F6EAC76C7119}"/>
-    <hyperlink ref="E55" r:id="rId56" tooltip="Abrir" xr:uid="{EEB26848-4BAC-46CE-8F91-E12EE2FED2BC}"/>
-    <hyperlink ref="C56" r:id="rId57" tooltip="Abrir" xr:uid="{26560F7E-35AD-442C-BEFC-A7E20001BBFC}"/>
-    <hyperlink ref="C57" r:id="rId58" tooltip="Abrir" xr:uid="{54D3A488-7C83-4F2D-9237-003D471E3F95}"/>
-    <hyperlink ref="E58" r:id="rId59" tooltip="Abrir" xr:uid="{531D3FAB-CD4C-4CFA-9615-04B3503C5725}"/>
-    <hyperlink ref="C59" r:id="rId60" tooltip="Abrir" xr:uid="{7E8029C9-F0A8-4A42-93CF-961EEECC83BF}"/>
-    <hyperlink ref="C60" r:id="rId61" tooltip="Abrir" xr:uid="{587F2B15-4B7F-4B4D-AFD4-A7771EEF16B1}"/>
-    <hyperlink ref="C61" r:id="rId62" tooltip="Abrir" xr:uid="{B83FE656-09CF-43EE-B9A3-02EFD7B41518}"/>
-    <hyperlink ref="E61" r:id="rId63" tooltip="Abrir" xr:uid="{478AE4B5-F0C5-442A-8E42-CFCA28FD4C3E}"/>
-    <hyperlink ref="E62" r:id="rId64" tooltip="Abrir" xr:uid="{A6BFE12E-9434-4F5A-881C-8AAD6D6EC2CA}"/>
-    <hyperlink ref="C63" r:id="rId65" tooltip="Abrir" xr:uid="{B408C1EC-2184-4E4D-A0EB-3F3E2C8DB41A}"/>
-    <hyperlink ref="E63" r:id="rId66" tooltip="Abrir" xr:uid="{1037911A-2A92-4D2C-A210-8C8C50B0F7E9}"/>
-    <hyperlink ref="C64" r:id="rId67" tooltip="Abrir" xr:uid="{4FE20F13-D49F-426B-B556-461B54D009E4}"/>
-    <hyperlink ref="C65" r:id="rId68" tooltip="Abrir" xr:uid="{09E1EBCA-5837-4E32-A360-5EE6819AFEC0}"/>
-    <hyperlink ref="C66" r:id="rId69" tooltip="Abrir" xr:uid="{DA460CA0-FF1F-45F6-8D4E-5A181471F86B}"/>
-    <hyperlink ref="C67" r:id="rId70" tooltip="Abrir" xr:uid="{66B8749E-FE81-46C2-B3FF-CC207DB8A72C}"/>
-    <hyperlink ref="E68" r:id="rId71" tooltip="Abrir" xr:uid="{7A9DB9FE-B800-4B67-BDED-7FD322ED3D61}"/>
-    <hyperlink ref="E69" r:id="rId72" tooltip="Abrir" xr:uid="{4D284511-C3C3-455B-AF50-7BDC6D938108}"/>
-    <hyperlink ref="C70" r:id="rId73" tooltip="Abrir" xr:uid="{5B0CE6C5-3B4F-48C1-8DAC-D5B60D9B0DB8}"/>
-    <hyperlink ref="E70" r:id="rId74" tooltip="Abrir" xr:uid="{CC5D85DA-6540-4087-AA8F-CB4F94594221}"/>
-    <hyperlink ref="E71" r:id="rId75" tooltip="Abrir" xr:uid="{10E0D00B-F167-4F22-A4E5-F17B1AE48287}"/>
-    <hyperlink ref="C72" r:id="rId76" tooltip="Abrir" xr:uid="{980CAE2E-2EBF-4690-8183-8E7BCD7D4911}"/>
-    <hyperlink ref="C73" r:id="rId77" tooltip="Abrir" xr:uid="{E4690932-7C41-4634-BEBD-02825C40BC68}"/>
-    <hyperlink ref="C74" r:id="rId78" tooltip="Abrir" xr:uid="{49EAC0BB-6666-4221-8987-5C00E021A802}"/>
-    <hyperlink ref="E74" r:id="rId79" tooltip="Abrir" xr:uid="{E4CE4BB5-F0C5-4A4D-95BA-5C97227A9216}"/>
-    <hyperlink ref="C75" r:id="rId80" tooltip="Abrir" xr:uid="{F6164C21-327F-4AFC-9A5C-81E36E951128}"/>
-    <hyperlink ref="E76" r:id="rId81" tooltip="Abrir" xr:uid="{1E62F237-679E-4D37-9D9E-061BA7920A9F}"/>
-    <hyperlink ref="C77" r:id="rId82" tooltip="Abrir" xr:uid="{156E836B-5198-46C2-9F25-FD0C5E462191}"/>
-    <hyperlink ref="E77" r:id="rId83" tooltip="Abrir" xr:uid="{945A4F86-30AB-42C7-AD48-CBFFCD9F9249}"/>
-    <hyperlink ref="E78" r:id="rId84" tooltip="Abrir" xr:uid="{031F0F2F-E815-47B6-A5A3-6FE216F5E935}"/>
-    <hyperlink ref="C79" r:id="rId85" tooltip="Abrir" xr:uid="{F61F33D9-4ECB-466D-AFBF-B691E900A154}"/>
-    <hyperlink ref="C80" r:id="rId86" tooltip="Abrir" xr:uid="{E8467F6C-3AE0-4D7D-98E2-6FD9C26292B3}"/>
-    <hyperlink ref="E80" r:id="rId87" tooltip="Abrir" xr:uid="{1ECFC035-970A-4D59-A1CD-05B1CC54B197}"/>
-    <hyperlink ref="E81" r:id="rId88" tooltip="Abrir" xr:uid="{0F3B2767-09D9-48D4-8B3A-8008E935227B}"/>
-    <hyperlink ref="E82" r:id="rId89" tooltip="Abrir" xr:uid="{E797C687-4AA2-408B-A2F7-C6EA776B2780}"/>
-    <hyperlink ref="E83" r:id="rId90" tooltip="Abrir" xr:uid="{275C23DD-70F0-40E8-A15E-2060A9C7D60B}"/>
-    <hyperlink ref="C84" r:id="rId91" tooltip="Abrir" xr:uid="{7800E8FC-2142-4664-A7BA-2C01E2C5F3BF}"/>
-    <hyperlink ref="C85" r:id="rId92" tooltip="Abrir" xr:uid="{74CE0937-06B3-435A-B38B-D07D97DC09E6}"/>
-    <hyperlink ref="E86" r:id="rId93" tooltip="Abrir" xr:uid="{BD6B72F5-D734-47B2-8286-A36C2627FCEF}"/>
-    <hyperlink ref="C87" r:id="rId94" tooltip="Abrir" xr:uid="{75E5D49C-2B0D-4553-9665-E7F87F2BB43A}"/>
-    <hyperlink ref="E87" r:id="rId95" tooltip="Abrir" xr:uid="{E720D6C6-6AD0-41AB-AAE6-D87D3EDB3B42}"/>
-    <hyperlink ref="C88" r:id="rId96" tooltip="Abrir" xr:uid="{3ACB47D0-BCF8-404B-BB92-0656101FF1E4}"/>
-    <hyperlink ref="E89" r:id="rId97" tooltip="Abrir" xr:uid="{5AFB743D-3D73-4C36-B845-1FB7B8F3ED3B}"/>
-    <hyperlink ref="C90" r:id="rId98" tooltip="Abrir" xr:uid="{1E543008-A6CD-42A9-B6B0-4B9CE44664BA}"/>
-    <hyperlink ref="E91" r:id="rId99" tooltip="Abrir" xr:uid="{1E5AAAD6-279E-4483-940F-91734C2269B3}"/>
-    <hyperlink ref="E92" r:id="rId100" tooltip="Abrir" xr:uid="{9AF8CF7B-B404-4C3B-B3C0-DA59B9488CA2}"/>
-    <hyperlink ref="E93" r:id="rId101" tooltip="Abrir" xr:uid="{2F211534-40F0-4901-89F5-CAB84C76CDB1}"/>
-    <hyperlink ref="C94" r:id="rId102" tooltip="Abrir" xr:uid="{55A2015E-4ADC-456C-B6BA-16222A163CC5}"/>
-    <hyperlink ref="E95" r:id="rId103" tooltip="Abrir" xr:uid="{D2F2FF41-F130-4EC3-89FE-AF341A61CE3E}"/>
-    <hyperlink ref="E96" r:id="rId104" tooltip="Abrir" xr:uid="{C2357090-B837-49C3-9F9F-52B2483EE2B2}"/>
-    <hyperlink ref="E97" r:id="rId105" tooltip="Abrir" xr:uid="{10E67DF1-F717-4D77-99E1-A791BBC837BC}"/>
-    <hyperlink ref="E98" r:id="rId106" tooltip="Abrir" xr:uid="{ECD955DB-5D1C-474E-8018-2C3C293A2522}"/>
-    <hyperlink ref="C99" r:id="rId107" tooltip="Abrir" xr:uid="{FD87FBAE-9CF0-409A-A7D3-D8F7897B980D}"/>
-    <hyperlink ref="E100" r:id="rId108" tooltip="Abrir" xr:uid="{E05D55A1-4F82-43A7-9CD5-6CF96CF60739}"/>
-    <hyperlink ref="E101" r:id="rId109" tooltip="Abrir" xr:uid="{300731FC-9071-44C4-AAA1-9E46F97A86A8}"/>
-    <hyperlink ref="E102" r:id="rId110" tooltip="Abrir" xr:uid="{933C1875-E77D-4198-BB95-7A0C36B249BE}"/>
-    <hyperlink ref="C103" r:id="rId111" tooltip="Abrir" xr:uid="{DA561C50-9F24-48C0-A3D1-828F1FF5A8BD}"/>
-    <hyperlink ref="E104" r:id="rId112" tooltip="Abrir" xr:uid="{30D7C48D-89DB-4282-B4F0-9AC007543BFC}"/>
-    <hyperlink ref="C105" r:id="rId113" tooltip="Abrir" xr:uid="{7BF9A9E9-2CD3-4D98-AADE-D36874CA4FD0}"/>
-    <hyperlink ref="E105" r:id="rId114" tooltip="Abrir" xr:uid="{29F35FDB-8BC0-4774-9DF8-6543B07F4640}"/>
-    <hyperlink ref="C106" r:id="rId115" tooltip="Abrir" xr:uid="{3FB3F5F8-5916-4BAD-80D4-88702BC193B0}"/>
-    <hyperlink ref="E107" r:id="rId116" tooltip="Abrir" xr:uid="{2A1BCC8C-A2F4-424A-AD4C-CC574FEE37F2}"/>
-    <hyperlink ref="C108" r:id="rId117" tooltip="Abrir" xr:uid="{AB334B09-2BE3-410B-A1BB-18A3B42547BC}"/>
-    <hyperlink ref="C109" r:id="rId118" tooltip="Abrir" xr:uid="{C89786B2-06FB-4B0A-B7D0-52A19B50CB44}"/>
-    <hyperlink ref="E109" r:id="rId119" tooltip="Abrir" xr:uid="{63BD2F21-5688-4BCF-9770-63F38006484B}"/>
-    <hyperlink ref="E110" r:id="rId120" tooltip="Abrir" xr:uid="{5DB4C7EF-1B4A-43D8-90FC-433CD099D30A}"/>
-    <hyperlink ref="C111" r:id="rId121" tooltip="Abrir" xr:uid="{075E785C-F191-48D8-9645-C238EDC3CA7F}"/>
-    <hyperlink ref="C112" r:id="rId122" tooltip="Abrir" xr:uid="{BE3A1C69-42AB-475D-A950-5F71347CA417}"/>
-    <hyperlink ref="E113" r:id="rId123" tooltip="Abrir" xr:uid="{F85E6D6E-14FD-4F7A-A04D-ACDA2BF558FC}"/>
-    <hyperlink ref="C114" r:id="rId124" tooltip="Abrir" xr:uid="{BD542881-4CD7-4B42-9D58-2652A7CA856E}"/>
-    <hyperlink ref="C115" r:id="rId125" tooltip="Abrir" xr:uid="{A516DA45-8FF3-4945-A4A7-A6FD10A834DD}"/>
-    <hyperlink ref="C116" r:id="rId126" tooltip="Abrir" xr:uid="{3F1888A6-0F9F-4821-AA1C-B05EB646C3F4}"/>
-    <hyperlink ref="E116" r:id="rId127" tooltip="Abrir" xr:uid="{CC05D665-B7AE-451D-A148-DDC150C438DC}"/>
-    <hyperlink ref="C117" r:id="rId128" tooltip="Abrir" xr:uid="{07B23666-C628-40D3-A689-E826BE35A470}"/>
-    <hyperlink ref="C118" r:id="rId129" tooltip="Abrir" xr:uid="{3EE598FC-092B-4808-8BD1-2482AE998132}"/>
-    <hyperlink ref="E119" r:id="rId130" tooltip="Abrir" xr:uid="{6C1886CF-2611-4993-AFD7-87E60D313D23}"/>
-    <hyperlink ref="C120" r:id="rId131" tooltip="Abrir" xr:uid="{CC4E75AC-4269-4019-B36C-642216945FC1}"/>
-    <hyperlink ref="C121" r:id="rId132" tooltip="Abrir" xr:uid="{0D0C5B6F-D73F-4933-8650-39CA014AF2B2}"/>
-    <hyperlink ref="C122" r:id="rId133" tooltip="Abrir" xr:uid="{7A94A3F4-93FF-44C3-8637-E0CAB7B1C9B7}"/>
-    <hyperlink ref="E123" r:id="rId134" tooltip="Abrir" xr:uid="{22715729-1387-47D5-867B-C57E5250C70E}"/>
-    <hyperlink ref="E124" r:id="rId135" tooltip="Abrir" xr:uid="{523B0863-DA1C-42EC-9B57-FD4E0349B64D}"/>
-    <hyperlink ref="E125" r:id="rId136" tooltip="Abrir" xr:uid="{674EA4C1-FE5A-4102-A26F-7E3DB5ACCF72}"/>
-    <hyperlink ref="E126" r:id="rId137" tooltip="Abrir" xr:uid="{10D21822-40B6-4A23-AB17-C6E8F9B6A5E0}"/>
-    <hyperlink ref="E127" r:id="rId138" tooltip="Abrir" xr:uid="{CEA0B605-AB2F-49B2-9570-1BB60C1A15BD}"/>
-    <hyperlink ref="E128" r:id="rId139" tooltip="Abrir" xr:uid="{4C9C06D6-E3FD-4A07-B7B1-C3D14F522A1C}"/>
-    <hyperlink ref="C129" r:id="rId140" tooltip="Abrir" xr:uid="{4197A6F4-E3AB-4F47-8875-E480A98B1B95}"/>
-    <hyperlink ref="E130" r:id="rId141" tooltip="Abrir" xr:uid="{04549B44-7BFD-4367-9B38-C09A01515FEA}"/>
-    <hyperlink ref="E131" r:id="rId142" tooltip="Abrir" xr:uid="{4BC7514A-24F1-4436-AD04-328618A7D927}"/>
-    <hyperlink ref="C132" r:id="rId143" tooltip="Abrir" xr:uid="{B476F2E7-0E5E-4948-ABD3-9CDA1EEB4B66}"/>
-    <hyperlink ref="E133" r:id="rId144" tooltip="Abrir" xr:uid="{7198C234-B287-4F24-B03B-EB7EEC899F3B}"/>
-    <hyperlink ref="C134" r:id="rId145" tooltip="Abrir" xr:uid="{A46F1589-5674-4BBB-818B-507B4301D878}"/>
-    <hyperlink ref="E135" r:id="rId146" tooltip="Abrir" xr:uid="{A646FD0C-A88E-49AE-9DE4-1DBA1EF6358C}"/>
-    <hyperlink ref="C136" r:id="rId147" tooltip="Abrir" xr:uid="{A587F654-CF52-4A7A-ABD8-76F8FC0F9BF4}"/>
-    <hyperlink ref="E137" r:id="rId148" tooltip="Abrir" xr:uid="{1D78C8D9-0A97-437B-AE2F-F06F493FAD82}"/>
-    <hyperlink ref="E138" r:id="rId149" tooltip="Abrir" xr:uid="{D856D426-CC17-4A6D-B07A-159062443953}"/>
-    <hyperlink ref="E139" r:id="rId150" tooltip="Abrir" xr:uid="{3937F15A-B4B9-4DCA-9FDC-69F98CA2E6CA}"/>
-    <hyperlink ref="C140" r:id="rId151" tooltip="Abrir" xr:uid="{8AB73D99-C65A-48FB-9F28-6955024F52E4}"/>
-    <hyperlink ref="C141" r:id="rId152" tooltip="Abrir" xr:uid="{038D4011-E9E4-48A8-B96B-9FD6AF487DC7}"/>
-    <hyperlink ref="E142" r:id="rId153" tooltip="Abrir" xr:uid="{8307459A-2BFB-4192-8DA7-ECD1554932FF}"/>
-    <hyperlink ref="E143" r:id="rId154" tooltip="Abrir" xr:uid="{78C305BD-6B19-44E5-89CA-489FC002C598}"/>
-    <hyperlink ref="E144" r:id="rId155" tooltip="Abrir" xr:uid="{1D6E078E-F67B-46C7-8CC0-15302EC7156C}"/>
-    <hyperlink ref="C145" r:id="rId156" tooltip="Abrir" xr:uid="{FE6D8B78-52BB-4BEE-8C2C-1573DEA09664}"/>
-    <hyperlink ref="E146" r:id="rId157" tooltip="Abrir" xr:uid="{EE33EE83-04C8-48A9-A7A2-DA9EEF9E47B8}"/>
-    <hyperlink ref="E147" r:id="rId158" tooltip="Abrir" xr:uid="{CEA9DF3D-FCEB-42E3-901C-818B32D9614E}"/>
-    <hyperlink ref="E148" r:id="rId159" tooltip="Abrir" xr:uid="{4533C99F-E3AD-49CE-8058-6DDB623BE485}"/>
-    <hyperlink ref="E149" r:id="rId160" tooltip="Abrir" xr:uid="{62811A87-7376-48D1-BD98-7F24DD0D5DD9}"/>
-    <hyperlink ref="C150" r:id="rId161" tooltip="Abrir" xr:uid="{4551B7B5-272A-4E24-AA34-2507FF6570BE}"/>
-    <hyperlink ref="E151" r:id="rId162" tooltip="Abrir" xr:uid="{6A90F53A-6319-41E0-915B-CAC20DEBC381}"/>
-    <hyperlink ref="E152" r:id="rId163" tooltip="Abrir" xr:uid="{4924FE93-1AA9-4164-A887-106F45CD7FD8}"/>
-    <hyperlink ref="C153" r:id="rId164" tooltip="Abrir" xr:uid="{9FFF51AB-7278-4ECF-9D74-75B8A8979A68}"/>
-    <hyperlink ref="C154" r:id="rId165" tooltip="Abrir" xr:uid="{EB82D071-C38F-40D7-9EC3-AB2B5F22BAC0}"/>
-    <hyperlink ref="C155" r:id="rId166" tooltip="Abrir" xr:uid="{ABA69C72-E591-4684-AFB6-510FF0E74E35}"/>
-    <hyperlink ref="E156" r:id="rId167" tooltip="Abrir" xr:uid="{5E31A16E-5835-48D4-BF1B-3A184D482B33}"/>
-    <hyperlink ref="E157" r:id="rId168" tooltip="Abrir" xr:uid="{69B6080D-05B6-4BD7-9AA5-2BF055931E0C}"/>
-    <hyperlink ref="C158" r:id="rId169" tooltip="Abrir" xr:uid="{25CF2774-4851-4218-9F0A-F0188E1303B9}"/>
-    <hyperlink ref="E159" r:id="rId170" tooltip="Abrir" xr:uid="{4E9AE86B-62B8-4494-AA43-593619EA6887}"/>
-    <hyperlink ref="E160" r:id="rId171" tooltip="Abrir" xr:uid="{9ECAA3D6-2754-4813-95CF-AE6439904B0A}"/>
-    <hyperlink ref="C161" r:id="rId172" tooltip="Abrir" xr:uid="{5E9E46CF-230E-4FC7-B392-6564E8D1FEE7}"/>
-    <hyperlink ref="E161" r:id="rId173" tooltip="Abrir" xr:uid="{59345E53-CA35-40E9-994C-3948C4B954E7}"/>
-    <hyperlink ref="E162" r:id="rId174" tooltip="Abrir" xr:uid="{6472ACD2-0A83-43ED-BCD5-98AA25389420}"/>
-    <hyperlink ref="C163" r:id="rId175" tooltip="Abrir" xr:uid="{E2BA1F7F-3584-415E-A24F-F17A393D1610}"/>
-    <hyperlink ref="C164" r:id="rId176" tooltip="Abrir" xr:uid="{11A06884-5546-4A59-A8E2-926C34F6AB28}"/>
-    <hyperlink ref="C165" r:id="rId177" tooltip="Abrir" xr:uid="{CC755ABC-3A59-40D9-957C-A1A24ABE7CD4}"/>
-    <hyperlink ref="C166" r:id="rId178" tooltip="Abrir" xr:uid="{45C90029-28C3-4E6E-BF33-F42B0480F285}"/>
-    <hyperlink ref="C167" r:id="rId179" tooltip="Abrir" xr:uid="{B310B482-B014-4850-85AA-29FB9AB6D498}"/>
-    <hyperlink ref="E167" r:id="rId180" tooltip="Abrir" xr:uid="{7F8FF049-B62B-4FF7-8773-F3057D73E00A}"/>
-    <hyperlink ref="C168" r:id="rId181" tooltip="Abrir" xr:uid="{5B00DE40-5B6A-4838-A768-373A1852635E}"/>
-    <hyperlink ref="E169" r:id="rId182" tooltip="Abrir" xr:uid="{ABFA76F1-706F-4B70-ADCC-51A70ABD91A8}"/>
-    <hyperlink ref="E170" r:id="rId183" tooltip="Abrir" xr:uid="{BE0AAAD3-80C0-49DA-916A-8D85AA8B6E23}"/>
-    <hyperlink ref="E171" r:id="rId184" tooltip="Abrir" xr:uid="{753AF08F-A2E1-4160-BCF3-7F689BBA1E04}"/>
-    <hyperlink ref="E172" r:id="rId185" tooltip="Abrir" xr:uid="{D391972B-7B63-4153-9C71-CAE70FF6FC1F}"/>
-    <hyperlink ref="C173" r:id="rId186" tooltip="Abrir" xr:uid="{A47A49E1-113B-4B9A-BA72-204C12456A2C}"/>
-    <hyperlink ref="E174" r:id="rId187" tooltip="Abrir" xr:uid="{9797824E-3326-40C6-B97F-2B7479E83B9D}"/>
-    <hyperlink ref="C175" r:id="rId188" tooltip="Abrir" xr:uid="{B6859F4F-EEA8-4C44-BF1C-12FFCAE55945}"/>
-    <hyperlink ref="C176" r:id="rId189" tooltip="Abrir" xr:uid="{4E1AAFEE-0819-49EB-80B3-039B3FB9416E}"/>
-    <hyperlink ref="E176" r:id="rId190" tooltip="Abrir" xr:uid="{093734ED-3DD6-4FE5-ABA5-1F6B4CBCED90}"/>
-    <hyperlink ref="E177" r:id="rId191" tooltip="Abrir" xr:uid="{44EB3130-1DC5-4206-A928-3FFDEA3DAA74}"/>
-    <hyperlink ref="E178" r:id="rId192" tooltip="Abrir" xr:uid="{39E728B0-92A2-44E2-800F-DF9EC03228AE}"/>
-    <hyperlink ref="E179" r:id="rId193" tooltip="Abrir" xr:uid="{74810D06-BEF9-44A5-A76C-A9ED0457473A}"/>
-    <hyperlink ref="E180" r:id="rId194" tooltip="Abrir" xr:uid="{D2BA2942-7B2F-4476-A81B-D8E9E2EEB099}"/>
-    <hyperlink ref="E181" r:id="rId195" tooltip="Abrir" xr:uid="{082B592B-4270-4648-B0F8-E79EED07547B}"/>
-    <hyperlink ref="C182" r:id="rId196" tooltip="Abrir" xr:uid="{E0C29173-9E1B-4023-8E5E-14E80C60444C}"/>
-    <hyperlink ref="E183" r:id="rId197" tooltip="Abrir" xr:uid="{61DD8A17-F6F0-4B1F-B309-0420CE1965D6}"/>
-    <hyperlink ref="C184" r:id="rId198" tooltip="Abrir" xr:uid="{1F2F830D-887B-4FDD-B23C-054FA8E10BCA}"/>
-    <hyperlink ref="E184" r:id="rId199" tooltip="Abrir" xr:uid="{94A3D0A2-3D25-4914-891F-E7F94ADA962C}"/>
-    <hyperlink ref="C185" r:id="rId200" tooltip="Abrir" xr:uid="{96C64E39-A2AC-44A9-9A7B-004761166304}"/>
-    <hyperlink ref="C186" r:id="rId201" tooltip="Abrir" xr:uid="{68C91F71-D5A6-42E9-96E8-23812358D679}"/>
-    <hyperlink ref="C187" r:id="rId202" tooltip="Abrir" xr:uid="{11F65986-6796-4167-A02B-6F24F418FC70}"/>
-    <hyperlink ref="E188" r:id="rId203" tooltip="Abrir" xr:uid="{50F4840A-F49A-4313-922F-45370A518826}"/>
-    <hyperlink ref="C189" r:id="rId204" tooltip="Abrir" xr:uid="{1C46ED21-7C26-42B9-97DA-D7CA8ACED76D}"/>
-    <hyperlink ref="C190" r:id="rId205" tooltip="Abrir" xr:uid="{8ADA2E4D-264E-46D1-8AA5-E028ABDDE8C3}"/>
-    <hyperlink ref="E191" r:id="rId206" tooltip="Abrir" xr:uid="{31DDB0DD-B919-4FCE-B9DF-4B7CDF23EC44}"/>
-    <hyperlink ref="C192" r:id="rId207" tooltip="Abrir" xr:uid="{523734B3-84E9-470F-97D1-060E62BEE5AF}"/>
-    <hyperlink ref="C193" r:id="rId208" tooltip="Abrir" xr:uid="{448EC363-09E9-456C-A366-D44CCB0E7CB0}"/>
-    <hyperlink ref="C194" r:id="rId209" tooltip="Abrir" xr:uid="{F5856DCF-8671-4FB8-9FCC-57BF40B2F1BE}"/>
-    <hyperlink ref="E195" r:id="rId210" tooltip="Abrir" xr:uid="{4CFADBFD-9FB0-4A9F-AE5A-DA7797701BCF}"/>
-    <hyperlink ref="C196" r:id="rId211" tooltip="Abrir" xr:uid="{E611CB0F-75C3-47CD-BE34-3DAB5E8CF857}"/>
-    <hyperlink ref="E197" r:id="rId212" tooltip="Abrir" xr:uid="{DB36DB05-FF24-4BB0-AC5D-F82DB5ECDCFD}"/>
-    <hyperlink ref="E198" r:id="rId213" tooltip="Abrir" xr:uid="{AA12E9FC-7065-4BCA-A53E-41856492BAA7}"/>
-    <hyperlink ref="E199" r:id="rId214" tooltip="Abrir" xr:uid="{A5D3E6E4-4FCF-49AB-AB4B-890A0B969F83}"/>
-    <hyperlink ref="E200" r:id="rId215" tooltip="Abrir" xr:uid="{ADD0858F-C6CA-4F47-BF43-4BC8A9976306}"/>
-    <hyperlink ref="E201" r:id="rId216" tooltip="Abrir" xr:uid="{3321A3ED-813B-482E-8221-8981CD22F31C}"/>
-    <hyperlink ref="C202" r:id="rId217" tooltip="Abrir" xr:uid="{FEBCE586-DF6A-4CE2-9FBC-ECA07F24ACD2}"/>
-    <hyperlink ref="C203" r:id="rId218" tooltip="Abrir" xr:uid="{A31FB4F3-2AE7-4B56-9645-B3204EB3AA62}"/>
-    <hyperlink ref="C204" r:id="rId219" tooltip="Abrir" xr:uid="{8C9A6164-7A8D-4D60-9913-6855C3AE894B}"/>
-    <hyperlink ref="E204" r:id="rId220" tooltip="Abrir" xr:uid="{DF53CA5D-6D9D-4E6B-8492-BE050AA5332B}"/>
-    <hyperlink ref="C205" r:id="rId221" tooltip="Abrir" xr:uid="{5125A3A0-DCDE-4AE4-A26F-8F38D6A27DC5}"/>
-    <hyperlink ref="E206" r:id="rId222" tooltip="Abrir" xr:uid="{6A411B32-11D3-4E50-8A14-791E04563255}"/>
-    <hyperlink ref="C207" r:id="rId223" tooltip="Abrir" xr:uid="{9B0ACBE9-6C91-44B0-9E11-2F966A6322A0}"/>
-    <hyperlink ref="E208" r:id="rId224" tooltip="Abrir" xr:uid="{512FD1C9-3B65-42E9-B5E0-E99019C5EB5C}"/>
-    <hyperlink ref="E209" r:id="rId225" tooltip="Abrir" xr:uid="{8173CC5B-A5F3-4F63-99D1-4D09034769CC}"/>
-    <hyperlink ref="C210" r:id="rId226" tooltip="Abrir" xr:uid="{EC9C07F9-A3AD-492A-9940-89824B71D523}"/>
-    <hyperlink ref="E210" r:id="rId227" tooltip="Abrir" xr:uid="{C4BE06E3-675F-4718-A85B-FEBD97A87191}"/>
-    <hyperlink ref="C211" r:id="rId228" tooltip="Abrir" xr:uid="{CA73C153-21B0-41DA-B357-B3572B7DA443}"/>
-    <hyperlink ref="E212" r:id="rId229" tooltip="Abrir" xr:uid="{4463174D-055D-47BD-9374-CC503CC7C52E}"/>
-    <hyperlink ref="C213" r:id="rId230" tooltip="Abrir" xr:uid="{DC57BDCC-5075-4210-8B5F-EE3D67C7D919}"/>
-    <hyperlink ref="C214" r:id="rId231" tooltip="Abrir" xr:uid="{50710A6F-4818-44DB-A688-FC3D462316EC}"/>
-    <hyperlink ref="C215" r:id="rId232" tooltip="Abrir" xr:uid="{FEDB44CB-EBA1-4AF3-A31D-A859E64AD7B1}"/>
-    <hyperlink ref="E215" r:id="rId233" tooltip="Abrir" xr:uid="{C00D1DBC-AA85-4255-BC78-E3EBD25E44E3}"/>
-    <hyperlink ref="E216" r:id="rId234" tooltip="Abrir" xr:uid="{3DD7D44E-8587-4884-92A3-F73A6E48766E}"/>
-    <hyperlink ref="E217" r:id="rId235" tooltip="Abrir" xr:uid="{1A861268-DA48-4F4F-8A53-7902CA5CC254}"/>
-    <hyperlink ref="C218" r:id="rId236" tooltip="Abrir" xr:uid="{8BA69A33-3015-4098-8496-8BBCBB64B055}"/>
-    <hyperlink ref="C219" r:id="rId237" tooltip="Abrir" xr:uid="{FE6BE3A3-5D76-4B36-97D6-2777C65AF63C}"/>
-    <hyperlink ref="E220" r:id="rId238" tooltip="Abrir" xr:uid="{73CBD840-CBB4-4EE9-9257-A3A7C4FC72BF}"/>
-    <hyperlink ref="C221" r:id="rId239" tooltip="Abrir" xr:uid="{2D8CA50F-CD56-47A1-AC6B-001E38E0299C}"/>
-    <hyperlink ref="E222" r:id="rId240" tooltip="Abrir" xr:uid="{224054D2-FE20-4CBA-AD65-008A2949EC99}"/>
-    <hyperlink ref="E223" r:id="rId241" tooltip="Abrir" xr:uid="{1E8D84EB-E016-4ABD-A068-64959622EA21}"/>
-    <hyperlink ref="C224" r:id="rId242" tooltip="Abrir" xr:uid="{8D7851F4-6993-4654-AF5A-A8733AF28F68}"/>
-    <hyperlink ref="E225" r:id="rId243" tooltip="Abrir" xr:uid="{C36E5929-9517-433C-9FB6-507798BF86BA}"/>
-    <hyperlink ref="C226" r:id="rId244" tooltip="Abrir" xr:uid="{96CFA27F-CDC0-4837-94AD-BE17CD49A0FA}"/>
-    <hyperlink ref="E227" r:id="rId245" tooltip="Abrir" xr:uid="{2EC11159-4A5B-4768-A369-21CAD2250172}"/>
-    <hyperlink ref="E228" r:id="rId246" tooltip="Abrir" xr:uid="{0B3DBBD6-7AAF-4C8C-9E6C-1AE6ED8D85A7}"/>
-    <hyperlink ref="E229" r:id="rId247" tooltip="Abrir" xr:uid="{765925A5-7D75-4531-B535-60901670B740}"/>
-    <hyperlink ref="E230" r:id="rId248" tooltip="Abrir" xr:uid="{B8FABFBC-F528-4DF6-A2A4-272805BFADF3}"/>
-    <hyperlink ref="E231" r:id="rId249" tooltip="Abrir" xr:uid="{9F1810A6-56FD-4091-B98A-0E2C871940E0}"/>
-    <hyperlink ref="C232" r:id="rId250" tooltip="Abrir" xr:uid="{7D1034C4-4315-4294-BD4B-68F9A87B75D3}"/>
-    <hyperlink ref="E233" r:id="rId251" tooltip="Abrir" xr:uid="{B7F32301-0BB6-40A9-B9C6-77158FD3F504}"/>
-    <hyperlink ref="C234" r:id="rId252" tooltip="Abrir" xr:uid="{A272D6B5-DDE8-4268-8929-EB760E65D608}"/>
-    <hyperlink ref="E234" r:id="rId253" tooltip="Abrir" xr:uid="{597B7452-88D7-4492-9EE4-9404FC82FDD1}"/>
-    <hyperlink ref="E235" r:id="rId254" tooltip="Abrir" xr:uid="{C74E5C24-A433-4DD0-B348-29F9A7637119}"/>
-    <hyperlink ref="C236" r:id="rId255" tooltip="Abrir" xr:uid="{6CEBE2F0-0183-432D-A90F-77A2A105FE72}"/>
-    <hyperlink ref="C237" r:id="rId256" tooltip="Abrir" xr:uid="{2D352E41-61D1-4B3A-BF8E-8FC98D5D1404}"/>
-    <hyperlink ref="E238" r:id="rId257" tooltip="Abrir" xr:uid="{F19147A5-E337-498E-AD9F-FC87E6726EC7}"/>
-    <hyperlink ref="E239" r:id="rId258" tooltip="Abrir" xr:uid="{069A909E-82BD-44DC-8E24-8FBA02A8F2A7}"/>
-    <hyperlink ref="C240" r:id="rId259" tooltip="Abrir" xr:uid="{B4982149-9A51-4D19-A5E0-5DE2A449AABF}"/>
-    <hyperlink ref="E241" r:id="rId260" tooltip="Abrir" xr:uid="{6869D439-14BD-499E-9D9E-0CF9A2FDB0A9}"/>
-    <hyperlink ref="C242" r:id="rId261" tooltip="Abrir" xr:uid="{43176566-6F04-4504-8833-3F9BAA078036}"/>
-    <hyperlink ref="C243" r:id="rId262" tooltip="Abrir" xr:uid="{467EC418-96E9-4ECD-A287-29BD7DA869E6}"/>
-    <hyperlink ref="E243" r:id="rId263" tooltip="Abrir" xr:uid="{69D1F11D-6065-4285-9A47-7008DB008B09}"/>
-    <hyperlink ref="E244" r:id="rId264" tooltip="Abrir" xr:uid="{F2164227-E2B9-4395-928A-2329F1D2BC97}"/>
-    <hyperlink ref="C245" r:id="rId265" tooltip="Abrir" xr:uid="{694A056C-C30B-44F3-A7A5-251460D37DE0}"/>
-    <hyperlink ref="C246" r:id="rId266" tooltip="Abrir" xr:uid="{D87F07AD-6BD9-4709-93D5-5D1918293587}"/>
-    <hyperlink ref="E247" r:id="rId267" tooltip="Abrir" xr:uid="{B5D8C032-396B-4A77-B6C2-ADDD6EDE32FD}"/>
-    <hyperlink ref="C248" r:id="rId268" tooltip="Abrir" xr:uid="{8C003D89-EF3E-4F6B-BCB7-5B58DAE0D16C}"/>
-    <hyperlink ref="E249" r:id="rId269" tooltip="Abrir" xr:uid="{4E29B7D3-61B6-448D-983B-E607CE835E87}"/>
-    <hyperlink ref="C250" r:id="rId270" tooltip="Abrir" xr:uid="{CFA67088-FEF9-4FE2-844E-618759EA42A2}"/>
-    <hyperlink ref="C251" r:id="rId271" tooltip="Abrir" xr:uid="{B6FDDD78-FFCF-43BC-91BB-F5CF14E9FBE1}"/>
-    <hyperlink ref="E252" r:id="rId272" tooltip="Abrir" xr:uid="{FCFEC6A5-A2BA-43AE-BF62-E7466CF20B40}"/>
+    <hyperlink ref="E2" r:id="rId1" tooltip="Abrir" xr:uid="{3A2A5880-4513-4C1E-806A-2436684F1181}"/>
+    <hyperlink ref="C3" r:id="rId2" tooltip="Abrir" xr:uid="{69273A75-A79B-4A08-B7F7-1C02E8C8629B}"/>
+    <hyperlink ref="E4" r:id="rId3" tooltip="Abrir" xr:uid="{7671E440-11EF-44F4-850D-D95E3954A8C2}"/>
+    <hyperlink ref="C5" r:id="rId4" tooltip="Abrir" xr:uid="{E094D177-8E45-42FC-A370-70CF1EB0B4AE}"/>
+    <hyperlink ref="C6" r:id="rId5" tooltip="Abrir" xr:uid="{2CA34661-91E4-4899-A8E1-556ED9AB9468}"/>
+    <hyperlink ref="C7" r:id="rId6" tooltip="Abrir" xr:uid="{A72AF812-EB91-4CDD-A1EB-0A02949DD2B5}"/>
+    <hyperlink ref="C8" r:id="rId7" tooltip="Abrir" xr:uid="{70B13848-3E3B-40B9-81A3-15508E7BA462}"/>
+    <hyperlink ref="E9" r:id="rId8" tooltip="Abrir" xr:uid="{60069A10-4D92-4D41-A9DB-3737CFF18CEF}"/>
+    <hyperlink ref="C10" r:id="rId9" tooltip="Abrir" xr:uid="{01D3ED66-A750-4697-9731-5E710787FE61}"/>
+    <hyperlink ref="C11" r:id="rId10" tooltip="Abrir" xr:uid="{85073FF1-BCEC-4660-B418-97AD2126A60F}"/>
+    <hyperlink ref="C12" r:id="rId11" tooltip="Abrir" xr:uid="{2BFA7E4C-5B3B-46CF-BF13-B16EF448C707}"/>
+    <hyperlink ref="E13" r:id="rId12" tooltip="Abrir" xr:uid="{A26D65BF-0A57-4B3A-9353-18A81838223D}"/>
+    <hyperlink ref="C14" r:id="rId13" tooltip="Abrir" xr:uid="{93FD4ECB-7529-4C83-B053-9BEC1D6AC5E1}"/>
+    <hyperlink ref="E14" r:id="rId14" tooltip="Abrir" xr:uid="{32F09711-6E1A-4E5A-8649-5B3D70A8B4DD}"/>
+    <hyperlink ref="E15" r:id="rId15" tooltip="Abrir" xr:uid="{032CB391-3BEE-499C-9233-5FEAD91AFE37}"/>
+    <hyperlink ref="C16" r:id="rId16" tooltip="Abrir" xr:uid="{591A4010-3E96-4661-8CAD-76E3E849EA06}"/>
+    <hyperlink ref="C17" r:id="rId17" tooltip="Abrir" xr:uid="{3ACEE7FE-3547-4CDE-8DF1-73F9419DD0ED}"/>
+    <hyperlink ref="E18" r:id="rId18" tooltip="Abrir" xr:uid="{4321688D-982B-4179-91B1-CC2F301FAC43}"/>
+    <hyperlink ref="E19" r:id="rId19" tooltip="Abrir" xr:uid="{167811F3-B20D-485D-8393-C1D9B4D2198F}"/>
+    <hyperlink ref="C20" r:id="rId20" tooltip="Abrir" xr:uid="{BBC79BA2-D882-4884-9E91-36C4C6151F3C}"/>
+    <hyperlink ref="E21" r:id="rId21" tooltip="Abrir" xr:uid="{AFB1DD2A-ED45-43D3-B993-899CDA3A60D7}"/>
+    <hyperlink ref="C22" r:id="rId22" tooltip="Abrir" xr:uid="{9EA900FE-182C-4058-AB7E-A45438AE0656}"/>
+    <hyperlink ref="C23" r:id="rId23" tooltip="Abrir" xr:uid="{FADCADC5-7D20-40D7-A6DF-7BF3DA1371C2}"/>
+    <hyperlink ref="E24" r:id="rId24" tooltip="Abrir" xr:uid="{79E856B9-51DD-4EED-869B-100E4897D03F}"/>
+    <hyperlink ref="E25" r:id="rId25" tooltip="Abrir" xr:uid="{E3E8D3A6-559C-45A9-A7B0-7B67BEC35833}"/>
+    <hyperlink ref="C26" r:id="rId26" tooltip="Abrir" xr:uid="{55B26EA3-D5E3-4FBA-A840-E6C1DADB39EB}"/>
+    <hyperlink ref="C27" r:id="rId27" tooltip="Abrir" xr:uid="{45F05344-D8D3-47D0-8BE2-28A6C6E13623}"/>
+    <hyperlink ref="C28" r:id="rId28" tooltip="Abrir" xr:uid="{6A515B99-2C17-4C32-82E5-762484FE2982}"/>
+    <hyperlink ref="E29" r:id="rId29" tooltip="Abrir" xr:uid="{E083915E-D65A-4FFB-910D-9693A0AF3A86}"/>
+    <hyperlink ref="E30" r:id="rId30" tooltip="Abrir" xr:uid="{5B34B677-21BA-401A-9F07-858C71527A19}"/>
+    <hyperlink ref="E31" r:id="rId31" tooltip="Abrir" xr:uid="{9E12B458-23BF-4F45-96B5-0C3EBF5BD8F6}"/>
+    <hyperlink ref="E32" r:id="rId32" tooltip="Abrir" xr:uid="{879F508B-8A3E-471E-A88E-DF54851C9AC4}"/>
+    <hyperlink ref="C33" r:id="rId33" tooltip="Abrir" xr:uid="{FF075D0C-06FE-431F-ADE1-43CBC450343E}"/>
+    <hyperlink ref="E34" r:id="rId34" tooltip="Abrir" xr:uid="{87818694-2C3A-4F19-B89E-0A7A5B27A759}"/>
+    <hyperlink ref="C35" r:id="rId35" tooltip="Abrir" xr:uid="{71E1D603-FD58-4947-84C9-45856C524352}"/>
+    <hyperlink ref="C36" r:id="rId36" tooltip="Abrir" xr:uid="{62217CAA-C554-4001-AF5E-3CABE7A3EE35}"/>
+    <hyperlink ref="E37" r:id="rId37" tooltip="Abrir" xr:uid="{6B11AB16-3025-4A59-BA13-F0324AA5E136}"/>
+    <hyperlink ref="C38" r:id="rId38" tooltip="Abrir" xr:uid="{AE269BE0-CC60-4F64-B62B-8845EB702A8C}"/>
+    <hyperlink ref="C39" r:id="rId39" tooltip="Abrir" xr:uid="{C9671566-794B-4D32-A531-743AA32BFD62}"/>
+    <hyperlink ref="C40" r:id="rId40" tooltip="Abrir" xr:uid="{696C4271-41A6-4F46-98F7-E2A4DF230E60}"/>
+    <hyperlink ref="E41" r:id="rId41" tooltip="Abrir" xr:uid="{163431B6-B2C3-44F0-A94A-B537ED6AC467}"/>
+    <hyperlink ref="C42" r:id="rId42" tooltip="Abrir" xr:uid="{20D7D0D6-607E-422C-B779-D73C415642FC}"/>
+    <hyperlink ref="E42" r:id="rId43" tooltip="Abrir" xr:uid="{0662047B-BE79-4832-BF7D-E43B72B63700}"/>
+    <hyperlink ref="E43" r:id="rId44" tooltip="Abrir" xr:uid="{5239C386-BF25-409B-A9BE-063E704A80DB}"/>
+    <hyperlink ref="C44" r:id="rId45" tooltip="Abrir" xr:uid="{80968F04-D707-46B4-A6CC-9688666E11AB}"/>
+    <hyperlink ref="E45" r:id="rId46" tooltip="Abrir" xr:uid="{1417F4E9-4CD5-4A41-B94D-875758868EF8}"/>
+    <hyperlink ref="C46" r:id="rId47" tooltip="Abrir" xr:uid="{716325E5-F963-405E-9609-B02770B6E1D9}"/>
+    <hyperlink ref="E47" r:id="rId48" tooltip="Abrir" xr:uid="{F45C6F0A-A494-429D-949C-B1F7CEF43D6E}"/>
+    <hyperlink ref="C48" r:id="rId49" tooltip="Abrir" xr:uid="{EFEE8F01-C7DD-4526-952F-C76C7CCD9C62}"/>
+    <hyperlink ref="E49" r:id="rId50" tooltip="Abrir" xr:uid="{884C4D94-3225-4229-83D6-6DC1487A7C5A}"/>
+    <hyperlink ref="C50" r:id="rId51" tooltip="Abrir" xr:uid="{54E12DF3-357B-4855-BB61-9015F36185CF}"/>
+    <hyperlink ref="C51" r:id="rId52" tooltip="Abrir" xr:uid="{EDF10CF4-AD72-4454-A835-1DCF8482C61F}"/>
+    <hyperlink ref="E52" r:id="rId53" tooltip="Abrir" xr:uid="{A271F0D2-CF9B-4DE2-952B-DB8F70BF5B3F}"/>
+    <hyperlink ref="C53" r:id="rId54" tooltip="Abrir" xr:uid="{886DBC68-54A6-472F-A337-D2E6C84B28A0}"/>
+    <hyperlink ref="E54" r:id="rId55" tooltip="Abrir" xr:uid="{2613B379-4386-4F76-B1B8-06CFD3CE0AC0}"/>
+    <hyperlink ref="E55" r:id="rId56" tooltip="Abrir" xr:uid="{9C20DF72-3CB7-4178-A22F-142FE47E9662}"/>
+    <hyperlink ref="C56" r:id="rId57" tooltip="Abrir" xr:uid="{F4B01D4E-A913-4CEA-87E1-0BABB03A88EE}"/>
+    <hyperlink ref="C57" r:id="rId58" tooltip="Abrir" xr:uid="{17B625DA-8797-49B2-9D04-BA88540639AC}"/>
+    <hyperlink ref="E58" r:id="rId59" tooltip="Abrir" xr:uid="{94956F76-785D-474C-A15C-CA24EBD3D5F9}"/>
+    <hyperlink ref="C59" r:id="rId60" tooltip="Abrir" xr:uid="{BD20DAA5-8554-48EF-9006-528D8E6A24D6}"/>
+    <hyperlink ref="C60" r:id="rId61" tooltip="Abrir" xr:uid="{105D3733-06A2-40AB-BBD4-B7CC17DCDCCD}"/>
+    <hyperlink ref="C61" r:id="rId62" tooltip="Abrir" xr:uid="{32CE3044-D86E-4026-8DE8-4BB477913BA5}"/>
+    <hyperlink ref="E61" r:id="rId63" tooltip="Abrir" xr:uid="{6C2C0AD0-FCE4-426F-9E11-481BFBD6C2B7}"/>
+    <hyperlink ref="E62" r:id="rId64" tooltip="Abrir" xr:uid="{B34348F2-32CE-483E-8948-C92F16521A9C}"/>
+    <hyperlink ref="C63" r:id="rId65" tooltip="Abrir" xr:uid="{E62AF935-AE31-4322-9A11-E08510184E36}"/>
+    <hyperlink ref="E63" r:id="rId66" tooltip="Abrir" xr:uid="{F1AE0F3F-8926-4EA7-ADEE-CA000F351892}"/>
+    <hyperlink ref="C64" r:id="rId67" tooltip="Abrir" xr:uid="{92782482-C953-461B-84B2-006AAF06470B}"/>
+    <hyperlink ref="C65" r:id="rId68" tooltip="Abrir" xr:uid="{4C726B8A-6ED8-4C77-99BF-283BA2285382}"/>
+    <hyperlink ref="C66" r:id="rId69" tooltip="Abrir" xr:uid="{3D7A0694-A8E7-4C8E-98DA-9D571311F41D}"/>
+    <hyperlink ref="C67" r:id="rId70" tooltip="Abrir" xr:uid="{26762FD3-7BDA-4139-8B16-E0136EDA1156}"/>
+    <hyperlink ref="E68" r:id="rId71" tooltip="Abrir" xr:uid="{EBEE8EC8-3C9F-44AF-A609-13AC3C64F8ED}"/>
+    <hyperlink ref="E69" r:id="rId72" tooltip="Abrir" xr:uid="{39B10451-377C-4D45-B08F-C8454AB0E15C}"/>
+    <hyperlink ref="C70" r:id="rId73" tooltip="Abrir" xr:uid="{90676A6C-C015-4CCA-85AE-7AF721E1B0CC}"/>
+    <hyperlink ref="E70" r:id="rId74" tooltip="Abrir" xr:uid="{0AA6EC7A-2694-4C0E-AE4F-A49A57E5C3CE}"/>
+    <hyperlink ref="E71" r:id="rId75" tooltip="Abrir" xr:uid="{B18DCF89-8F45-49C2-92D4-AE2D03F95A71}"/>
+    <hyperlink ref="C72" r:id="rId76" tooltip="Abrir" xr:uid="{3070AA19-8AE3-4F61-A3CD-97E375225F1E}"/>
+    <hyperlink ref="C73" r:id="rId77" tooltip="Abrir" xr:uid="{061EAF8C-C594-4AE6-81C5-14C6848B79C5}"/>
+    <hyperlink ref="C74" r:id="rId78" tooltip="Abrir" xr:uid="{2E7ADD9B-2F34-4F3C-9A26-2B88EBA8F5F3}"/>
+    <hyperlink ref="E74" r:id="rId79" tooltip="Abrir" xr:uid="{FABD735D-52BA-48FB-A165-5B8C1E635565}"/>
+    <hyperlink ref="C75" r:id="rId80" tooltip="Abrir" xr:uid="{650791FC-49B6-4152-B9CB-BAD0571903FE}"/>
+    <hyperlink ref="E76" r:id="rId81" tooltip="Abrir" xr:uid="{6DF60BB7-9EE1-43AD-84AB-AE1B36C6EE34}"/>
+    <hyperlink ref="C77" r:id="rId82" tooltip="Abrir" xr:uid="{40EFAA96-8312-4D12-A16D-F6EEB8D44D5B}"/>
+    <hyperlink ref="E77" r:id="rId83" tooltip="Abrir" xr:uid="{A2C608D1-2BC9-4459-AA97-48DD27A6101A}"/>
+    <hyperlink ref="E78" r:id="rId84" tooltip="Abrir" xr:uid="{1342EAC4-00AB-43CE-8954-3F058E74005A}"/>
+    <hyperlink ref="C79" r:id="rId85" tooltip="Abrir" xr:uid="{60A9D7F7-1FCB-42BC-847C-984948BAAC5A}"/>
+    <hyperlink ref="C80" r:id="rId86" tooltip="Abrir" xr:uid="{50ADD295-8338-4F58-B7A3-D848CBCC6D5B}"/>
+    <hyperlink ref="E80" r:id="rId87" tooltip="Abrir" xr:uid="{0A57B9CA-AE54-45ED-9C41-9FC6C065045D}"/>
+    <hyperlink ref="E81" r:id="rId88" tooltip="Abrir" xr:uid="{93E7D522-BE8C-4F5E-AB37-5B197D0F4A38}"/>
+    <hyperlink ref="E82" r:id="rId89" tooltip="Abrir" xr:uid="{1EAF06A3-44A6-48CD-A847-4FC1AA9CA98A}"/>
+    <hyperlink ref="E83" r:id="rId90" tooltip="Abrir" xr:uid="{0E2FFB3F-D534-46E1-B15B-9CAFB210D379}"/>
+    <hyperlink ref="C84" r:id="rId91" tooltip="Abrir" xr:uid="{2E2DF435-16F0-41C4-9492-40C1DEE15C71}"/>
+    <hyperlink ref="C85" r:id="rId92" tooltip="Abrir" xr:uid="{9A11E199-43EB-49A8-9E26-0176D3EAA20E}"/>
+    <hyperlink ref="E86" r:id="rId93" tooltip="Abrir" xr:uid="{63B12F5F-D6DC-4C79-8D96-27145CBE430B}"/>
+    <hyperlink ref="C87" r:id="rId94" tooltip="Abrir" xr:uid="{C6F7B72E-C71A-47A6-981C-A8D0D0CA02C6}"/>
+    <hyperlink ref="E87" r:id="rId95" tooltip="Abrir" xr:uid="{C499A430-96FC-4A71-B14F-78EB125A4051}"/>
+    <hyperlink ref="C88" r:id="rId96" tooltip="Abrir" xr:uid="{7D9FFB22-57F9-48CD-88D2-F4837BC054EF}"/>
+    <hyperlink ref="E89" r:id="rId97" tooltip="Abrir" xr:uid="{96DDCAB8-5567-43A0-9624-A054760B2515}"/>
+    <hyperlink ref="C90" r:id="rId98" tooltip="Abrir" xr:uid="{83A5FFAB-B99E-4016-A716-BD3584D9B9CA}"/>
+    <hyperlink ref="E91" r:id="rId99" tooltip="Abrir" xr:uid="{3FDFF0A1-EDD2-4E19-9D07-38773EF77EE7}"/>
+    <hyperlink ref="E92" r:id="rId100" tooltip="Abrir" xr:uid="{6F1AB874-3285-4AA9-8195-6FB18EB88F07}"/>
+    <hyperlink ref="E93" r:id="rId101" tooltip="Abrir" xr:uid="{EF5459EA-AE04-47D3-8808-E8131DE5175B}"/>
+    <hyperlink ref="C94" r:id="rId102" tooltip="Abrir" xr:uid="{A50EE8F8-760D-4B33-8EAD-498FD9E07A48}"/>
+    <hyperlink ref="E95" r:id="rId103" tooltip="Abrir" xr:uid="{7335943F-4380-4B1C-ABCE-FDCF21C9832A}"/>
+    <hyperlink ref="E96" r:id="rId104" tooltip="Abrir" xr:uid="{33767306-6E3C-4CC7-B59C-2EFD4133BB00}"/>
+    <hyperlink ref="E97" r:id="rId105" tooltip="Abrir" xr:uid="{09C538B1-7A15-4896-ABB5-8CF8DE9B4E43}"/>
+    <hyperlink ref="E98" r:id="rId106" tooltip="Abrir" xr:uid="{C2A73C1D-6808-4208-A508-143A8B2E6B32}"/>
+    <hyperlink ref="C99" r:id="rId107" tooltip="Abrir" xr:uid="{015738AD-C5B7-4936-824D-26D9AD24776E}"/>
+    <hyperlink ref="E100" r:id="rId108" tooltip="Abrir" xr:uid="{67996164-A6F2-4275-A18E-CF41AC10AEC5}"/>
+    <hyperlink ref="E101" r:id="rId109" tooltip="Abrir" xr:uid="{D1570B8A-FA47-4E99-89B9-296EE2E79DCD}"/>
+    <hyperlink ref="E102" r:id="rId110" tooltip="Abrir" xr:uid="{558077F0-5DE0-463D-B051-9554D4D41A32}"/>
+    <hyperlink ref="C103" r:id="rId111" tooltip="Abrir" xr:uid="{503C1975-042E-4A7E-BD1E-A6193BB31ED1}"/>
+    <hyperlink ref="E104" r:id="rId112" tooltip="Abrir" xr:uid="{C13B45F3-E4FF-4C3C-8829-D48F2CE019BA}"/>
+    <hyperlink ref="C105" r:id="rId113" tooltip="Abrir" xr:uid="{953A8DA4-8478-41C2-A7DA-EDDCC704E59E}"/>
+    <hyperlink ref="E105" r:id="rId114" tooltip="Abrir" xr:uid="{6479A34D-8F94-4198-B92E-74BC29320F0F}"/>
+    <hyperlink ref="C106" r:id="rId115" tooltip="Abrir" xr:uid="{25C57CE7-5E73-4531-9E94-45EB82B25F90}"/>
+    <hyperlink ref="E107" r:id="rId116" tooltip="Abrir" xr:uid="{5205C6F3-7C58-43AC-97AB-5B2CD56D3CFA}"/>
+    <hyperlink ref="C108" r:id="rId117" tooltip="Abrir" xr:uid="{888DB5A0-B77B-4C27-B2E2-C1B94D11A0CF}"/>
+    <hyperlink ref="C109" r:id="rId118" tooltip="Abrir" xr:uid="{004D0D15-ADAA-4FF3-A1EB-B7A28B99B55F}"/>
+    <hyperlink ref="E109" r:id="rId119" tooltip="Abrir" xr:uid="{A750F1F5-FAF2-40E6-A1E5-E15B33710C5C}"/>
+    <hyperlink ref="E110" r:id="rId120" tooltip="Abrir" xr:uid="{67529702-5C39-4D6D-8853-2D3EF33B7E7F}"/>
+    <hyperlink ref="C111" r:id="rId121" tooltip="Abrir" xr:uid="{577CFFB0-5AF1-42B7-BC8C-DECA89F61F3A}"/>
+    <hyperlink ref="C112" r:id="rId122" tooltip="Abrir" xr:uid="{35B3F594-C4A0-49AF-B140-912501AE8647}"/>
+    <hyperlink ref="E113" r:id="rId123" tooltip="Abrir" xr:uid="{380F81DC-9ADB-4D4B-B4D7-D5821D0CDCE7}"/>
+    <hyperlink ref="C114" r:id="rId124" tooltip="Abrir" xr:uid="{47A17D1A-9FFF-409B-8E1F-196EE69CE530}"/>
+    <hyperlink ref="C115" r:id="rId125" tooltip="Abrir" xr:uid="{1BF9D3CD-A73F-4754-86B8-DCC6321619AA}"/>
+    <hyperlink ref="C116" r:id="rId126" tooltip="Abrir" xr:uid="{E4EFDCA8-82FA-46CB-85B7-4C08140627C2}"/>
+    <hyperlink ref="E116" r:id="rId127" tooltip="Abrir" xr:uid="{AD69508A-01A8-43EB-BD75-8B8E0DD79536}"/>
+    <hyperlink ref="C117" r:id="rId128" tooltip="Abrir" xr:uid="{C9081BBF-4D86-495C-80EB-4B6CF6174721}"/>
+    <hyperlink ref="C118" r:id="rId129" tooltip="Abrir" xr:uid="{024E9DC0-FD73-4C48-8053-77897C1FC2A6}"/>
+    <hyperlink ref="E119" r:id="rId130" tooltip="Abrir" xr:uid="{9BC317EA-057E-4891-8C5A-E08413071958}"/>
+    <hyperlink ref="C120" r:id="rId131" tooltip="Abrir" xr:uid="{3D54844D-342B-4F2B-997C-E7237FEACE7D}"/>
+    <hyperlink ref="C121" r:id="rId132" tooltip="Abrir" xr:uid="{79957F58-175B-470D-9C2C-034C8513659F}"/>
+    <hyperlink ref="C122" r:id="rId133" tooltip="Abrir" xr:uid="{BFB14150-EB9A-4408-96AF-DED663C5EF7F}"/>
+    <hyperlink ref="E123" r:id="rId134" tooltip="Abrir" xr:uid="{9AA7E02E-A31C-42F4-9387-60BAA82F2640}"/>
+    <hyperlink ref="E124" r:id="rId135" tooltip="Abrir" xr:uid="{0A7ED8F9-29A1-432A-BAAE-9B50043FA062}"/>
+    <hyperlink ref="E125" r:id="rId136" tooltip="Abrir" xr:uid="{9D13AC2F-F617-4A99-9207-0AE987F4880E}"/>
+    <hyperlink ref="E126" r:id="rId137" tooltip="Abrir" xr:uid="{CB569654-5D04-429B-A344-6CA6D64FE5F0}"/>
+    <hyperlink ref="E127" r:id="rId138" tooltip="Abrir" xr:uid="{BF5BAB4B-A699-4DFE-9258-1B7755CE6769}"/>
+    <hyperlink ref="E128" r:id="rId139" tooltip="Abrir" xr:uid="{F726E704-FA9C-4A4C-9FB7-2646FF1EC198}"/>
+    <hyperlink ref="C129" r:id="rId140" tooltip="Abrir" xr:uid="{4A532B9D-5349-4CE8-921C-E788891EDBB4}"/>
+    <hyperlink ref="E130" r:id="rId141" tooltip="Abrir" xr:uid="{1D0106E3-9C55-4B11-8B98-E280AFFC5138}"/>
+    <hyperlink ref="E131" r:id="rId142" tooltip="Abrir" xr:uid="{E1672195-1960-4C1E-802B-CD5574604655}"/>
+    <hyperlink ref="C132" r:id="rId143" tooltip="Abrir" xr:uid="{8E58985A-516D-453B-9FF8-5DC41DD81AC9}"/>
+    <hyperlink ref="E133" r:id="rId144" tooltip="Abrir" xr:uid="{D7FCB0CD-4E53-4818-B0A7-DF5AB932FF77}"/>
+    <hyperlink ref="C134" r:id="rId145" tooltip="Abrir" xr:uid="{576A4AC2-1A51-44EC-B059-53D9F9CD17E7}"/>
+    <hyperlink ref="E135" r:id="rId146" tooltip="Abrir" xr:uid="{F4AED695-0F1D-4637-BC43-81CB7D54A126}"/>
+    <hyperlink ref="C136" r:id="rId147" tooltip="Abrir" xr:uid="{00F36C7B-FD55-4496-A1B0-F64BF117C13E}"/>
+    <hyperlink ref="E137" r:id="rId148" tooltip="Abrir" xr:uid="{83D07784-0392-4879-8847-25316886DEA7}"/>
+    <hyperlink ref="E138" r:id="rId149" tooltip="Abrir" xr:uid="{A8C65B1B-D212-4B76-8F2E-5A8F409D49B3}"/>
+    <hyperlink ref="E139" r:id="rId150" tooltip="Abrir" xr:uid="{259C8A28-6D74-4F77-A9A8-C15BA3C16FAC}"/>
+    <hyperlink ref="C140" r:id="rId151" tooltip="Abrir" xr:uid="{3B01C53B-191C-46DA-B6F2-E5A7E0B26FF7}"/>
+    <hyperlink ref="C141" r:id="rId152" tooltip="Abrir" xr:uid="{B96F6D3F-BA3B-4CC8-BEC3-BED30FECA66D}"/>
+    <hyperlink ref="E142" r:id="rId153" tooltip="Abrir" xr:uid="{20737A53-388A-43F2-A823-8772D47B2037}"/>
+    <hyperlink ref="E143" r:id="rId154" tooltip="Abrir" xr:uid="{66A55CDB-1100-4EFD-B6C2-0068FFB815EE}"/>
+    <hyperlink ref="E144" r:id="rId155" tooltip="Abrir" xr:uid="{1C820C5A-E421-4497-82F8-D4F492C5C44B}"/>
+    <hyperlink ref="C145" r:id="rId156" tooltip="Abrir" xr:uid="{AF9058B5-E9AC-4231-BC40-81CF2B26D59F}"/>
+    <hyperlink ref="E146" r:id="rId157" tooltip="Abrir" xr:uid="{819724C0-A39D-48E7-9732-203B084511AA}"/>
+    <hyperlink ref="E147" r:id="rId158" tooltip="Abrir" xr:uid="{CEE89A70-70F2-4CE9-B5F1-C81610E0799D}"/>
+    <hyperlink ref="E148" r:id="rId159" tooltip="Abrir" xr:uid="{2D599E1D-D78D-46DC-B81C-087D819FED03}"/>
+    <hyperlink ref="E149" r:id="rId160" tooltip="Abrir" xr:uid="{E88F68C9-CB0B-4975-A36A-14052F5A4D73}"/>
+    <hyperlink ref="C150" r:id="rId161" tooltip="Abrir" xr:uid="{A4AEAB9B-F520-4FC9-B4C0-EC28FECB7541}"/>
+    <hyperlink ref="E151" r:id="rId162" tooltip="Abrir" xr:uid="{890DF849-4944-4E42-B7C0-7757771A21E9}"/>
+    <hyperlink ref="E152" r:id="rId163" tooltip="Abrir" xr:uid="{B63E4434-3336-405C-B4D2-CFC6AAB34C42}"/>
+    <hyperlink ref="C153" r:id="rId164" tooltip="Abrir" xr:uid="{93147E14-3219-4ED2-9E87-56B6C31C9385}"/>
+    <hyperlink ref="C154" r:id="rId165" tooltip="Abrir" xr:uid="{F1E24201-7869-4E14-82CC-1D6184A1B085}"/>
+    <hyperlink ref="C155" r:id="rId166" tooltip="Abrir" xr:uid="{72A3EE8F-EADE-472C-98C0-5FE85072DBE8}"/>
+    <hyperlink ref="E156" r:id="rId167" tooltip="Abrir" xr:uid="{3E677352-6084-436D-B05F-2D55FD6BA707}"/>
+    <hyperlink ref="E157" r:id="rId168" tooltip="Abrir" xr:uid="{EBD68DBC-5575-4E5A-A55D-C7AFAE08A00C}"/>
+    <hyperlink ref="C158" r:id="rId169" tooltip="Abrir" xr:uid="{FBDDED30-CDF2-4446-8C73-F44F715903DB}"/>
+    <hyperlink ref="E159" r:id="rId170" tooltip="Abrir" xr:uid="{146F3C48-DA7F-472F-BB59-382ADDFDF598}"/>
+    <hyperlink ref="E160" r:id="rId171" tooltip="Abrir" xr:uid="{FCA59CBC-2C97-4B69-A872-554230DB7E63}"/>
+    <hyperlink ref="C161" r:id="rId172" tooltip="Abrir" xr:uid="{366BCF69-35DD-4309-B26D-7A6F69CEFA8C}"/>
+    <hyperlink ref="E161" r:id="rId173" tooltip="Abrir" xr:uid="{4B2E8E2F-1573-47FE-88E3-A9F43AD1126F}"/>
+    <hyperlink ref="E162" r:id="rId174" tooltip="Abrir" xr:uid="{00A1B05D-61DC-42E3-BB33-C944668F976A}"/>
+    <hyperlink ref="C163" r:id="rId175" tooltip="Abrir" xr:uid="{D2CB7542-4E48-49CF-8038-8B4705C7971F}"/>
+    <hyperlink ref="C164" r:id="rId176" tooltip="Abrir" xr:uid="{03CDCCB9-8704-4220-A859-B9C41CEA993E}"/>
+    <hyperlink ref="C165" r:id="rId177" tooltip="Abrir" xr:uid="{7A367811-9F83-4BDF-A52C-2C30B4BCC83D}"/>
+    <hyperlink ref="C166" r:id="rId178" tooltip="Abrir" xr:uid="{EA6ECB7E-9935-49C5-803C-1D4BE073F513}"/>
+    <hyperlink ref="C167" r:id="rId179" tooltip="Abrir" xr:uid="{90C470F9-55DC-40F9-B652-931285C14527}"/>
+    <hyperlink ref="E167" r:id="rId180" tooltip="Abrir" xr:uid="{C9DFB841-4356-4D08-8C6C-F56F82EF8218}"/>
+    <hyperlink ref="C168" r:id="rId181" tooltip="Abrir" xr:uid="{05E94A8F-75FB-490F-AF0F-CF012E49E567}"/>
+    <hyperlink ref="E169" r:id="rId182" tooltip="Abrir" xr:uid="{3C371CB6-0E81-4499-AD63-47B0EAB5CFBC}"/>
+    <hyperlink ref="E170" r:id="rId183" tooltip="Abrir" xr:uid="{6F9CBC02-2A6E-491E-96AD-297F7ACC98A2}"/>
+    <hyperlink ref="E171" r:id="rId184" tooltip="Abrir" xr:uid="{96EACE93-262D-44D7-A3B5-E269CBCE7557}"/>
+    <hyperlink ref="E172" r:id="rId185" tooltip="Abrir" xr:uid="{D400E0C7-4409-4958-8E51-48A0BCA6C405}"/>
+    <hyperlink ref="C173" r:id="rId186" tooltip="Abrir" xr:uid="{235B1B74-5FDC-410E-8F9B-E35C9B7912E1}"/>
+    <hyperlink ref="E174" r:id="rId187" tooltip="Abrir" xr:uid="{6922019F-ABDF-43AF-BE61-1232A9E76386}"/>
+    <hyperlink ref="C175" r:id="rId188" tooltip="Abrir" xr:uid="{DD76E2B2-9D37-4690-9E7C-358570848102}"/>
+    <hyperlink ref="C176" r:id="rId189" tooltip="Abrir" xr:uid="{33610603-599A-4723-9F5C-ECCAB602E72A}"/>
+    <hyperlink ref="E176" r:id="rId190" tooltip="Abrir" xr:uid="{BBB5CED3-3A74-44B4-B601-5DDC9841743E}"/>
+    <hyperlink ref="E177" r:id="rId191" tooltip="Abrir" xr:uid="{6B1692F2-A57B-42A8-8EC7-63930E4186AD}"/>
+    <hyperlink ref="E178" r:id="rId192" tooltip="Abrir" xr:uid="{D6BFA15F-B029-4E03-A7A6-8BE54CFA2250}"/>
+    <hyperlink ref="E179" r:id="rId193" tooltip="Abrir" xr:uid="{CB55E54D-6368-4350-9471-C602878A760F}"/>
+    <hyperlink ref="E180" r:id="rId194" tooltip="Abrir" xr:uid="{E89DFE2E-75AF-461F-A291-C1E1CFF51DB1}"/>
+    <hyperlink ref="E181" r:id="rId195" tooltip="Abrir" xr:uid="{E258B2CD-CEE2-408B-94A8-4D7E2039EC4F}"/>
+    <hyperlink ref="C182" r:id="rId196" tooltip="Abrir" xr:uid="{53738BED-D97B-40F7-8C6B-66C8648743AB}"/>
+    <hyperlink ref="E183" r:id="rId197" tooltip="Abrir" xr:uid="{2E01F112-6FE5-438E-ADE4-BC3319B8D916}"/>
+    <hyperlink ref="C184" r:id="rId198" tooltip="Abrir" xr:uid="{AC954F55-8D7B-4B74-A6D1-B5074A13F343}"/>
+    <hyperlink ref="E184" r:id="rId199" tooltip="Abrir" xr:uid="{26191FD1-E2F4-4543-80E1-4EB4807E3355}"/>
+    <hyperlink ref="C185" r:id="rId200" tooltip="Abrir" xr:uid="{A8C99C2B-D510-42ED-89B8-28E93E4C142C}"/>
+    <hyperlink ref="C186" r:id="rId201" tooltip="Abrir" xr:uid="{E21F7A8F-3C0C-4504-9642-B04BEFBF0B05}"/>
+    <hyperlink ref="C187" r:id="rId202" tooltip="Abrir" xr:uid="{5B2DE61A-3A90-4B5C-AA3A-B350D7278554}"/>
+    <hyperlink ref="E188" r:id="rId203" tooltip="Abrir" xr:uid="{C04716BA-ABD2-4B14-888D-1EC82018E020}"/>
+    <hyperlink ref="C189" r:id="rId204" tooltip="Abrir" xr:uid="{BCC2E9AF-5116-4CE7-A55A-1F76B9E7C4AA}"/>
+    <hyperlink ref="C190" r:id="rId205" tooltip="Abrir" xr:uid="{207C9EC7-DF30-4D36-8919-3550E642D958}"/>
+    <hyperlink ref="E191" r:id="rId206" tooltip="Abrir" xr:uid="{CE36C685-7886-456A-9D1D-AB9C224DDDF1}"/>
+    <hyperlink ref="C192" r:id="rId207" tooltip="Abrir" xr:uid="{95B49670-CA06-45AA-B6CB-410D27CAFA78}"/>
+    <hyperlink ref="C193" r:id="rId208" tooltip="Abrir" xr:uid="{8E386F02-FAB0-44DB-A404-E3E249B213F9}"/>
+    <hyperlink ref="C194" r:id="rId209" tooltip="Abrir" xr:uid="{18BAEA36-2298-43E9-8AF0-B98E6218E595}"/>
+    <hyperlink ref="E195" r:id="rId210" tooltip="Abrir" xr:uid="{9C520AB7-DECA-45FA-B953-CB273F6AE70D}"/>
+    <hyperlink ref="E196" r:id="rId211" tooltip="Abrir" xr:uid="{3B1D6AAB-066A-4F35-8702-79D47D6D97A3}"/>
+    <hyperlink ref="E197" r:id="rId212" tooltip="Abrir" xr:uid="{51CFA209-2783-49A5-8C48-C5013E15B5E5}"/>
+    <hyperlink ref="E198" r:id="rId213" tooltip="Abrir" xr:uid="{7845589F-722C-4BC7-941D-F0EC7D14C9BE}"/>
+    <hyperlink ref="E199" r:id="rId214" tooltip="Abrir" xr:uid="{0F217C98-C7F0-4A65-9C86-C3379C49F88D}"/>
+    <hyperlink ref="E200" r:id="rId215" tooltip="Abrir" xr:uid="{0288B9CA-678C-4E2A-89E5-48BEB08A5573}"/>
+    <hyperlink ref="C201" r:id="rId216" tooltip="Abrir" xr:uid="{4304E043-CE45-4670-8AA2-E7F458C0937C}"/>
+    <hyperlink ref="C202" r:id="rId217" tooltip="Abrir" xr:uid="{8884D644-0D62-4DE5-BAB4-F75CBDF6EA38}"/>
+    <hyperlink ref="C203" r:id="rId218" tooltip="Abrir" xr:uid="{41778206-63D7-44A1-8156-73647B081783}"/>
+    <hyperlink ref="E203" r:id="rId219" tooltip="Abrir" xr:uid="{EB36D268-A3ED-4447-ACB2-B0EA775634BB}"/>
+    <hyperlink ref="C204" r:id="rId220" tooltip="Abrir" xr:uid="{FA9F8E86-9D15-4596-845E-BB9B7FF84EFC}"/>
+    <hyperlink ref="E205" r:id="rId221" tooltip="Abrir" xr:uid="{85FD8994-9647-40FA-8A35-646094C1FF89}"/>
+    <hyperlink ref="C206" r:id="rId222" tooltip="Abrir" xr:uid="{514C4223-40FE-4E2B-8DDC-641657A78AAA}"/>
+    <hyperlink ref="E207" r:id="rId223" tooltip="Abrir" xr:uid="{D83CAE82-66C6-406B-B8B2-1DEAF7548EE0}"/>
+    <hyperlink ref="E208" r:id="rId224" tooltip="Abrir" xr:uid="{4F90ED52-0085-4C84-81EF-650F7BF954D1}"/>
+    <hyperlink ref="C209" r:id="rId225" tooltip="Abrir" xr:uid="{B3AA3C60-DDBB-46E7-9E39-F165081843F1}"/>
+    <hyperlink ref="E209" r:id="rId226" tooltip="Abrir" xr:uid="{CBB70B8B-E935-4CB7-AC0E-30B75F96E748}"/>
+    <hyperlink ref="C210" r:id="rId227" tooltip="Abrir" xr:uid="{744B9BA7-9AD1-469B-9B43-24DF3DD485BA}"/>
+    <hyperlink ref="E211" r:id="rId228" tooltip="Abrir" xr:uid="{F52AE4A0-BF24-4A3A-9DEF-FD65DB5B9ABA}"/>
+    <hyperlink ref="C212" r:id="rId229" tooltip="Abrir" xr:uid="{8CE60A9E-9DC5-46AB-9A09-BD278B0227E2}"/>
+    <hyperlink ref="C213" r:id="rId230" tooltip="Abrir" xr:uid="{EB86D5A0-53A9-4685-A17D-2BC9E963A522}"/>
+    <hyperlink ref="C214" r:id="rId231" tooltip="Abrir" xr:uid="{74FD6DC3-9BFB-431B-9235-13766222883F}"/>
+    <hyperlink ref="E214" r:id="rId232" tooltip="Abrir" xr:uid="{1619E39F-52E9-49F4-99AE-FD845330A5C6}"/>
+    <hyperlink ref="E215" r:id="rId233" tooltip="Abrir" xr:uid="{496FAEC0-23B1-47FD-9B64-E0F5B861B779}"/>
+    <hyperlink ref="E216" r:id="rId234" tooltip="Abrir" xr:uid="{57AF79FB-CC2F-4CED-9457-F3B15D1BC27C}"/>
+    <hyperlink ref="C217" r:id="rId235" tooltip="Abrir" xr:uid="{B465D877-9F15-4ABF-9DD5-0DD5E840412D}"/>
+    <hyperlink ref="C218" r:id="rId236" tooltip="Abrir" xr:uid="{20DF7074-8AF7-41CE-8AF3-8AEFE981EB12}"/>
+    <hyperlink ref="E219" r:id="rId237" tooltip="Abrir" xr:uid="{7DE7098A-08F0-433B-9DEB-CEDBD7C02C34}"/>
+    <hyperlink ref="C220" r:id="rId238" tooltip="Abrir" xr:uid="{5D03D54F-6385-4BBA-96C9-64B326F6F4A0}"/>
+    <hyperlink ref="E221" r:id="rId239" tooltip="Abrir" xr:uid="{A00BB373-6D1F-4649-B29F-9B6EA78AE8D6}"/>
+    <hyperlink ref="E222" r:id="rId240" tooltip="Abrir" xr:uid="{469FD974-0C06-4E62-BE92-92782D3ED953}"/>
+    <hyperlink ref="C223" r:id="rId241" tooltip="Abrir" xr:uid="{AE7CA50A-AA52-4574-B61D-1BE0A1111C75}"/>
+    <hyperlink ref="E224" r:id="rId242" tooltip="Abrir" xr:uid="{EB3EF163-2F63-4FE3-8BD5-910AE3730B19}"/>
+    <hyperlink ref="C225" r:id="rId243" tooltip="Abrir" xr:uid="{A1BE8D20-71DC-423E-AE4F-89FFCEDF6AC3}"/>
+    <hyperlink ref="E226" r:id="rId244" tooltip="Abrir" xr:uid="{FCC87514-0F3E-43B3-9DD3-A63E268F7986}"/>
+    <hyperlink ref="E227" r:id="rId245" tooltip="Abrir" xr:uid="{F22E346D-948A-4AF9-AF83-B5C85873ADE4}"/>
+    <hyperlink ref="E228" r:id="rId246" tooltip="Abrir" xr:uid="{F663E2C4-2A0C-4BF7-9FAC-2E32FD28E0B5}"/>
+    <hyperlink ref="E229" r:id="rId247" tooltip="Abrir" xr:uid="{027AECCA-D94B-41AD-8545-F495B820AFD6}"/>
+    <hyperlink ref="E230" r:id="rId248" tooltip="Abrir" xr:uid="{B0A1B480-439F-404A-9D6E-9C2E00D328A4}"/>
+    <hyperlink ref="C231" r:id="rId249" tooltip="Abrir" xr:uid="{3925B726-8FF0-4E1B-8940-B436E55E0D78}"/>
+    <hyperlink ref="E232" r:id="rId250" tooltip="Abrir" xr:uid="{F48EEC03-2C34-4C9D-99C8-564691967424}"/>
+    <hyperlink ref="C233" r:id="rId251" tooltip="Abrir" xr:uid="{0FE748A9-A081-4CAB-935B-28B9DF356DB9}"/>
+    <hyperlink ref="E233" r:id="rId252" tooltip="Abrir" xr:uid="{6EDA2BCC-CD98-4918-AAED-6B2AA53FD96E}"/>
+    <hyperlink ref="E234" r:id="rId253" tooltip="Abrir" xr:uid="{D63E2270-4F98-4DD0-B448-1478BB4CDB98}"/>
+    <hyperlink ref="C235" r:id="rId254" tooltip="Abrir" xr:uid="{0E3BE346-B031-4F7E-B3C5-79133324E0D5}"/>
+    <hyperlink ref="C236" r:id="rId255" tooltip="Abrir" xr:uid="{6936AC63-9B0B-4963-99A1-6908C5C97DD6}"/>
+    <hyperlink ref="E237" r:id="rId256" tooltip="Abrir" xr:uid="{80F7354D-C118-41E3-B1CA-85BF5DF0DD19}"/>
+    <hyperlink ref="E238" r:id="rId257" tooltip="Abrir" xr:uid="{3C50AB49-5729-47DE-AA82-E00F36BB9E35}"/>
+    <hyperlink ref="C239" r:id="rId258" tooltip="Abrir" xr:uid="{C460DECF-CEF1-4637-81C6-7ED27103BCB3}"/>
+    <hyperlink ref="E240" r:id="rId259" tooltip="Abrir" xr:uid="{178C9787-BDD0-4635-8786-613AD94676C6}"/>
+    <hyperlink ref="C241" r:id="rId260" tooltip="Abrir" xr:uid="{8A547AF3-0126-4F8F-8174-773736D2D6DC}"/>
+    <hyperlink ref="C242" r:id="rId261" tooltip="Abrir" xr:uid="{2A4B5417-CCCD-47FC-8598-EB7B6EE452B6}"/>
+    <hyperlink ref="E242" r:id="rId262" tooltip="Abrir" xr:uid="{C3A3EA23-E524-4628-979B-2798162AE408}"/>
+    <hyperlink ref="E243" r:id="rId263" tooltip="Abrir" xr:uid="{4EF6B189-1C5C-47AC-B528-E859E8EEFDDC}"/>
+    <hyperlink ref="C244" r:id="rId264" tooltip="Abrir" xr:uid="{3F906219-AC72-4CAE-886A-A58EB04A1A3B}"/>
+    <hyperlink ref="C245" r:id="rId265" tooltip="Abrir" xr:uid="{2FD54B94-DB50-460A-8ED0-711A80ED3BA9}"/>
+    <hyperlink ref="E246" r:id="rId266" tooltip="Abrir" xr:uid="{33B0294F-BF6B-4823-B362-B4B146AD80E7}"/>
+    <hyperlink ref="C247" r:id="rId267" tooltip="Abrir" xr:uid="{208F28FB-0351-40E9-81CD-6BC52D1D5ABF}"/>
+    <hyperlink ref="E248" r:id="rId268" tooltip="Abrir" xr:uid="{2051DAFC-552C-4159-B8E8-8E6A347F00F6}"/>
+    <hyperlink ref="C249" r:id="rId269" tooltip="Abrir" xr:uid="{B34D7019-D98E-4D75-98AE-7F0202AB1B7F}"/>
+    <hyperlink ref="C250" r:id="rId270" tooltip="Abrir" xr:uid="{542978D3-F0B0-412B-8C80-F57A9E043573}"/>
+    <hyperlink ref="E251" r:id="rId271" tooltip="Abrir" xr:uid="{DCBE4781-3838-4CB2-A1DA-BBDBED622787}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDCBC571-1C57-412E-99B9-B39F0A053C51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1ECDF95-05EE-4AA2-A317-B2DBCB7BDA2D}">
   <dimension ref="A1:C300"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8090,7 +8117,7 @@
         <v>417</v>
       </c>
       <c r="B2">
-        <v>980</v>
+        <v>997</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -8101,7 +8128,7 @@
         <v>418</v>
       </c>
       <c r="B3">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -8123,7 +8150,7 @@
         <v>420</v>
       </c>
       <c r="B5">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>20</v>
@@ -8134,7 +8161,7 @@
         <v>421</v>
       </c>
       <c r="B6">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -8145,7 +8172,7 @@
         <v>422</v>
       </c>
       <c r="B7">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
@@ -8156,7 +8183,7 @@
         <v>423</v>
       </c>
       <c r="B8">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -8167,7 +8194,7 @@
         <v>424</v>
       </c>
       <c r="B9">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -8189,7 +8216,7 @@
         <v>426</v>
       </c>
       <c r="B11">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>20</v>
@@ -8255,7 +8282,7 @@
         <v>432</v>
       </c>
       <c r="B17">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>20</v>
@@ -8277,7 +8304,7 @@
         <v>434</v>
       </c>
       <c r="B19">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
@@ -8288,7 +8315,7 @@
         <v>435</v>
       </c>
       <c r="B20">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>20</v>
@@ -8376,7 +8403,7 @@
         <v>443</v>
       </c>
       <c r="B28">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>20</v>
@@ -8387,7 +8414,7 @@
         <v>444</v>
       </c>
       <c r="B29">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>20</v>
@@ -8420,7 +8447,7 @@
         <v>447</v>
       </c>
       <c r="B32">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>20</v>
@@ -8453,7 +8480,7 @@
         <v>450</v>
       </c>
       <c r="B35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>20</v>
@@ -8475,7 +8502,7 @@
         <v>452</v>
       </c>
       <c r="B37">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>20</v>
@@ -8497,7 +8524,7 @@
         <v>454</v>
       </c>
       <c r="B39">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
@@ -8527,7 +8554,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B42">
         <v>31</v>
@@ -8541,7 +8568,7 @@
         <v>457</v>
       </c>
       <c r="B43">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>20</v>
@@ -8552,7 +8579,7 @@
         <v>458</v>
       </c>
       <c r="B44">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>20</v>
@@ -8574,7 +8601,7 @@
         <v>460</v>
       </c>
       <c r="B46">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>20</v>
@@ -8607,7 +8634,7 @@
         <v>463</v>
       </c>
       <c r="B49">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>20</v>
@@ -8651,7 +8678,7 @@
         <v>467</v>
       </c>
       <c r="B53">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>20</v>
@@ -8739,7 +8766,7 @@
         <v>475</v>
       </c>
       <c r="B61">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>20</v>
@@ -8948,7 +8975,7 @@
         <v>494</v>
       </c>
       <c r="B80">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>20</v>
@@ -9025,7 +9052,7 @@
         <v>501</v>
       </c>
       <c r="B87">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>20</v>
@@ -9102,7 +9129,7 @@
         <v>508</v>
       </c>
       <c r="B94">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>20</v>
@@ -9168,7 +9195,7 @@
         <v>514</v>
       </c>
       <c r="B100">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>20</v>
@@ -9179,7 +9206,7 @@
         <v>515</v>
       </c>
       <c r="B101">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>20</v>
@@ -9190,7 +9217,7 @@
         <v>516</v>
       </c>
       <c r="B102">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>20</v>
@@ -9212,7 +9239,7 @@
         <v>518</v>
       </c>
       <c r="B104">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>20</v>
@@ -9223,7 +9250,7 @@
         <v>519</v>
       </c>
       <c r="B105">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>20</v>
@@ -9300,7 +9327,7 @@
         <v>526</v>
       </c>
       <c r="B112">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>20</v>
@@ -9366,7 +9393,7 @@
         <v>532</v>
       </c>
       <c r="B118">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>20</v>
@@ -9377,7 +9404,7 @@
         <v>533</v>
       </c>
       <c r="B119">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>20</v>
@@ -9443,7 +9470,7 @@
         <v>539</v>
       </c>
       <c r="B125">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>20</v>
@@ -9619,7 +9646,7 @@
         <v>555</v>
       </c>
       <c r="B141">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>20</v>
@@ -9839,7 +9866,7 @@
         <v>575</v>
       </c>
       <c r="B161">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>20</v>
@@ -9880,7 +9907,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B165">
         <v>7</v>
@@ -9891,7 +9918,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B166">
         <v>7</v>
@@ -10034,7 +10061,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>449</v>
+        <v>592</v>
       </c>
       <c r="B179">
         <v>7</v>
@@ -10045,7 +10072,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>592</v>
+        <v>450</v>
       </c>
       <c r="B180">
         <v>7</v>
@@ -10103,7 +10130,7 @@
         <v>597</v>
       </c>
       <c r="B185">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>20</v>
@@ -10114,7 +10141,7 @@
         <v>598</v>
       </c>
       <c r="B186">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>20</v>
@@ -11082,7 +11109,7 @@
         <v>685</v>
       </c>
       <c r="B274">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>20</v>
@@ -11222,7 +11249,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -11375,307 +11402,307 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C300" xr:uid="{DDCBC571-1C57-412E-99B9-B39F0A053C51}"/>
+  <autoFilter ref="A1:C300" xr:uid="{E1ECDF95-05EE-4AA2-A317-B2DBCB7BDA2D}"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="Abrir" xr:uid="{66334098-DF34-46DD-B9B0-DAB67C2086EB}"/>
-    <hyperlink ref="C3" r:id="rId2" tooltip="Abrir" xr:uid="{441931B4-8131-4F94-AD11-0E90875B878E}"/>
-    <hyperlink ref="C4" r:id="rId3" tooltip="Abrir" xr:uid="{9EF6EACB-0FC6-4634-A2A7-6D9E695EAC7E}"/>
-    <hyperlink ref="C5" r:id="rId4" tooltip="Abrir" xr:uid="{265B1722-2DE6-482F-ACF6-5A4A41B82AFA}"/>
-    <hyperlink ref="C6" r:id="rId5" tooltip="Abrir" xr:uid="{ABB30D06-AC71-483A-A23D-5441543C0E77}"/>
-    <hyperlink ref="C7" r:id="rId6" tooltip="Abrir" xr:uid="{8F88EC95-9D03-4772-90A8-66742AA7C66E}"/>
-    <hyperlink ref="C8" r:id="rId7" tooltip="Abrir" xr:uid="{6735D6CB-0E0B-4534-AF1A-0A500C5B2168}"/>
-    <hyperlink ref="C9" r:id="rId8" tooltip="Abrir" xr:uid="{8A60B893-5B79-47EB-88DF-BD89C16B0B07}"/>
-    <hyperlink ref="C10" r:id="rId9" tooltip="Abrir" xr:uid="{4E607138-BFC7-4508-A961-7E6C1E05597F}"/>
-    <hyperlink ref="C11" r:id="rId10" tooltip="Abrir" xr:uid="{12CE2D65-B424-478C-9FDF-0E56B55B8367}"/>
-    <hyperlink ref="C12" r:id="rId11" tooltip="Abrir" xr:uid="{5DF7835F-B3FC-4F0E-A23B-605F4B0A678C}"/>
-    <hyperlink ref="C13" r:id="rId12" tooltip="Abrir" xr:uid="{D09032F0-5617-4768-A92E-1E2A7E689B93}"/>
-    <hyperlink ref="C14" r:id="rId13" tooltip="Abrir" xr:uid="{2DB58624-91B1-45EB-BAD7-EF799DF8F3D2}"/>
-    <hyperlink ref="C15" r:id="rId14" tooltip="Abrir" xr:uid="{388ADE87-E954-4C63-91ED-3462F441485E}"/>
-    <hyperlink ref="C16" r:id="rId15" tooltip="Abrir" xr:uid="{204041A3-5C5D-4206-ACAB-C3655D81ACFA}"/>
-    <hyperlink ref="C17" r:id="rId16" tooltip="Abrir" xr:uid="{D821BA36-529B-4406-AB3D-551844E98368}"/>
-    <hyperlink ref="C18" r:id="rId17" tooltip="Abrir" xr:uid="{AA3551CE-BEA5-4DA1-9520-774AED6B5807}"/>
-    <hyperlink ref="C19" r:id="rId18" tooltip="Abrir" xr:uid="{6CA6B9D1-3BCD-46B3-8510-B719EA389C6F}"/>
-    <hyperlink ref="C20" r:id="rId19" tooltip="Abrir" xr:uid="{E5A3AEA4-E685-4C6B-B9ED-59260878AF5A}"/>
-    <hyperlink ref="C21" r:id="rId20" tooltip="Abrir" xr:uid="{6B4A56C2-339B-420A-BEF0-4A717942B14F}"/>
-    <hyperlink ref="C22" r:id="rId21" tooltip="Abrir" xr:uid="{3F53943B-FE0D-4522-A9E7-BBC399A025EF}"/>
-    <hyperlink ref="C23" r:id="rId22" tooltip="Abrir" xr:uid="{6F1ABAB0-879D-4901-97F3-9C3FC504EB68}"/>
-    <hyperlink ref="C24" r:id="rId23" tooltip="Abrir" xr:uid="{B9B8B82B-DB34-4797-82E5-E7D211B8F9BA}"/>
-    <hyperlink ref="C25" r:id="rId24" tooltip="Abrir" xr:uid="{47267E5C-D85C-4672-A394-A4109D74891A}"/>
-    <hyperlink ref="C26" r:id="rId25" tooltip="Abrir" xr:uid="{71FEE918-FF3C-40AE-BAC5-AA5871F6483C}"/>
-    <hyperlink ref="C27" r:id="rId26" tooltip="Abrir" xr:uid="{03488EC9-0B14-4605-9961-4A4ABFD60E90}"/>
-    <hyperlink ref="C28" r:id="rId27" tooltip="Abrir" xr:uid="{47F4D590-E286-4961-91DA-B39753E29A30}"/>
-    <hyperlink ref="C29" r:id="rId28" tooltip="Abrir" xr:uid="{7831FA3C-EC3A-4539-A5C6-E260C472608E}"/>
-    <hyperlink ref="C30" r:id="rId29" tooltip="Abrir" xr:uid="{2CCD8B43-3C7D-4B32-BC71-64DEDF8DC58D}"/>
-    <hyperlink ref="C31" r:id="rId30" tooltip="Abrir" xr:uid="{F8C5128E-3012-4796-BD26-EAF2251A0279}"/>
-    <hyperlink ref="C32" r:id="rId31" tooltip="Abrir" xr:uid="{5A91386A-9D0B-40ED-9C54-2283A02C05B8}"/>
-    <hyperlink ref="C33" r:id="rId32" tooltip="Abrir" xr:uid="{9CEB05A4-42CE-4C33-BEF9-81DA0AB73601}"/>
-    <hyperlink ref="C34" r:id="rId33" tooltip="Abrir" xr:uid="{3EC4F09E-9903-4248-8BC5-A4B9DF416BF1}"/>
-    <hyperlink ref="C35" r:id="rId34" tooltip="Abrir" xr:uid="{FD196035-70E9-4730-BFAD-83C8E7DAF965}"/>
-    <hyperlink ref="C36" r:id="rId35" tooltip="Abrir" xr:uid="{E448E347-3011-46D1-B02B-BF7B72FF6B0B}"/>
-    <hyperlink ref="C37" r:id="rId36" tooltip="Abrir" xr:uid="{E70E9BF5-B514-4F01-9766-7AC18C8D677A}"/>
-    <hyperlink ref="C38" r:id="rId37" tooltip="Abrir" xr:uid="{212F5A68-5D2F-44FF-A800-D1FE3C36D366}"/>
-    <hyperlink ref="C39" r:id="rId38" tooltip="Abrir" xr:uid="{B12CE5D9-99E4-453D-B40E-92D93D7A8FFC}"/>
-    <hyperlink ref="C40" r:id="rId39" tooltip="Abrir" xr:uid="{A610676A-C11D-43DE-B48B-AAC074685D60}"/>
-    <hyperlink ref="C41" r:id="rId40" tooltip="Abrir" xr:uid="{ED0CF112-BF3A-49D4-B696-0FDE2ACE4639}"/>
-    <hyperlink ref="C42" r:id="rId41" tooltip="Abrir" xr:uid="{8AE9F84A-89AF-4ECA-A878-718BD2881DA4}"/>
-    <hyperlink ref="C43" r:id="rId42" tooltip="Abrir" xr:uid="{3A4FE6AA-328F-475A-BB7C-0D14D0C836A3}"/>
-    <hyperlink ref="C44" r:id="rId43" tooltip="Abrir" xr:uid="{B593EAE8-D112-4F2D-84D6-059D93FCD5C4}"/>
-    <hyperlink ref="C45" r:id="rId44" tooltip="Abrir" xr:uid="{D10E8BEF-3607-41F8-BB07-2782C35E9888}"/>
-    <hyperlink ref="C46" r:id="rId45" tooltip="Abrir" xr:uid="{3D890D8F-BD9F-44BD-BE3F-B10CF68DFC60}"/>
-    <hyperlink ref="C47" r:id="rId46" tooltip="Abrir" xr:uid="{393E0D0A-C15E-4A0D-ADBE-444F9D4BA16E}"/>
-    <hyperlink ref="C48" r:id="rId47" tooltip="Abrir" xr:uid="{27BDD2C0-D9CE-43E6-BC26-B5B51738160C}"/>
-    <hyperlink ref="C49" r:id="rId48" tooltip="Abrir" xr:uid="{C59EF03D-1EF0-43B1-8D3D-8F8E4F87E7F8}"/>
-    <hyperlink ref="C50" r:id="rId49" tooltip="Abrir" xr:uid="{433FE84C-89B1-4C9E-A9CF-89B5D8A1B851}"/>
-    <hyperlink ref="C51" r:id="rId50" tooltip="Abrir" xr:uid="{DDE37DB1-F79E-46F3-9612-EE380D540829}"/>
-    <hyperlink ref="C52" r:id="rId51" tooltip="Abrir" xr:uid="{F696B4EE-9E16-4035-B71D-7AD5EAA243DF}"/>
-    <hyperlink ref="C53" r:id="rId52" tooltip="Abrir" xr:uid="{A1B8F328-4E48-4EF7-98B6-A47E0BB5F22C}"/>
-    <hyperlink ref="C54" r:id="rId53" tooltip="Abrir" xr:uid="{11F3AEA9-C757-4649-9976-2169345E64A3}"/>
-    <hyperlink ref="C55" r:id="rId54" tooltip="Abrir" xr:uid="{6F20ED46-AB35-435C-A9A2-D289969C20BE}"/>
-    <hyperlink ref="C56" r:id="rId55" tooltip="Abrir" xr:uid="{831A04E0-795E-4DBA-A361-6E296E8C11F1}"/>
-    <hyperlink ref="C57" r:id="rId56" tooltip="Abrir" xr:uid="{2B4F6AC6-AE4F-4199-9B5C-5F8B3823B5FF}"/>
-    <hyperlink ref="C58" r:id="rId57" tooltip="Abrir" xr:uid="{78EC10BF-C56F-407A-A325-525EBFA63D46}"/>
-    <hyperlink ref="C59" r:id="rId58" tooltip="Abrir" xr:uid="{42ED598D-A1C5-4C7C-853B-80A0251C5340}"/>
-    <hyperlink ref="C60" r:id="rId59" tooltip="Abrir" xr:uid="{1599E776-05BC-4A3E-89F1-19C0A8DECB39}"/>
-    <hyperlink ref="C61" r:id="rId60" tooltip="Abrir" xr:uid="{5074951F-A76F-4088-9938-9903CBD8820F}"/>
-    <hyperlink ref="C62" r:id="rId61" tooltip="Abrir" xr:uid="{0852B0A1-FC1A-4DE6-9B5D-1DE0631C540D}"/>
-    <hyperlink ref="C63" r:id="rId62" tooltip="Abrir" xr:uid="{6756FA72-4193-47A3-83A8-ED98D368D9CF}"/>
-    <hyperlink ref="C64" r:id="rId63" tooltip="Abrir" xr:uid="{BFD42CBF-5953-491E-ABDE-4237D110E45D}"/>
-    <hyperlink ref="C65" r:id="rId64" tooltip="Abrir" xr:uid="{110CA279-343F-4ABD-9325-0AA185D54E90}"/>
-    <hyperlink ref="C66" r:id="rId65" tooltip="Abrir" xr:uid="{3BCB6AC1-21D3-4730-9599-D9F6237F68DF}"/>
-    <hyperlink ref="C67" r:id="rId66" tooltip="Abrir" xr:uid="{A6FA8032-067B-48F5-9DDC-636B62311764}"/>
-    <hyperlink ref="C68" r:id="rId67" tooltip="Abrir" xr:uid="{EFD58ABC-3BB7-4298-96F4-8F40E1D92854}"/>
-    <hyperlink ref="C69" r:id="rId68" tooltip="Abrir" xr:uid="{AC86AC30-FF9C-4918-98E1-0638417AF046}"/>
-    <hyperlink ref="C70" r:id="rId69" tooltip="Abrir" xr:uid="{CC5A3360-7BB4-4AB7-924A-2C8C60D5AAF6}"/>
-    <hyperlink ref="C71" r:id="rId70" tooltip="Abrir" xr:uid="{B9472AD1-2953-48DD-98C2-960BA12E4377}"/>
-    <hyperlink ref="C72" r:id="rId71" tooltip="Abrir" xr:uid="{E04908A3-6AA2-4197-8F2F-E5B145415589}"/>
-    <hyperlink ref="C73" r:id="rId72" tooltip="Abrir" xr:uid="{02009979-B81B-4A69-ADC5-4BB0042C41F3}"/>
-    <hyperlink ref="C74" r:id="rId73" tooltip="Abrir" xr:uid="{E10CF059-9AF6-4DF2-A086-3B1BA14F8D7C}"/>
-    <hyperlink ref="C75" r:id="rId74" tooltip="Abrir" xr:uid="{9F9328FE-B03F-440D-8AF5-5DB3B43FDA55}"/>
-    <hyperlink ref="C76" r:id="rId75" tooltip="Abrir" xr:uid="{FBDED079-BE08-4CD6-A4FE-0B0563FF4125}"/>
-    <hyperlink ref="C77" r:id="rId76" tooltip="Abrir" xr:uid="{030355B0-5619-4716-9E6E-0F40B54D29CA}"/>
-    <hyperlink ref="C78" r:id="rId77" tooltip="Abrir" xr:uid="{EB728981-E769-4CFA-ABDB-8E3682E966AF}"/>
-    <hyperlink ref="C79" r:id="rId78" tooltip="Abrir" xr:uid="{A7068357-E243-43D4-9783-8B5CF6F55AA1}"/>
-    <hyperlink ref="C80" r:id="rId79" tooltip="Abrir" xr:uid="{20D7137E-7910-4CFF-83A9-67FCF61CA175}"/>
-    <hyperlink ref="C81" r:id="rId80" tooltip="Abrir" xr:uid="{BBB68157-6304-4C0B-AF06-B31627F14598}"/>
-    <hyperlink ref="C82" r:id="rId81" tooltip="Abrir" xr:uid="{293E7306-5B8E-4CB6-BF6C-6202D83D6C70}"/>
-    <hyperlink ref="C83" r:id="rId82" tooltip="Abrir" xr:uid="{0AC6C22B-562D-491E-8D2A-80E734D7661A}"/>
-    <hyperlink ref="C84" r:id="rId83" tooltip="Abrir" xr:uid="{4B18CB60-CFD4-47D1-B525-7B7507C84128}"/>
-    <hyperlink ref="C85" r:id="rId84" tooltip="Abrir" xr:uid="{145870C0-20EC-4B0D-B4DE-57D4D2017670}"/>
-    <hyperlink ref="C86" r:id="rId85" tooltip="Abrir" xr:uid="{9A79B4CD-92E6-454D-BD78-070686C9F6F3}"/>
-    <hyperlink ref="C87" r:id="rId86" tooltip="Abrir" xr:uid="{3FA5D3DD-09F0-484C-9A1A-F233253E910C}"/>
-    <hyperlink ref="C88" r:id="rId87" tooltip="Abrir" xr:uid="{BB031486-08E8-4280-B4A0-A08E3C248B59}"/>
-    <hyperlink ref="C89" r:id="rId88" tooltip="Abrir" xr:uid="{2F24513C-3BD6-4CEE-8401-AF86A357DD85}"/>
-    <hyperlink ref="C90" r:id="rId89" tooltip="Abrir" xr:uid="{0759A854-E1C7-4B8B-B6B4-CAC2EDC70107}"/>
-    <hyperlink ref="C91" r:id="rId90" tooltip="Abrir" xr:uid="{0CF67A57-5514-4EF0-93A5-81EB65850B5C}"/>
-    <hyperlink ref="C92" r:id="rId91" tooltip="Abrir" xr:uid="{7B5C5531-942A-4A50-AFB7-B803A39BB9F4}"/>
-    <hyperlink ref="C93" r:id="rId92" tooltip="Abrir" xr:uid="{00E26E4C-5FBD-47DD-8BA9-35198741D526}"/>
-    <hyperlink ref="C94" r:id="rId93" tooltip="Abrir" xr:uid="{4E5672AF-F4AC-4CFC-BDF4-AAB455DAFFD2}"/>
-    <hyperlink ref="C95" r:id="rId94" tooltip="Abrir" xr:uid="{355CB307-9D5E-47EB-85BF-0427699308EA}"/>
-    <hyperlink ref="C96" r:id="rId95" tooltip="Abrir" xr:uid="{57E7A940-85EF-406A-BF71-FBAF59778790}"/>
-    <hyperlink ref="C97" r:id="rId96" tooltip="Abrir" xr:uid="{B24685D5-1999-403A-A574-9AEE30B9EC35}"/>
-    <hyperlink ref="C98" r:id="rId97" tooltip="Abrir" xr:uid="{34EBCF37-7790-4176-BB2C-454272CC342F}"/>
-    <hyperlink ref="C99" r:id="rId98" tooltip="Abrir" xr:uid="{911B3437-D70B-46B0-9A32-A8C00A13327A}"/>
-    <hyperlink ref="C100" r:id="rId99" tooltip="Abrir" xr:uid="{7B586B93-FB64-4718-AC74-C9806BEB6938}"/>
-    <hyperlink ref="C101" r:id="rId100" tooltip="Abrir" xr:uid="{2ABE47BD-409E-4E7C-B4B2-DAB8BCA3F0BA}"/>
-    <hyperlink ref="C102" r:id="rId101" tooltip="Abrir" xr:uid="{14916054-63B4-4DAE-83E7-BAF2D06781E8}"/>
-    <hyperlink ref="C103" r:id="rId102" tooltip="Abrir" xr:uid="{5FD7D363-D965-4341-ADC7-D4DB9B4A7418}"/>
-    <hyperlink ref="C104" r:id="rId103" tooltip="Abrir" xr:uid="{DDA523E9-6E0D-4BAE-AD53-667A78C42A21}"/>
-    <hyperlink ref="C105" r:id="rId104" tooltip="Abrir" xr:uid="{C792C789-FBD3-4F83-B756-BBC28650192A}"/>
-    <hyperlink ref="C106" r:id="rId105" tooltip="Abrir" xr:uid="{34E16FD4-AB85-47E3-96C9-2958EF31EACA}"/>
-    <hyperlink ref="C107" r:id="rId106" tooltip="Abrir" xr:uid="{EEBEDE9F-703F-4E39-B180-5F8DE6C3F7C6}"/>
-    <hyperlink ref="C108" r:id="rId107" tooltip="Abrir" xr:uid="{5489D38F-14AD-4D65-A434-52C8CCE17FE2}"/>
-    <hyperlink ref="C109" r:id="rId108" tooltip="Abrir" xr:uid="{B05A84AD-A204-4707-AB8C-ADBAFDEBDD9C}"/>
-    <hyperlink ref="C110" r:id="rId109" tooltip="Abrir" xr:uid="{5838383A-88C0-439E-8EEF-0977FB5D5C05}"/>
-    <hyperlink ref="C111" r:id="rId110" tooltip="Abrir" xr:uid="{64930FE6-8145-42A1-94D4-D56D74F37F3E}"/>
-    <hyperlink ref="C112" r:id="rId111" tooltip="Abrir" xr:uid="{CB34716C-0F61-4A1C-9443-42AEAD1ED981}"/>
-    <hyperlink ref="C113" r:id="rId112" tooltip="Abrir" xr:uid="{0004E918-A6FD-48EB-A403-2253C228AA26}"/>
-    <hyperlink ref="C114" r:id="rId113" tooltip="Abrir" xr:uid="{F32BC983-7AA9-4EEE-88A5-2741C19C0813}"/>
-    <hyperlink ref="C115" r:id="rId114" tooltip="Abrir" xr:uid="{70FF6A06-9EC8-447A-9CFE-DF66583FEE75}"/>
-    <hyperlink ref="C116" r:id="rId115" tooltip="Abrir" xr:uid="{7CCA5735-453F-434E-B747-3E87E8B2A852}"/>
-    <hyperlink ref="C117" r:id="rId116" tooltip="Abrir" xr:uid="{4E41A600-7A53-44F3-86C0-482C8F7CA18F}"/>
-    <hyperlink ref="C118" r:id="rId117" tooltip="Abrir" xr:uid="{F1F087AF-075C-400A-9FBC-250622FA045B}"/>
-    <hyperlink ref="C119" r:id="rId118" tooltip="Abrir" xr:uid="{12CB189B-616C-49D5-9964-2352F4DAB35B}"/>
-    <hyperlink ref="C120" r:id="rId119" tooltip="Abrir" xr:uid="{42BDDAF3-92FD-46B3-9B0D-4EE17A1B9EE9}"/>
-    <hyperlink ref="C121" r:id="rId120" tooltip="Abrir" xr:uid="{1321F373-4C56-4239-B3D4-B2D4BA28E5F4}"/>
-    <hyperlink ref="C122" r:id="rId121" tooltip="Abrir" xr:uid="{344EC753-76D9-4DA7-A02C-7502AFFE8F76}"/>
-    <hyperlink ref="C123" r:id="rId122" tooltip="Abrir" xr:uid="{DE41E8BA-F542-4EB9-9D41-ACCD5971DD70}"/>
-    <hyperlink ref="C124" r:id="rId123" tooltip="Abrir" xr:uid="{1537E508-BE71-41C5-9AFF-CFEF6B798E32}"/>
-    <hyperlink ref="C125" r:id="rId124" tooltip="Abrir" xr:uid="{9BE12E8A-5B36-495F-8CDF-0CA99280683A}"/>
-    <hyperlink ref="C126" r:id="rId125" tooltip="Abrir" xr:uid="{5828854A-64F5-425B-B3EC-E42BB67AD807}"/>
-    <hyperlink ref="C127" r:id="rId126" tooltip="Abrir" xr:uid="{9F30F847-57C7-44ED-86C5-2515DD640100}"/>
-    <hyperlink ref="C128" r:id="rId127" tooltip="Abrir" xr:uid="{360A9B35-3AF6-4DDE-A5B2-941F99919977}"/>
-    <hyperlink ref="C129" r:id="rId128" tooltip="Abrir" xr:uid="{0BB393A2-AD80-49AF-A3F0-E87CB03B85DF}"/>
-    <hyperlink ref="C130" r:id="rId129" tooltip="Abrir" xr:uid="{3F09C8FE-FC55-4785-8468-B9A24FC55CF6}"/>
-    <hyperlink ref="C131" r:id="rId130" tooltip="Abrir" xr:uid="{28E20BAC-9E27-42E6-BF1E-43DAC8466E9B}"/>
-    <hyperlink ref="C132" r:id="rId131" tooltip="Abrir" xr:uid="{B85DD7A9-4E5D-42FF-8D15-0016BF537165}"/>
-    <hyperlink ref="C133" r:id="rId132" tooltip="Abrir" xr:uid="{F3BCC699-6387-4ABC-9242-28FFD5153F77}"/>
-    <hyperlink ref="C134" r:id="rId133" tooltip="Abrir" xr:uid="{FE51F210-1320-48D1-8952-FA807E6706E2}"/>
-    <hyperlink ref="C135" r:id="rId134" tooltip="Abrir" xr:uid="{F388D4FB-5018-4339-A97B-076A54A01C1B}"/>
-    <hyperlink ref="C136" r:id="rId135" tooltip="Abrir" xr:uid="{221EC8A9-18EC-46C0-B746-E7F06CB5BDD2}"/>
-    <hyperlink ref="C137" r:id="rId136" tooltip="Abrir" xr:uid="{BF59BE92-617E-4E91-8087-F29231B7EF54}"/>
-    <hyperlink ref="C138" r:id="rId137" tooltip="Abrir" xr:uid="{94F21B1E-EBCC-44DF-B242-CE3776175324}"/>
-    <hyperlink ref="C139" r:id="rId138" tooltip="Abrir" xr:uid="{3AE818AC-EE34-49A8-B38F-AC2494501AC9}"/>
-    <hyperlink ref="C140" r:id="rId139" tooltip="Abrir" xr:uid="{B5D0DBAD-74D0-4245-9579-B8C7473E5B33}"/>
-    <hyperlink ref="C141" r:id="rId140" tooltip="Abrir" xr:uid="{36143B2C-E491-4A0E-AA94-386C951F3F67}"/>
-    <hyperlink ref="C142" r:id="rId141" tooltip="Abrir" xr:uid="{769305CD-BA07-460C-A052-11E11E0C163D}"/>
-    <hyperlink ref="C143" r:id="rId142" tooltip="Abrir" xr:uid="{1C96FB3A-BA01-45CF-9347-5098C9E0966E}"/>
-    <hyperlink ref="C144" r:id="rId143" tooltip="Abrir" xr:uid="{604894A8-50EB-4DC8-A050-866095F4F4D5}"/>
-    <hyperlink ref="C145" r:id="rId144" tooltip="Abrir" xr:uid="{4378DA09-C357-43DD-AD87-567BCF65CBAB}"/>
-    <hyperlink ref="C146" r:id="rId145" tooltip="Abrir" xr:uid="{6FAF7144-38C6-4A6C-BAFB-59F27924A987}"/>
-    <hyperlink ref="C147" r:id="rId146" tooltip="Abrir" xr:uid="{A374295A-4325-4917-A600-92D273DF9255}"/>
-    <hyperlink ref="C148" r:id="rId147" tooltip="Abrir" xr:uid="{525C90BB-5073-4173-BCF8-18CEC2C53D72}"/>
-    <hyperlink ref="C149" r:id="rId148" tooltip="Abrir" xr:uid="{C52A493C-FC6D-4013-A02B-BF533BB7225C}"/>
-    <hyperlink ref="C150" r:id="rId149" tooltip="Abrir" xr:uid="{57E4F6D4-4E76-44D3-8EFF-38CCE43D8106}"/>
-    <hyperlink ref="C151" r:id="rId150" tooltip="Abrir" xr:uid="{C6CE925B-F142-4133-AA89-4E3B53B5A288}"/>
-    <hyperlink ref="C152" r:id="rId151" tooltip="Abrir" xr:uid="{10A013DA-607E-4320-A452-FA1C626EBDC5}"/>
-    <hyperlink ref="C153" r:id="rId152" tooltip="Abrir" xr:uid="{F79C940A-548C-4DCC-A967-9F7FB79521AC}"/>
-    <hyperlink ref="C154" r:id="rId153" tooltip="Abrir" xr:uid="{2BC3B938-4E85-418D-B541-A4F2D5B74707}"/>
-    <hyperlink ref="C155" r:id="rId154" tooltip="Abrir" xr:uid="{DB98B391-E5F2-4CE8-B520-2CAC053683D4}"/>
-    <hyperlink ref="C156" r:id="rId155" tooltip="Abrir" xr:uid="{98217AD4-2922-45CE-8462-33A8044C6800}"/>
-    <hyperlink ref="C157" r:id="rId156" tooltip="Abrir" xr:uid="{89E24472-0A1E-4D73-B82C-C2859065FBC5}"/>
-    <hyperlink ref="C158" r:id="rId157" tooltip="Abrir" xr:uid="{6229CC18-BEB8-426A-9110-0A8302D9061C}"/>
-    <hyperlink ref="C159" r:id="rId158" tooltip="Abrir" xr:uid="{367A2D50-C83B-4354-9826-DAC24308674D}"/>
-    <hyperlink ref="C160" r:id="rId159" tooltip="Abrir" xr:uid="{872EADB7-A103-4062-86DC-8A881EB730A3}"/>
-    <hyperlink ref="C161" r:id="rId160" tooltip="Abrir" xr:uid="{7B44B86E-8452-4AD8-91BC-89A031D205C4}"/>
-    <hyperlink ref="C162" r:id="rId161" tooltip="Abrir" xr:uid="{460D8ED6-CF2C-444E-BD15-7475218B2030}"/>
-    <hyperlink ref="C163" r:id="rId162" tooltip="Abrir" xr:uid="{B96728E0-7D54-434F-803D-A23F24ABCEEC}"/>
-    <hyperlink ref="C164" r:id="rId163" tooltip="Abrir" xr:uid="{DED2147F-04DE-4EFD-8310-4324D03C766F}"/>
-    <hyperlink ref="C165" r:id="rId164" tooltip="Abrir" xr:uid="{5782EE70-4AFA-491C-BD72-9D14FDE196EB}"/>
-    <hyperlink ref="C166" r:id="rId165" tooltip="Abrir" xr:uid="{6CD70498-B824-4213-9D5B-2538F0F49722}"/>
-    <hyperlink ref="C167" r:id="rId166" tooltip="Abrir" xr:uid="{CCBC458D-BEB6-4573-B1F5-48169BA53814}"/>
-    <hyperlink ref="C168" r:id="rId167" tooltip="Abrir" xr:uid="{C6C85B4A-EA7D-479D-87AF-781D5BD4620E}"/>
-    <hyperlink ref="C169" r:id="rId168" tooltip="Abrir" xr:uid="{E4AD942F-C280-4412-B7B1-5250AC2D33D8}"/>
-    <hyperlink ref="C170" r:id="rId169" tooltip="Abrir" xr:uid="{27B02E65-E1BF-4C06-9F75-E06FC77C7C6A}"/>
-    <hyperlink ref="C171" r:id="rId170" tooltip="Abrir" xr:uid="{9D852A73-8FD0-404D-8341-B865F2B89DF4}"/>
-    <hyperlink ref="C172" r:id="rId171" tooltip="Abrir" xr:uid="{8D9E29B6-E33D-415B-AA64-BAFE87FCE4D5}"/>
-    <hyperlink ref="C173" r:id="rId172" tooltip="Abrir" xr:uid="{F2E36F3A-1651-4469-A2ED-0B67B00A1ADD}"/>
-    <hyperlink ref="C174" r:id="rId173" tooltip="Abrir" xr:uid="{B1DCCC7B-2C5F-4EAC-908C-021D23D9C3F0}"/>
-    <hyperlink ref="C175" r:id="rId174" tooltip="Abrir" xr:uid="{E34A5A3A-24B4-41EF-BCE0-2120212FD540}"/>
-    <hyperlink ref="C176" r:id="rId175" tooltip="Abrir" xr:uid="{B37DEA8B-EB29-4F57-A741-34550EB77FA3}"/>
-    <hyperlink ref="C177" r:id="rId176" tooltip="Abrir" xr:uid="{5438405E-4B46-4ABE-9D68-643292ECD75F}"/>
-    <hyperlink ref="C178" r:id="rId177" tooltip="Abrir" xr:uid="{04FD570E-2A19-427D-BB05-4B0F0AED2197}"/>
-    <hyperlink ref="C179" r:id="rId178" tooltip="Abrir" xr:uid="{66C6E3CF-529B-446D-94CF-768089D73565}"/>
-    <hyperlink ref="C180" r:id="rId179" tooltip="Abrir" xr:uid="{0AB4715D-1D73-47B3-816F-59C323C584D3}"/>
-    <hyperlink ref="C181" r:id="rId180" tooltip="Abrir" xr:uid="{CE275445-3D2D-4169-A2E5-BF7E712C746A}"/>
-    <hyperlink ref="C182" r:id="rId181" tooltip="Abrir" xr:uid="{52D6BA60-F97C-4A54-A48C-3CA10EFE86BA}"/>
-    <hyperlink ref="C183" r:id="rId182" tooltip="Abrir" xr:uid="{0D9E5EF9-62BA-4524-B3BC-5378D955DDB3}"/>
-    <hyperlink ref="C184" r:id="rId183" tooltip="Abrir" xr:uid="{F2068604-7675-4CF0-BA72-0DC0F1EFB831}"/>
-    <hyperlink ref="C185" r:id="rId184" tooltip="Abrir" xr:uid="{D3C941B1-83A7-494C-A833-6963163A9157}"/>
-    <hyperlink ref="C186" r:id="rId185" tooltip="Abrir" xr:uid="{C9D230A6-A935-4FEA-AFCE-3C4F037B3940}"/>
-    <hyperlink ref="C187" r:id="rId186" tooltip="Abrir" xr:uid="{9B5BF91B-58A3-4604-A59E-72FFA065799B}"/>
-    <hyperlink ref="C188" r:id="rId187" tooltip="Abrir" xr:uid="{EF577421-FAC4-4511-B47D-16FE9481613F}"/>
-    <hyperlink ref="C189" r:id="rId188" tooltip="Abrir" xr:uid="{354AA5D9-4CB7-40DC-B228-9C4C4DFF68B6}"/>
-    <hyperlink ref="C190" r:id="rId189" tooltip="Abrir" xr:uid="{A8AED613-67F4-4758-8439-870CED86A7FB}"/>
-    <hyperlink ref="C191" r:id="rId190" tooltip="Abrir" xr:uid="{6C85B0A2-A252-495F-9A02-62F1E129C775}"/>
-    <hyperlink ref="C192" r:id="rId191" tooltip="Abrir" xr:uid="{95B0A906-FD06-4614-9A30-CD4E10FA4950}"/>
-    <hyperlink ref="C193" r:id="rId192" tooltip="Abrir" xr:uid="{E1578801-6B70-4215-A9E2-45A256BD8232}"/>
-    <hyperlink ref="C194" r:id="rId193" tooltip="Abrir" xr:uid="{878B23BB-867A-4455-9C78-B32C23BD151C}"/>
-    <hyperlink ref="C195" r:id="rId194" tooltip="Abrir" xr:uid="{731AAD2B-C630-453B-9FBC-2DC942E6C5B8}"/>
-    <hyperlink ref="C196" r:id="rId195" tooltip="Abrir" xr:uid="{167856BD-2E2A-4FF9-9512-4230959EC7CF}"/>
-    <hyperlink ref="C197" r:id="rId196" tooltip="Abrir" xr:uid="{5AC64BD0-D9B5-4164-B66B-263CE40FA558}"/>
-    <hyperlink ref="C198" r:id="rId197" tooltip="Abrir" xr:uid="{1EFD6658-BCC6-4ABC-9AD9-82CA7D0D2B5A}"/>
-    <hyperlink ref="C199" r:id="rId198" tooltip="Abrir" xr:uid="{48676D2F-415E-4526-9064-FE1AA1B38B1B}"/>
-    <hyperlink ref="C200" r:id="rId199" tooltip="Abrir" xr:uid="{15D0DB4A-2907-4EFF-BB85-1063D3C49486}"/>
-    <hyperlink ref="C201" r:id="rId200" tooltip="Abrir" xr:uid="{A5B97340-4E3C-4D74-AAB9-3CD7F3A2F59A}"/>
-    <hyperlink ref="C202" r:id="rId201" tooltip="Abrir" xr:uid="{B2696166-D398-4B7E-AB6B-366338F97E76}"/>
-    <hyperlink ref="C203" r:id="rId202" tooltip="Abrir" xr:uid="{82A90CA1-771E-48CF-A770-DCE03CF68B6C}"/>
-    <hyperlink ref="C204" r:id="rId203" tooltip="Abrir" xr:uid="{E780CEB9-F0CE-4187-981D-A73122993BAE}"/>
-    <hyperlink ref="C205" r:id="rId204" tooltip="Abrir" xr:uid="{81415652-02BA-4A49-B7E0-13D68C281013}"/>
-    <hyperlink ref="C206" r:id="rId205" tooltip="Abrir" xr:uid="{6F7A9F58-0AAA-489A-B560-4C2C39C748F7}"/>
-    <hyperlink ref="C207" r:id="rId206" tooltip="Abrir" xr:uid="{2A493BA2-3D43-4B7B-8E05-A95BFF31B255}"/>
-    <hyperlink ref="C208" r:id="rId207" tooltip="Abrir" xr:uid="{F067EC96-D248-4876-9DA9-823294D701B8}"/>
-    <hyperlink ref="C209" r:id="rId208" tooltip="Abrir" xr:uid="{E306A140-9435-4B61-B9E3-717DCDC874BD}"/>
-    <hyperlink ref="C210" r:id="rId209" tooltip="Abrir" xr:uid="{7FDD3534-7BEF-4CDB-BB22-D2491B800984}"/>
-    <hyperlink ref="C211" r:id="rId210" tooltip="Abrir" xr:uid="{0D5189F5-8692-4FDA-8D52-B0612C3CBE3E}"/>
-    <hyperlink ref="C212" r:id="rId211" tooltip="Abrir" xr:uid="{4D0E3ED7-5A40-4AB0-A797-9DC1ECE33834}"/>
-    <hyperlink ref="C213" r:id="rId212" tooltip="Abrir" xr:uid="{059C717F-1BC8-42BE-9B4E-5BF794903EB6}"/>
-    <hyperlink ref="C214" r:id="rId213" tooltip="Abrir" xr:uid="{D385DB68-9CE2-4430-883A-E41E1ECAB776}"/>
-    <hyperlink ref="C215" r:id="rId214" tooltip="Abrir" xr:uid="{D4162E49-7074-49BD-9DB7-5587125DBA9E}"/>
-    <hyperlink ref="C216" r:id="rId215" tooltip="Abrir" xr:uid="{595F5340-70FC-47BB-8FBA-FB4F4C6922B5}"/>
-    <hyperlink ref="C217" r:id="rId216" tooltip="Abrir" xr:uid="{5516EC60-E3EA-47BD-A093-00EF46DF1533}"/>
-    <hyperlink ref="C218" r:id="rId217" tooltip="Abrir" xr:uid="{67834E27-8843-48AD-92F2-7435727B0F72}"/>
-    <hyperlink ref="C219" r:id="rId218" tooltip="Abrir" xr:uid="{897CF8BD-B0FA-412D-91E2-409EFB36885C}"/>
-    <hyperlink ref="C220" r:id="rId219" tooltip="Abrir" xr:uid="{9E3A2E00-CCFB-4023-B504-3CF7C9E8A4D3}"/>
-    <hyperlink ref="C221" r:id="rId220" tooltip="Abrir" xr:uid="{E20A01F8-E9E6-4F6D-A4F0-F941B15A544F}"/>
-    <hyperlink ref="C222" r:id="rId221" tooltip="Abrir" xr:uid="{FD1BDE44-F4F8-42FC-8CDE-53D6C5E651C8}"/>
-    <hyperlink ref="C223" r:id="rId222" tooltip="Abrir" xr:uid="{B2A4B1EA-4BE5-4D77-BF4B-2339C18D6047}"/>
-    <hyperlink ref="C224" r:id="rId223" tooltip="Abrir" xr:uid="{609DCCB2-5217-4E09-8C68-2A8B862E0664}"/>
-    <hyperlink ref="C225" r:id="rId224" tooltip="Abrir" xr:uid="{21C8A463-6DB4-462E-8790-D690C442DA97}"/>
-    <hyperlink ref="C226" r:id="rId225" tooltip="Abrir" xr:uid="{9847C49C-10A4-4CA6-9CD3-472C40914748}"/>
-    <hyperlink ref="C227" r:id="rId226" tooltip="Abrir" xr:uid="{7F9C8521-CBF8-45F4-909A-A597A5234CDA}"/>
-    <hyperlink ref="C228" r:id="rId227" tooltip="Abrir" xr:uid="{1B8EDAF3-927B-4019-BA2A-DF21BAD0AB0D}"/>
-    <hyperlink ref="C229" r:id="rId228" tooltip="Abrir" xr:uid="{4115BE97-904E-4A78-8873-DC7F266D0718}"/>
-    <hyperlink ref="C230" r:id="rId229" tooltip="Abrir" xr:uid="{452974AB-4699-4561-81D5-E45BE9DE81AB}"/>
-    <hyperlink ref="C231" r:id="rId230" tooltip="Abrir" xr:uid="{CDD4B4B0-C71D-4613-9AB2-274C73F2A05B}"/>
-    <hyperlink ref="C232" r:id="rId231" tooltip="Abrir" xr:uid="{219A0BE8-0740-4D1B-847D-4D746C714167}"/>
-    <hyperlink ref="C233" r:id="rId232" tooltip="Abrir" xr:uid="{B9B95937-A8B5-420A-B484-2C2BE685082A}"/>
-    <hyperlink ref="C234" r:id="rId233" tooltip="Abrir" xr:uid="{1122BF82-CBCD-4589-A984-4B209D37D7E7}"/>
-    <hyperlink ref="C235" r:id="rId234" tooltip="Abrir" xr:uid="{E45A9740-7541-4872-97E9-0CC6D71AAFC7}"/>
-    <hyperlink ref="C236" r:id="rId235" tooltip="Abrir" xr:uid="{1A7A3D21-23A0-42B5-81EE-C8698B167BFE}"/>
-    <hyperlink ref="C237" r:id="rId236" tooltip="Abrir" xr:uid="{2D495C24-BAA5-47E4-908B-CBD60F7810D4}"/>
-    <hyperlink ref="C238" r:id="rId237" tooltip="Abrir" xr:uid="{D27DC639-52D0-4AB4-A15C-27514F1BBB13}"/>
-    <hyperlink ref="C239" r:id="rId238" tooltip="Abrir" xr:uid="{4C6E75FD-5B6D-4FBB-A44F-94958D14DB63}"/>
-    <hyperlink ref="C240" r:id="rId239" tooltip="Abrir" xr:uid="{B4AE866A-4F05-47B3-9586-AE5BE80CA67F}"/>
-    <hyperlink ref="C241" r:id="rId240" tooltip="Abrir" xr:uid="{25D59B0F-9209-4187-9C26-F830F30CA694}"/>
-    <hyperlink ref="C242" r:id="rId241" tooltip="Abrir" xr:uid="{76465FC3-4D5C-42E4-9F80-876A215B0602}"/>
-    <hyperlink ref="C243" r:id="rId242" tooltip="Abrir" xr:uid="{427A21E0-B742-4FCE-B22D-22305DBBC30C}"/>
-    <hyperlink ref="C244" r:id="rId243" tooltip="Abrir" xr:uid="{169D2C6E-7FCC-4C6A-A442-AA3795CFA70F}"/>
-    <hyperlink ref="C245" r:id="rId244" tooltip="Abrir" xr:uid="{BBB8BA02-F739-45AC-BB26-5D70368EBEBD}"/>
-    <hyperlink ref="C246" r:id="rId245" tooltip="Abrir" xr:uid="{D863218C-ED5A-4ADD-A1F5-170CA873B6C3}"/>
-    <hyperlink ref="C247" r:id="rId246" tooltip="Abrir" xr:uid="{CAA3FBB2-62CE-4B66-92D3-F64683F730D0}"/>
-    <hyperlink ref="C248" r:id="rId247" tooltip="Abrir" xr:uid="{C7499007-FADE-4F54-A4E9-634E25A5BB80}"/>
-    <hyperlink ref="C249" r:id="rId248" tooltip="Abrir" xr:uid="{68058260-3F41-4F09-BE63-FAC37B86988B}"/>
-    <hyperlink ref="C250" r:id="rId249" tooltip="Abrir" xr:uid="{BE633F97-A5A8-4643-94F6-4684F8ED65E2}"/>
-    <hyperlink ref="C251" r:id="rId250" tooltip="Abrir" xr:uid="{DB594134-2192-4129-A5D8-943CDE71751C}"/>
-    <hyperlink ref="C252" r:id="rId251" tooltip="Abrir" xr:uid="{01D3B046-4A6F-4D94-BDE7-7173D8C444CC}"/>
-    <hyperlink ref="C253" r:id="rId252" tooltip="Abrir" xr:uid="{9869720A-5E60-4820-A5A6-F964EB87EFF6}"/>
-    <hyperlink ref="C254" r:id="rId253" tooltip="Abrir" xr:uid="{63080ED0-EBB5-48C9-95A7-C21D4DAEA8FF}"/>
-    <hyperlink ref="C255" r:id="rId254" tooltip="Abrir" xr:uid="{BBD9A021-01D4-4A37-8533-34FA61A2ABCF}"/>
-    <hyperlink ref="C256" r:id="rId255" tooltip="Abrir" xr:uid="{B4801D83-E8E8-4568-8875-AB91A478FBE2}"/>
-    <hyperlink ref="C257" r:id="rId256" tooltip="Abrir" xr:uid="{3C7439F7-B235-42B1-AA35-E98D6AE197A0}"/>
-    <hyperlink ref="C258" r:id="rId257" tooltip="Abrir" xr:uid="{B0C955B3-4973-406D-8B2A-AD0B2323509B}"/>
-    <hyperlink ref="C259" r:id="rId258" tooltip="Abrir" xr:uid="{9A0CC771-8C37-4C64-898F-D0EE81413746}"/>
-    <hyperlink ref="C260" r:id="rId259" tooltip="Abrir" xr:uid="{4221A003-A361-4447-A227-A8C56AC10AF1}"/>
-    <hyperlink ref="C261" r:id="rId260" tooltip="Abrir" xr:uid="{39DCA1E1-EEBD-4C6A-BED0-3CFD25D47A66}"/>
-    <hyperlink ref="C262" r:id="rId261" tooltip="Abrir" xr:uid="{56591ABF-3B9E-4543-AC1F-2590C13EA169}"/>
-    <hyperlink ref="C263" r:id="rId262" tooltip="Abrir" xr:uid="{675CD2B5-0AF6-45DA-80D6-69F5400C260F}"/>
-    <hyperlink ref="C264" r:id="rId263" tooltip="Abrir" xr:uid="{4A2E0FC7-0EC4-462F-BB99-8669B8513211}"/>
-    <hyperlink ref="C265" r:id="rId264" tooltip="Abrir" xr:uid="{2C35DE65-74E8-43CC-A216-46F7440C31C3}"/>
-    <hyperlink ref="C266" r:id="rId265" tooltip="Abrir" xr:uid="{592A2C97-EC89-4BFA-8625-07971DEFA6F2}"/>
-    <hyperlink ref="C267" r:id="rId266" tooltip="Abrir" xr:uid="{026C1848-87CA-42F9-8BB7-565058D395D4}"/>
-    <hyperlink ref="C268" r:id="rId267" tooltip="Abrir" xr:uid="{1A672519-3599-47FC-B170-23A33DEAFEB2}"/>
-    <hyperlink ref="C269" r:id="rId268" tooltip="Abrir" xr:uid="{C6E85730-C58F-46F6-A414-B25AC75439B5}"/>
-    <hyperlink ref="C270" r:id="rId269" tooltip="Abrir" xr:uid="{41719A53-8DA2-4F83-889B-6AE3CC8D7FF8}"/>
-    <hyperlink ref="C271" r:id="rId270" tooltip="Abrir" xr:uid="{20C205B9-9976-4DBB-A331-42F88E158609}"/>
-    <hyperlink ref="C272" r:id="rId271" tooltip="Abrir" xr:uid="{6F42B048-0AA1-49B6-ADB3-261147D07942}"/>
-    <hyperlink ref="C273" r:id="rId272" tooltip="Abrir" xr:uid="{E16634C7-4EDB-42C5-B286-3AEA23A4FA2B}"/>
-    <hyperlink ref="C274" r:id="rId273" tooltip="Abrir" xr:uid="{7DF3013C-010F-49E8-9A5A-7C0549D35A63}"/>
-    <hyperlink ref="C275" r:id="rId274" tooltip="Abrir" xr:uid="{9B559804-DFA2-4A37-AD6F-B5924A7D3D8D}"/>
-    <hyperlink ref="C276" r:id="rId275" tooltip="Abrir" xr:uid="{0D2E05EF-2678-4337-9F88-3559D37E284F}"/>
-    <hyperlink ref="C277" r:id="rId276" tooltip="Abrir" xr:uid="{2518C5EC-F585-459F-9E3A-90A302D37A76}"/>
-    <hyperlink ref="C278" r:id="rId277" tooltip="Abrir" xr:uid="{DBC03E99-E1BF-4409-8884-7A3D0EEF427B}"/>
-    <hyperlink ref="C279" r:id="rId278" tooltip="Abrir" xr:uid="{08817922-A7FB-49EE-BBC0-E682C574E7B6}"/>
-    <hyperlink ref="C280" r:id="rId279" tooltip="Abrir" xr:uid="{47601CB4-972C-42EE-86D0-36F1A0F648DB}"/>
-    <hyperlink ref="C281" r:id="rId280" tooltip="Abrir" xr:uid="{A1B8831E-BE7E-44EA-9762-92A131BB2159}"/>
-    <hyperlink ref="C282" r:id="rId281" tooltip="Abrir" xr:uid="{92FDEC33-F5B1-4656-A0A2-AFB248F48DA8}"/>
-    <hyperlink ref="C283" r:id="rId282" tooltip="Abrir" xr:uid="{9994DB41-9A0E-4C5C-B940-52B175CEB7A3}"/>
-    <hyperlink ref="C284" r:id="rId283" tooltip="Abrir" xr:uid="{D7416B31-899E-4872-A501-9770D916E1FB}"/>
-    <hyperlink ref="C285" r:id="rId284" tooltip="Abrir" xr:uid="{33879144-C662-44AA-873D-26FA3E4670D2}"/>
-    <hyperlink ref="C286" r:id="rId285" tooltip="Abrir" xr:uid="{57BFA3CE-8EE7-4908-8A96-62A7C1DE81DA}"/>
-    <hyperlink ref="C287" r:id="rId286" tooltip="Abrir" xr:uid="{335E1F7F-7992-4C65-A6E7-4991C2F74D53}"/>
-    <hyperlink ref="C288" r:id="rId287" tooltip="Abrir" xr:uid="{4B0103DD-F17D-4AA6-B4A6-20B7ECBF7B55}"/>
-    <hyperlink ref="C289" r:id="rId288" tooltip="Abrir" xr:uid="{F54C3E20-6E49-449D-9DA7-562D8D486C72}"/>
-    <hyperlink ref="C290" r:id="rId289" tooltip="Abrir" xr:uid="{E5BB6FC3-A023-4350-AE5A-4B9FCEC57A58}"/>
-    <hyperlink ref="C291" r:id="rId290" tooltip="Abrir" xr:uid="{CAAC5B03-D411-4747-8B74-4D9C98C11235}"/>
-    <hyperlink ref="C292" r:id="rId291" tooltip="Abrir" xr:uid="{8037A56D-0B52-4632-9DD8-29CC421C1F4B}"/>
-    <hyperlink ref="C293" r:id="rId292" tooltip="Abrir" xr:uid="{C41B3ABB-A9F6-4996-96BE-0A95C286E51F}"/>
-    <hyperlink ref="C294" r:id="rId293" tooltip="Abrir" xr:uid="{19BBA45E-23F0-4758-9268-4CE01D9939BC}"/>
-    <hyperlink ref="C295" r:id="rId294" tooltip="Abrir" xr:uid="{CEFC66CD-45E8-45A2-BCB5-72419340A818}"/>
-    <hyperlink ref="C296" r:id="rId295" tooltip="Abrir" xr:uid="{436051ED-248A-4334-8624-5A44071E9437}"/>
-    <hyperlink ref="C297" r:id="rId296" tooltip="Abrir" xr:uid="{48EA8E2D-040A-41C4-B5FD-84D6EB333F80}"/>
-    <hyperlink ref="C298" r:id="rId297" tooltip="Abrir" xr:uid="{CF69BD5B-85C7-4CAC-8F5A-8BBFC089E19F}"/>
-    <hyperlink ref="C299" r:id="rId298" tooltip="Abrir" xr:uid="{E02FC803-48A3-4EB7-8BED-391B6CA4261C}"/>
-    <hyperlink ref="C300" r:id="rId299" tooltip="Abrir" xr:uid="{63F8104C-2A92-4847-AD9F-7C4AB9BD6025}"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="Abrir" xr:uid="{71073E04-7584-4672-B5E1-8043D74AD64D}"/>
+    <hyperlink ref="C3" r:id="rId2" tooltip="Abrir" xr:uid="{AF1D6E2D-545B-42EC-B4E5-A5744D6F81C2}"/>
+    <hyperlink ref="C4" r:id="rId3" tooltip="Abrir" xr:uid="{FFE8CC79-6DD0-423B-B61F-A6D2F32CD42D}"/>
+    <hyperlink ref="C5" r:id="rId4" tooltip="Abrir" xr:uid="{83B90E62-81CE-458B-B709-56064A114726}"/>
+    <hyperlink ref="C6" r:id="rId5" tooltip="Abrir" xr:uid="{0CF1D9B0-C089-4A4D-9666-9A926BE24543}"/>
+    <hyperlink ref="C7" r:id="rId6" tooltip="Abrir" xr:uid="{6F4A4531-EB36-41F6-8775-FAE85D8AABFE}"/>
+    <hyperlink ref="C8" r:id="rId7" tooltip="Abrir" xr:uid="{D64F66DA-0B12-4A05-89ED-ADB096735757}"/>
+    <hyperlink ref="C9" r:id="rId8" tooltip="Abrir" xr:uid="{F3B454D7-01BC-42B2-846C-A77DB7FFFE07}"/>
+    <hyperlink ref="C10" r:id="rId9" tooltip="Abrir" xr:uid="{4E55FC26-4E21-4F10-A0F0-8F172EC7D808}"/>
+    <hyperlink ref="C11" r:id="rId10" tooltip="Abrir" xr:uid="{A6C36C00-DB58-46FA-8924-24CE877ACCA5}"/>
+    <hyperlink ref="C12" r:id="rId11" tooltip="Abrir" xr:uid="{8EE3685D-852D-4BF0-BB08-38C67ED561A9}"/>
+    <hyperlink ref="C13" r:id="rId12" tooltip="Abrir" xr:uid="{49198A81-5D81-4AF2-BF49-ABE416F4C25E}"/>
+    <hyperlink ref="C14" r:id="rId13" tooltip="Abrir" xr:uid="{C302492B-2AB4-4095-AA60-21E264BBA1D6}"/>
+    <hyperlink ref="C15" r:id="rId14" tooltip="Abrir" xr:uid="{8A204BEC-1745-4B15-98AD-63DED5CA2FDA}"/>
+    <hyperlink ref="C16" r:id="rId15" tooltip="Abrir" xr:uid="{AE8E16B7-0827-4E2D-9D16-83CB8EE6CC88}"/>
+    <hyperlink ref="C17" r:id="rId16" tooltip="Abrir" xr:uid="{D75FA16C-C409-4FD9-B71A-84744C6B448C}"/>
+    <hyperlink ref="C18" r:id="rId17" tooltip="Abrir" xr:uid="{9FCCCF95-DC0B-410F-84B9-FF3022691338}"/>
+    <hyperlink ref="C19" r:id="rId18" tooltip="Abrir" xr:uid="{A5B7E61D-2D33-42EA-BD39-F514675E9F27}"/>
+    <hyperlink ref="C20" r:id="rId19" tooltip="Abrir" xr:uid="{2FAF6F68-CFA1-40CB-B7B1-17CDD91B9D73}"/>
+    <hyperlink ref="C21" r:id="rId20" tooltip="Abrir" xr:uid="{F2EC8180-CBEF-4144-BE5A-F296F1CCF1DC}"/>
+    <hyperlink ref="C22" r:id="rId21" tooltip="Abrir" xr:uid="{A2BA7E23-748F-4695-8388-298A2AA5AD35}"/>
+    <hyperlink ref="C23" r:id="rId22" tooltip="Abrir" xr:uid="{ACA471A3-E017-48BA-9357-3E6E82D550DA}"/>
+    <hyperlink ref="C24" r:id="rId23" tooltip="Abrir" xr:uid="{D980269B-2F9B-45D8-AB85-814308DCF233}"/>
+    <hyperlink ref="C25" r:id="rId24" tooltip="Abrir" xr:uid="{41E8D965-96FA-42D0-8CC3-7CFBC9112354}"/>
+    <hyperlink ref="C26" r:id="rId25" tooltip="Abrir" xr:uid="{09EB7E44-F7A4-4F74-B3C1-F27BEA9EE0F0}"/>
+    <hyperlink ref="C27" r:id="rId26" tooltip="Abrir" xr:uid="{19CC7F81-2CB3-41BA-86EE-8ADA555D9433}"/>
+    <hyperlink ref="C28" r:id="rId27" tooltip="Abrir" xr:uid="{B705551F-E81A-446D-8C69-BA86F2AE9233}"/>
+    <hyperlink ref="C29" r:id="rId28" tooltip="Abrir" xr:uid="{4BB30117-5025-4BD6-86E8-8B8CA4CE02D7}"/>
+    <hyperlink ref="C30" r:id="rId29" tooltip="Abrir" xr:uid="{349518E4-D33C-4084-8BD6-95709AC1CD70}"/>
+    <hyperlink ref="C31" r:id="rId30" tooltip="Abrir" xr:uid="{5934CAF4-8A24-4929-8B3E-210506FE2CEC}"/>
+    <hyperlink ref="C32" r:id="rId31" tooltip="Abrir" xr:uid="{92BDA605-7749-451D-B866-850EA8AD5E63}"/>
+    <hyperlink ref="C33" r:id="rId32" tooltip="Abrir" xr:uid="{5413E38E-974B-45E0-9531-E5E460342CEF}"/>
+    <hyperlink ref="C34" r:id="rId33" tooltip="Abrir" xr:uid="{8FF56AE3-8758-4D50-B7AB-6F9C6F7F5A82}"/>
+    <hyperlink ref="C35" r:id="rId34" tooltip="Abrir" xr:uid="{06BC7067-D1BC-47C0-83B3-05329B6AE325}"/>
+    <hyperlink ref="C36" r:id="rId35" tooltip="Abrir" xr:uid="{5F017ECF-0A8F-4A6A-AA78-C7FC591E0454}"/>
+    <hyperlink ref="C37" r:id="rId36" tooltip="Abrir" xr:uid="{CB47AC38-3007-4350-8EB9-10BE33F247D0}"/>
+    <hyperlink ref="C38" r:id="rId37" tooltip="Abrir" xr:uid="{8F84A7E6-CDE0-44CE-B3FF-F73C59471840}"/>
+    <hyperlink ref="C39" r:id="rId38" tooltip="Abrir" xr:uid="{601ADC5A-5D47-4173-B810-B073CD009B89}"/>
+    <hyperlink ref="C40" r:id="rId39" tooltip="Abrir" xr:uid="{093FC069-384D-4EB2-A17E-60BC8907956F}"/>
+    <hyperlink ref="C41" r:id="rId40" tooltip="Abrir" xr:uid="{4703FDEB-682B-4168-B74E-2716FB98021A}"/>
+    <hyperlink ref="C42" r:id="rId41" tooltip="Abrir" xr:uid="{9D487425-CFE1-4A93-8182-D56C874B2368}"/>
+    <hyperlink ref="C43" r:id="rId42" tooltip="Abrir" xr:uid="{9031FB66-2E41-47E5-963B-EF0329E5D4E3}"/>
+    <hyperlink ref="C44" r:id="rId43" tooltip="Abrir" xr:uid="{D29E7D1A-8C24-4D25-A87F-52FD0EB0DBEC}"/>
+    <hyperlink ref="C45" r:id="rId44" tooltip="Abrir" xr:uid="{1E4B6C21-F399-4DC5-8579-7D07503506F2}"/>
+    <hyperlink ref="C46" r:id="rId45" tooltip="Abrir" xr:uid="{92FFA31F-6616-4F7E-86AF-4F397F768D68}"/>
+    <hyperlink ref="C47" r:id="rId46" tooltip="Abrir" xr:uid="{02C12D5A-6657-4DEC-824B-6F388DF3C777}"/>
+    <hyperlink ref="C48" r:id="rId47" tooltip="Abrir" xr:uid="{A0A55F5D-A0BF-44D9-B0BD-D1C8C794791E}"/>
+    <hyperlink ref="C49" r:id="rId48" tooltip="Abrir" xr:uid="{AF34FCEE-8EF6-4B75-9270-F43B24AA771F}"/>
+    <hyperlink ref="C50" r:id="rId49" tooltip="Abrir" xr:uid="{36302DDE-6317-4A8F-85EE-F040B9386C85}"/>
+    <hyperlink ref="C51" r:id="rId50" tooltip="Abrir" xr:uid="{6C6A7FD5-D3AC-421B-B4CA-6F91820C5097}"/>
+    <hyperlink ref="C52" r:id="rId51" tooltip="Abrir" xr:uid="{36F00E75-AEE2-4EE2-AD62-114F4C1602D8}"/>
+    <hyperlink ref="C53" r:id="rId52" tooltip="Abrir" xr:uid="{7824568E-5A69-4169-8130-D7D21D32082C}"/>
+    <hyperlink ref="C54" r:id="rId53" tooltip="Abrir" xr:uid="{DF6B0D3C-0976-4A76-9882-AABAED628B94}"/>
+    <hyperlink ref="C55" r:id="rId54" tooltip="Abrir" xr:uid="{01A2A618-5651-4CE4-922E-853601557115}"/>
+    <hyperlink ref="C56" r:id="rId55" tooltip="Abrir" xr:uid="{A3B1AE7A-C42A-4F7D-9694-63D016FEF9AD}"/>
+    <hyperlink ref="C57" r:id="rId56" tooltip="Abrir" xr:uid="{DAC5800E-D3A1-4876-8C0A-CC8561ACD5B6}"/>
+    <hyperlink ref="C58" r:id="rId57" tooltip="Abrir" xr:uid="{DE809CCA-61A8-40C6-9DA9-FCEE077F4252}"/>
+    <hyperlink ref="C59" r:id="rId58" tooltip="Abrir" xr:uid="{88EEEC7E-FF56-4E51-BE53-6E971AF37552}"/>
+    <hyperlink ref="C60" r:id="rId59" tooltip="Abrir" xr:uid="{78F625F6-B46C-4A9C-9C19-850BC4DDDF42}"/>
+    <hyperlink ref="C61" r:id="rId60" tooltip="Abrir" xr:uid="{0591B375-FE70-4AAE-8A07-6F29B0F205E1}"/>
+    <hyperlink ref="C62" r:id="rId61" tooltip="Abrir" xr:uid="{B82349BB-59CE-48FC-B80D-36CED2B624FE}"/>
+    <hyperlink ref="C63" r:id="rId62" tooltip="Abrir" xr:uid="{8710B4D0-905B-49B0-B587-416F2AA554AE}"/>
+    <hyperlink ref="C64" r:id="rId63" tooltip="Abrir" xr:uid="{1D74344B-7FBE-4581-BC08-53A6B98E480F}"/>
+    <hyperlink ref="C65" r:id="rId64" tooltip="Abrir" xr:uid="{21A6F712-416B-4C37-952C-33B0F1BA4063}"/>
+    <hyperlink ref="C66" r:id="rId65" tooltip="Abrir" xr:uid="{89EA4365-DDEB-447E-A9D6-D5AC97C313F7}"/>
+    <hyperlink ref="C67" r:id="rId66" tooltip="Abrir" xr:uid="{C7907744-4785-420F-BB18-1853E510A7B7}"/>
+    <hyperlink ref="C68" r:id="rId67" tooltip="Abrir" xr:uid="{EC85A145-9BBB-45C2-BF4D-44AEE630DF1E}"/>
+    <hyperlink ref="C69" r:id="rId68" tooltip="Abrir" xr:uid="{57AA2228-B21E-4584-B17D-B75CBBAFDD66}"/>
+    <hyperlink ref="C70" r:id="rId69" tooltip="Abrir" xr:uid="{726B465D-4B91-4A8D-A994-C5BA7A258752}"/>
+    <hyperlink ref="C71" r:id="rId70" tooltip="Abrir" xr:uid="{915B1274-3734-4573-BE27-0E00272EC95D}"/>
+    <hyperlink ref="C72" r:id="rId71" tooltip="Abrir" xr:uid="{8229BD09-044E-40B1-9923-4E62F6FB3561}"/>
+    <hyperlink ref="C73" r:id="rId72" tooltip="Abrir" xr:uid="{93D98E4F-F79B-49A2-AC91-48271E4CDE63}"/>
+    <hyperlink ref="C74" r:id="rId73" tooltip="Abrir" xr:uid="{49F54E89-F53E-434F-8552-BAC7BECA1DE1}"/>
+    <hyperlink ref="C75" r:id="rId74" tooltip="Abrir" xr:uid="{17BE7786-BE04-466E-AF57-AFD610530351}"/>
+    <hyperlink ref="C76" r:id="rId75" tooltip="Abrir" xr:uid="{85AE98DD-B0E3-4A7A-B870-B51147B46AEE}"/>
+    <hyperlink ref="C77" r:id="rId76" tooltip="Abrir" xr:uid="{2F9D2503-5AFB-42CE-8CA1-09C6E72F34E0}"/>
+    <hyperlink ref="C78" r:id="rId77" tooltip="Abrir" xr:uid="{778FC9C5-7F63-46E7-B9DA-C24BFC8BD77A}"/>
+    <hyperlink ref="C79" r:id="rId78" tooltip="Abrir" xr:uid="{95105F95-B215-4C43-983A-89C1D6BF43EA}"/>
+    <hyperlink ref="C80" r:id="rId79" tooltip="Abrir" xr:uid="{DA53C3DD-6CB7-48E5-BE93-EEE6288AF3F5}"/>
+    <hyperlink ref="C81" r:id="rId80" tooltip="Abrir" xr:uid="{39FFD926-DCED-4E95-B728-7AF9B3AB049B}"/>
+    <hyperlink ref="C82" r:id="rId81" tooltip="Abrir" xr:uid="{661A3D6D-E652-4F0E-8C03-A63DB8189389}"/>
+    <hyperlink ref="C83" r:id="rId82" tooltip="Abrir" xr:uid="{539E528C-EEA5-4FB0-8166-C4E37743BA8B}"/>
+    <hyperlink ref="C84" r:id="rId83" tooltip="Abrir" xr:uid="{6F8E1AB0-FC29-4131-B7DA-F6B0903B33AE}"/>
+    <hyperlink ref="C85" r:id="rId84" tooltip="Abrir" xr:uid="{E9CC0DEC-4888-467D-B18E-9C4A20AE497D}"/>
+    <hyperlink ref="C86" r:id="rId85" tooltip="Abrir" xr:uid="{B0A1553F-BAE2-4C54-BB5E-7D12DB4643C5}"/>
+    <hyperlink ref="C87" r:id="rId86" tooltip="Abrir" xr:uid="{5FFB78DC-1D26-4244-BDF8-383A192CE220}"/>
+    <hyperlink ref="C88" r:id="rId87" tooltip="Abrir" xr:uid="{E617E0CD-2A21-483D-B927-ED608128E7BF}"/>
+    <hyperlink ref="C89" r:id="rId88" tooltip="Abrir" xr:uid="{393F8E1D-F1A4-46B6-A4C0-D146716EC3A5}"/>
+    <hyperlink ref="C90" r:id="rId89" tooltip="Abrir" xr:uid="{026FA2F8-8988-4F3E-8F99-D2CF18B01334}"/>
+    <hyperlink ref="C91" r:id="rId90" tooltip="Abrir" xr:uid="{A249378A-78FC-432B-A709-874581793392}"/>
+    <hyperlink ref="C92" r:id="rId91" tooltip="Abrir" xr:uid="{8FD960D0-02B3-4805-BAB8-0ED66767B3D3}"/>
+    <hyperlink ref="C93" r:id="rId92" tooltip="Abrir" xr:uid="{F81331E6-2B25-4A08-8E60-AC9303DD1C73}"/>
+    <hyperlink ref="C94" r:id="rId93" tooltip="Abrir" xr:uid="{3B50119C-0AC9-456C-BEB6-DEEB57397D74}"/>
+    <hyperlink ref="C95" r:id="rId94" tooltip="Abrir" xr:uid="{E81B6451-52F8-4458-9612-1D1B1D5B18F6}"/>
+    <hyperlink ref="C96" r:id="rId95" tooltip="Abrir" xr:uid="{C7DBC682-04F7-4FCE-8414-55CF326FC9B7}"/>
+    <hyperlink ref="C97" r:id="rId96" tooltip="Abrir" xr:uid="{571BAD09-2CFD-40FF-B49D-E6B0498B5D7D}"/>
+    <hyperlink ref="C98" r:id="rId97" tooltip="Abrir" xr:uid="{784714DB-01D9-4C12-897E-BEB6A1383710}"/>
+    <hyperlink ref="C99" r:id="rId98" tooltip="Abrir" xr:uid="{3011E5BD-62B8-4412-A8BF-DB9CD3B64B00}"/>
+    <hyperlink ref="C100" r:id="rId99" tooltip="Abrir" xr:uid="{E49D993E-BD60-4795-9A02-2F15C2247089}"/>
+    <hyperlink ref="C101" r:id="rId100" tooltip="Abrir" xr:uid="{53496FFB-5A2C-43DF-BEC6-58891D7FBC51}"/>
+    <hyperlink ref="C102" r:id="rId101" tooltip="Abrir" xr:uid="{A373CD01-1428-41CF-8EA1-FF7D8C3CFDC0}"/>
+    <hyperlink ref="C103" r:id="rId102" tooltip="Abrir" xr:uid="{ED9A4748-4E50-4CEC-ACE9-DE7FDD9451E7}"/>
+    <hyperlink ref="C104" r:id="rId103" tooltip="Abrir" xr:uid="{B24F1C21-7F72-4AF5-BFFE-5B117390CCDF}"/>
+    <hyperlink ref="C105" r:id="rId104" tooltip="Abrir" xr:uid="{C6FF7384-35E7-4D45-AA9D-78DA79A61B2B}"/>
+    <hyperlink ref="C106" r:id="rId105" tooltip="Abrir" xr:uid="{51F42B16-F323-44BB-915F-82C6288FB126}"/>
+    <hyperlink ref="C107" r:id="rId106" tooltip="Abrir" xr:uid="{B8D33398-EED9-4734-A0E7-7D76974514F6}"/>
+    <hyperlink ref="C108" r:id="rId107" tooltip="Abrir" xr:uid="{E65AA533-B023-4865-A71F-8E34EE87D7EE}"/>
+    <hyperlink ref="C109" r:id="rId108" tooltip="Abrir" xr:uid="{A7CEFCF0-8AAE-4FE1-B491-0C3C15BBAE49}"/>
+    <hyperlink ref="C110" r:id="rId109" tooltip="Abrir" xr:uid="{8AC011FB-514E-4CF4-8152-9DF143CDB2E9}"/>
+    <hyperlink ref="C111" r:id="rId110" tooltip="Abrir" xr:uid="{117BD7B3-C285-422D-8541-EC358258410F}"/>
+    <hyperlink ref="C112" r:id="rId111" tooltip="Abrir" xr:uid="{2498976A-EFC5-46AE-AAFD-72756D58F743}"/>
+    <hyperlink ref="C113" r:id="rId112" tooltip="Abrir" xr:uid="{882F058F-4627-4EF1-9CD1-7C244F5907A4}"/>
+    <hyperlink ref="C114" r:id="rId113" tooltip="Abrir" xr:uid="{C0D549B9-8413-4215-AF81-403525D31642}"/>
+    <hyperlink ref="C115" r:id="rId114" tooltip="Abrir" xr:uid="{01249541-A901-4D5B-808F-4DD5110FF88C}"/>
+    <hyperlink ref="C116" r:id="rId115" tooltip="Abrir" xr:uid="{38501573-8728-479F-B995-A0AD8D6429E1}"/>
+    <hyperlink ref="C117" r:id="rId116" tooltip="Abrir" xr:uid="{0DDA0454-5305-4941-A12C-6490393DD8CB}"/>
+    <hyperlink ref="C118" r:id="rId117" tooltip="Abrir" xr:uid="{94710B08-34BE-4895-8CD9-7429EEB5856C}"/>
+    <hyperlink ref="C119" r:id="rId118" tooltip="Abrir" xr:uid="{2A97BE34-D60D-411C-B570-45DCC1B4BD42}"/>
+    <hyperlink ref="C120" r:id="rId119" tooltip="Abrir" xr:uid="{B69CD0ED-0CC7-420A-8D9E-7EBF88364C3C}"/>
+    <hyperlink ref="C121" r:id="rId120" tooltip="Abrir" xr:uid="{D10A7ABA-82D0-4DEA-9031-32A3CDEC8DB2}"/>
+    <hyperlink ref="C122" r:id="rId121" tooltip="Abrir" xr:uid="{76515C82-BE53-47E8-BF6D-BED401B2931B}"/>
+    <hyperlink ref="C123" r:id="rId122" tooltip="Abrir" xr:uid="{06EADA14-8C1F-44BD-AF35-1A1E1C828CAF}"/>
+    <hyperlink ref="C124" r:id="rId123" tooltip="Abrir" xr:uid="{1F81CA0E-9E50-43F0-BE3B-81BB72C1EA53}"/>
+    <hyperlink ref="C125" r:id="rId124" tooltip="Abrir" xr:uid="{33F85F71-7679-4B35-BC49-D6A9EB41A75C}"/>
+    <hyperlink ref="C126" r:id="rId125" tooltip="Abrir" xr:uid="{AB79A248-AFC3-4AA0-8F2B-CFBFED24C126}"/>
+    <hyperlink ref="C127" r:id="rId126" tooltip="Abrir" xr:uid="{E4BB5815-A87F-4E19-854A-37E71ED78F49}"/>
+    <hyperlink ref="C128" r:id="rId127" tooltip="Abrir" xr:uid="{92959C44-35E4-4466-85AF-9FC75EA11C7B}"/>
+    <hyperlink ref="C129" r:id="rId128" tooltip="Abrir" xr:uid="{87B0F3F8-3F4A-4FD5-AB21-A1DA80E081BD}"/>
+    <hyperlink ref="C130" r:id="rId129" tooltip="Abrir" xr:uid="{CD627062-69C5-4ADB-8F67-2D8F9E12CF71}"/>
+    <hyperlink ref="C131" r:id="rId130" tooltip="Abrir" xr:uid="{93EA8013-AE7B-4CC3-91B0-15E3DD96ECC2}"/>
+    <hyperlink ref="C132" r:id="rId131" tooltip="Abrir" xr:uid="{1E8F1073-A4CB-46A6-8DC1-6BDC30FA12CB}"/>
+    <hyperlink ref="C133" r:id="rId132" tooltip="Abrir" xr:uid="{84EB480F-5C96-41D3-A84C-3A4E6DCF19B8}"/>
+    <hyperlink ref="C134" r:id="rId133" tooltip="Abrir" xr:uid="{26797405-F9C3-4B1D-A364-EFEA978C54E8}"/>
+    <hyperlink ref="C135" r:id="rId134" tooltip="Abrir" xr:uid="{A7BC214E-4737-43EE-B822-F0D02907CF93}"/>
+    <hyperlink ref="C136" r:id="rId135" tooltip="Abrir" xr:uid="{9F57C5F8-2994-4A08-AA2A-DFE7E5874ED8}"/>
+    <hyperlink ref="C137" r:id="rId136" tooltip="Abrir" xr:uid="{7A44DC72-BC10-421F-BD5E-255F8385C31D}"/>
+    <hyperlink ref="C138" r:id="rId137" tooltip="Abrir" xr:uid="{6D7B3E81-25D9-453F-A8BB-AEF364D0176E}"/>
+    <hyperlink ref="C139" r:id="rId138" tooltip="Abrir" xr:uid="{D97EF4D1-7EEF-4205-B1B2-B6868D2FBD04}"/>
+    <hyperlink ref="C140" r:id="rId139" tooltip="Abrir" xr:uid="{9F7C82A7-9DD5-49F0-B8B6-5B179BBA3EB0}"/>
+    <hyperlink ref="C141" r:id="rId140" tooltip="Abrir" xr:uid="{6D38102D-305D-4ABF-9900-5A63FC17FF91}"/>
+    <hyperlink ref="C142" r:id="rId141" tooltip="Abrir" xr:uid="{401018B7-4CFD-4F9E-9DCB-D68D01CF11F9}"/>
+    <hyperlink ref="C143" r:id="rId142" tooltip="Abrir" xr:uid="{5E40F144-1DF7-4097-9175-5C3B541DE258}"/>
+    <hyperlink ref="C144" r:id="rId143" tooltip="Abrir" xr:uid="{512C17A9-2B89-4561-86A6-DD8A796D1284}"/>
+    <hyperlink ref="C145" r:id="rId144" tooltip="Abrir" xr:uid="{C5FB7F6B-EB72-4F15-A9EC-2B38A1397ADC}"/>
+    <hyperlink ref="C146" r:id="rId145" tooltip="Abrir" xr:uid="{4F166315-BE8E-46F4-88FB-1B01A7718A12}"/>
+    <hyperlink ref="C147" r:id="rId146" tooltip="Abrir" xr:uid="{42A97EA2-3D08-4CFA-BAA6-4484D7AC6DC4}"/>
+    <hyperlink ref="C148" r:id="rId147" tooltip="Abrir" xr:uid="{9C7A3466-B7C2-4AD1-85EC-B31791AEBBF7}"/>
+    <hyperlink ref="C149" r:id="rId148" tooltip="Abrir" xr:uid="{C8556F2A-6C87-4E49-B261-61A691C6C723}"/>
+    <hyperlink ref="C150" r:id="rId149" tooltip="Abrir" xr:uid="{04B99F15-AA89-479D-BE8B-6723327902A0}"/>
+    <hyperlink ref="C151" r:id="rId150" tooltip="Abrir" xr:uid="{37710BB3-728A-4C05-AD34-A5E5CF34825C}"/>
+    <hyperlink ref="C152" r:id="rId151" tooltip="Abrir" xr:uid="{3697059B-F124-4870-B1AF-340AD0E28B35}"/>
+    <hyperlink ref="C153" r:id="rId152" tooltip="Abrir" xr:uid="{3A8DF666-39CA-49A8-9F47-DBA741FA4C46}"/>
+    <hyperlink ref="C154" r:id="rId153" tooltip="Abrir" xr:uid="{D5745E55-6664-4DB0-8ADC-04A5C04256F6}"/>
+    <hyperlink ref="C155" r:id="rId154" tooltip="Abrir" xr:uid="{F0E7C0E1-FB00-43D9-8111-918274FA854A}"/>
+    <hyperlink ref="C156" r:id="rId155" tooltip="Abrir" xr:uid="{E6D37C85-1A23-4E3B-8F6D-394AE160157D}"/>
+    <hyperlink ref="C157" r:id="rId156" tooltip="Abrir" xr:uid="{8FB90556-999F-4052-B7A8-6CC79E02A031}"/>
+    <hyperlink ref="C158" r:id="rId157" tooltip="Abrir" xr:uid="{B7C519DB-0B74-423E-A185-2105165CEAEF}"/>
+    <hyperlink ref="C159" r:id="rId158" tooltip="Abrir" xr:uid="{6F856B5A-4477-4CBF-A812-D4472EC0394A}"/>
+    <hyperlink ref="C160" r:id="rId159" tooltip="Abrir" xr:uid="{C0815E95-27FF-4D1D-BE32-ED3BA7D22791}"/>
+    <hyperlink ref="C161" r:id="rId160" tooltip="Abrir" xr:uid="{B05453E2-9ADF-49CF-B23C-87974009F495}"/>
+    <hyperlink ref="C162" r:id="rId161" tooltip="Abrir" xr:uid="{195828C5-7DDD-4DAE-8169-8BC4E09DA31C}"/>
+    <hyperlink ref="C163" r:id="rId162" tooltip="Abrir" xr:uid="{568069DB-D9FA-4D9A-8F8C-9FCA73706824}"/>
+    <hyperlink ref="C164" r:id="rId163" tooltip="Abrir" xr:uid="{F47C2404-CF5B-4BCE-B7BC-1B655987F7CF}"/>
+    <hyperlink ref="C165" r:id="rId164" tooltip="Abrir" xr:uid="{FE692324-A39C-4970-8D51-86E55CCEF4FF}"/>
+    <hyperlink ref="C166" r:id="rId165" tooltip="Abrir" xr:uid="{FE7FC654-8F3A-422F-A9BB-38B0170A1A31}"/>
+    <hyperlink ref="C167" r:id="rId166" tooltip="Abrir" xr:uid="{3866259F-B7FE-43DB-9F79-1AB23FEC0B64}"/>
+    <hyperlink ref="C168" r:id="rId167" tooltip="Abrir" xr:uid="{3E6CD60A-F276-47DF-A724-9A11DC2067A0}"/>
+    <hyperlink ref="C169" r:id="rId168" tooltip="Abrir" xr:uid="{0D1E58B0-81C9-4A0A-A2FC-99CB5CC0ABE9}"/>
+    <hyperlink ref="C170" r:id="rId169" tooltip="Abrir" xr:uid="{C69D2133-0C9F-4AA4-B1B7-4B7937A2BEA5}"/>
+    <hyperlink ref="C171" r:id="rId170" tooltip="Abrir" xr:uid="{599B04D6-532C-41EB-8997-951C2EF0D84B}"/>
+    <hyperlink ref="C172" r:id="rId171" tooltip="Abrir" xr:uid="{2F73D11D-1D9C-4106-AFD5-49916F923F31}"/>
+    <hyperlink ref="C173" r:id="rId172" tooltip="Abrir" xr:uid="{FD734EC7-6107-4EDB-B21F-CB02BD58C8CE}"/>
+    <hyperlink ref="C174" r:id="rId173" tooltip="Abrir" xr:uid="{E96C9226-195C-4860-BE59-CD5824026AD2}"/>
+    <hyperlink ref="C175" r:id="rId174" tooltip="Abrir" xr:uid="{FBACEAE5-C618-4083-8516-D96D1CAE6CFA}"/>
+    <hyperlink ref="C176" r:id="rId175" tooltip="Abrir" xr:uid="{67FC31E5-6FE4-4446-9D9F-D141FB35F912}"/>
+    <hyperlink ref="C177" r:id="rId176" tooltip="Abrir" xr:uid="{B8843FBB-1DC5-4F43-A3AA-52F1EC8329AC}"/>
+    <hyperlink ref="C178" r:id="rId177" tooltip="Abrir" xr:uid="{1958E26D-D211-4F60-9D85-1920D2A9EB5C}"/>
+    <hyperlink ref="C179" r:id="rId178" tooltip="Abrir" xr:uid="{173D7D82-F695-48B6-83C4-91FE2BBFC4EB}"/>
+    <hyperlink ref="C180" r:id="rId179" tooltip="Abrir" xr:uid="{DFDF3A95-1FC8-4D67-AF73-7CC059545495}"/>
+    <hyperlink ref="C181" r:id="rId180" tooltip="Abrir" xr:uid="{CAFFE8E8-67BC-4433-A6F2-50BC6BB1FAAD}"/>
+    <hyperlink ref="C182" r:id="rId181" tooltip="Abrir" xr:uid="{D782F85F-8697-4E16-AB57-9B6F5C3B9901}"/>
+    <hyperlink ref="C183" r:id="rId182" tooltip="Abrir" xr:uid="{B5659503-B08E-4911-A5D8-BB4C31EAA51D}"/>
+    <hyperlink ref="C184" r:id="rId183" tooltip="Abrir" xr:uid="{893A584D-0654-43B7-B4EA-5B8948EAD73F}"/>
+    <hyperlink ref="C185" r:id="rId184" tooltip="Abrir" xr:uid="{2D7DFDA4-5677-4826-8CEC-D4E3DABBF1E0}"/>
+    <hyperlink ref="C186" r:id="rId185" tooltip="Abrir" xr:uid="{916F935D-73E5-48A1-B9D2-936EEB591A1C}"/>
+    <hyperlink ref="C187" r:id="rId186" tooltip="Abrir" xr:uid="{FAC75B97-5893-406E-9F4C-3477BE57DC86}"/>
+    <hyperlink ref="C188" r:id="rId187" tooltip="Abrir" xr:uid="{D6A2B562-6538-43F1-818F-A2F574520D48}"/>
+    <hyperlink ref="C189" r:id="rId188" tooltip="Abrir" xr:uid="{EC277AE1-D1CF-4823-9B5A-AA7A91288026}"/>
+    <hyperlink ref="C190" r:id="rId189" tooltip="Abrir" xr:uid="{437F676D-8320-4A17-8ADC-C02B3DE74B09}"/>
+    <hyperlink ref="C191" r:id="rId190" tooltip="Abrir" xr:uid="{99122A71-205E-4A2D-AD6E-CBE83B823FAD}"/>
+    <hyperlink ref="C192" r:id="rId191" tooltip="Abrir" xr:uid="{C29600E1-E06C-4867-9C37-F22851B4F001}"/>
+    <hyperlink ref="C193" r:id="rId192" tooltip="Abrir" xr:uid="{BD6D3555-9C71-4DF8-897D-1B0191DCEE72}"/>
+    <hyperlink ref="C194" r:id="rId193" tooltip="Abrir" xr:uid="{074E8A97-B14F-48FD-A980-E60F45794B97}"/>
+    <hyperlink ref="C195" r:id="rId194" tooltip="Abrir" xr:uid="{2CD1189D-F317-4F42-9FD0-5CBDF2AF0ADC}"/>
+    <hyperlink ref="C196" r:id="rId195" tooltip="Abrir" xr:uid="{DDDDE5FB-6576-4AE5-99EC-DBD1AB7C2D67}"/>
+    <hyperlink ref="C197" r:id="rId196" tooltip="Abrir" xr:uid="{A33061AF-D0F6-4C9A-8EB7-47E7C9A5913C}"/>
+    <hyperlink ref="C198" r:id="rId197" tooltip="Abrir" xr:uid="{A69F9A99-67CA-4879-A079-1F5000ACF1F1}"/>
+    <hyperlink ref="C199" r:id="rId198" tooltip="Abrir" xr:uid="{283821A5-1C57-45FF-909D-F9C831CE948A}"/>
+    <hyperlink ref="C200" r:id="rId199" tooltip="Abrir" xr:uid="{6308C880-D332-481F-BC31-94065D6E1B0A}"/>
+    <hyperlink ref="C201" r:id="rId200" tooltip="Abrir" xr:uid="{B55A8279-5A62-4C7A-BDCB-CF74677A8072}"/>
+    <hyperlink ref="C202" r:id="rId201" tooltip="Abrir" xr:uid="{A6AEB560-0D9C-4CFF-AB79-31D8543E5A88}"/>
+    <hyperlink ref="C203" r:id="rId202" tooltip="Abrir" xr:uid="{BDA00AD7-75DF-44F4-8AEB-C941119B7CE2}"/>
+    <hyperlink ref="C204" r:id="rId203" tooltip="Abrir" xr:uid="{07046257-C0F3-4036-A6CE-4C4A95026451}"/>
+    <hyperlink ref="C205" r:id="rId204" tooltip="Abrir" xr:uid="{E8306AAF-F8BC-4323-9D2C-D5DEAE74DE12}"/>
+    <hyperlink ref="C206" r:id="rId205" tooltip="Abrir" xr:uid="{B6A9C81F-6D48-4222-8A05-7730546F3924}"/>
+    <hyperlink ref="C207" r:id="rId206" tooltip="Abrir" xr:uid="{CA55A807-2A0F-479A-996F-5893E20C58DF}"/>
+    <hyperlink ref="C208" r:id="rId207" tooltip="Abrir" xr:uid="{782DB9C7-372A-43FC-9266-29250A8C08EA}"/>
+    <hyperlink ref="C209" r:id="rId208" tooltip="Abrir" xr:uid="{73D5838E-3FCC-4261-8820-262E743448F7}"/>
+    <hyperlink ref="C210" r:id="rId209" tooltip="Abrir" xr:uid="{1E6EF3E5-63D3-4D4F-8B37-2E24097A38DF}"/>
+    <hyperlink ref="C211" r:id="rId210" tooltip="Abrir" xr:uid="{79161300-4F2F-407F-ADD7-4371527FAB98}"/>
+    <hyperlink ref="C212" r:id="rId211" tooltip="Abrir" xr:uid="{CD95ED90-7A36-49AD-BAB5-67A554F03FAA}"/>
+    <hyperlink ref="C213" r:id="rId212" tooltip="Abrir" xr:uid="{8A7EFAEC-8AFB-48D7-A236-E8F9E941C2FB}"/>
+    <hyperlink ref="C214" r:id="rId213" tooltip="Abrir" xr:uid="{844D2216-2EF4-43C6-91D3-C1367E761348}"/>
+    <hyperlink ref="C215" r:id="rId214" tooltip="Abrir" xr:uid="{51694D88-6ABA-4BE5-9DF2-C5E5DA952115}"/>
+    <hyperlink ref="C216" r:id="rId215" tooltip="Abrir" xr:uid="{C4B820CB-FC44-4BAE-9988-414A46A922AE}"/>
+    <hyperlink ref="C217" r:id="rId216" tooltip="Abrir" xr:uid="{81F596E0-8562-41D0-B1F1-B1367FC5943D}"/>
+    <hyperlink ref="C218" r:id="rId217" tooltip="Abrir" xr:uid="{1BBC640B-9D20-4AD1-9B1F-C6A644ECFF8A}"/>
+    <hyperlink ref="C219" r:id="rId218" tooltip="Abrir" xr:uid="{F53C8580-A4F2-4BB6-998D-AB92C7CB64E6}"/>
+    <hyperlink ref="C220" r:id="rId219" tooltip="Abrir" xr:uid="{567B9A7D-2661-460E-A2B2-56E6F26B6F20}"/>
+    <hyperlink ref="C221" r:id="rId220" tooltip="Abrir" xr:uid="{33049EF1-3740-48B9-A95B-CF490126BB0E}"/>
+    <hyperlink ref="C222" r:id="rId221" tooltip="Abrir" xr:uid="{2B64BE9E-5B53-40E0-B132-2E4F29FB8D56}"/>
+    <hyperlink ref="C223" r:id="rId222" tooltip="Abrir" xr:uid="{696E176A-C214-49D4-B4A1-21FD3CC6C6E1}"/>
+    <hyperlink ref="C224" r:id="rId223" tooltip="Abrir" xr:uid="{81B70D5A-E1B5-42CA-98C6-3D1211E4DD31}"/>
+    <hyperlink ref="C225" r:id="rId224" tooltip="Abrir" xr:uid="{7D084DB4-4B4E-4D73-892F-75ACC42005A1}"/>
+    <hyperlink ref="C226" r:id="rId225" tooltip="Abrir" xr:uid="{C225124D-3622-44A0-9594-D9CEA1BA4459}"/>
+    <hyperlink ref="C227" r:id="rId226" tooltip="Abrir" xr:uid="{204F19D0-CEB2-4E76-9B40-1AC5C5BDD8BD}"/>
+    <hyperlink ref="C228" r:id="rId227" tooltip="Abrir" xr:uid="{0384EF75-BA4C-4D32-AA58-C59F4B2A3165}"/>
+    <hyperlink ref="C229" r:id="rId228" tooltip="Abrir" xr:uid="{C7E95DC8-43FC-47F5-9945-7D958CB46971}"/>
+    <hyperlink ref="C230" r:id="rId229" tooltip="Abrir" xr:uid="{1ED133FD-9EEF-4FBC-9CC2-CAA5A764B8D5}"/>
+    <hyperlink ref="C231" r:id="rId230" tooltip="Abrir" xr:uid="{D2AEB781-B637-479A-A17F-F458732F7301}"/>
+    <hyperlink ref="C232" r:id="rId231" tooltip="Abrir" xr:uid="{B7EE181A-FC11-4C06-88C8-9285A8E94B21}"/>
+    <hyperlink ref="C233" r:id="rId232" tooltip="Abrir" xr:uid="{213C3993-D133-490A-84A5-88BB24569855}"/>
+    <hyperlink ref="C234" r:id="rId233" tooltip="Abrir" xr:uid="{4CAEFCFD-E629-458A-92EE-A5387DFEF703}"/>
+    <hyperlink ref="C235" r:id="rId234" tooltip="Abrir" xr:uid="{EA004A07-BA9C-4B39-AD0F-1AA98DB63040}"/>
+    <hyperlink ref="C236" r:id="rId235" tooltip="Abrir" xr:uid="{0C01CA75-0A25-4BA0-8B19-82D104F602A9}"/>
+    <hyperlink ref="C237" r:id="rId236" tooltip="Abrir" xr:uid="{796BF976-798C-4CF1-8471-98E6334092F9}"/>
+    <hyperlink ref="C238" r:id="rId237" tooltip="Abrir" xr:uid="{E461AAF2-06F6-4204-A74C-C5A8714C1B58}"/>
+    <hyperlink ref="C239" r:id="rId238" tooltip="Abrir" xr:uid="{FC643378-5E02-49AD-9414-213A20AB3FC6}"/>
+    <hyperlink ref="C240" r:id="rId239" tooltip="Abrir" xr:uid="{3908978C-5A98-4879-BA0C-74B0EE25DC04}"/>
+    <hyperlink ref="C241" r:id="rId240" tooltip="Abrir" xr:uid="{B0DF147B-AB6E-480F-811E-B32C8717B3B2}"/>
+    <hyperlink ref="C242" r:id="rId241" tooltip="Abrir" xr:uid="{34A29930-E9EE-45AE-B033-2F59D0F355AE}"/>
+    <hyperlink ref="C243" r:id="rId242" tooltip="Abrir" xr:uid="{D6FD579F-CA18-4B2F-9D2A-5327FDED8F9F}"/>
+    <hyperlink ref="C244" r:id="rId243" tooltip="Abrir" xr:uid="{3082CC12-A8E2-43E2-9F14-BFC7AC37F495}"/>
+    <hyperlink ref="C245" r:id="rId244" tooltip="Abrir" xr:uid="{345689FE-B65D-42A8-B2E9-3331D7A6747F}"/>
+    <hyperlink ref="C246" r:id="rId245" tooltip="Abrir" xr:uid="{E0AED3A2-36A7-48E2-9739-C5565AAB5681}"/>
+    <hyperlink ref="C247" r:id="rId246" tooltip="Abrir" xr:uid="{715B0602-F1DC-47CA-B1B4-7BACF9DA0333}"/>
+    <hyperlink ref="C248" r:id="rId247" tooltip="Abrir" xr:uid="{F3CDFC6C-EEF6-4ED6-BE0F-1DECA6DE92AC}"/>
+    <hyperlink ref="C249" r:id="rId248" tooltip="Abrir" xr:uid="{9A47E7F2-94F6-4DC7-A756-B1080939122A}"/>
+    <hyperlink ref="C250" r:id="rId249" tooltip="Abrir" xr:uid="{60BCDA21-3D57-4234-8FB9-C6F4B49ABDDA}"/>
+    <hyperlink ref="C251" r:id="rId250" tooltip="Abrir" xr:uid="{93847316-040F-4CA0-BA3A-91A8CFBDBE90}"/>
+    <hyperlink ref="C252" r:id="rId251" tooltip="Abrir" xr:uid="{887C6171-AE98-47D8-8126-20924E34DDA3}"/>
+    <hyperlink ref="C253" r:id="rId252" tooltip="Abrir" xr:uid="{948779B9-6DB4-4B30-AE56-10C0A47EEDA6}"/>
+    <hyperlink ref="C254" r:id="rId253" tooltip="Abrir" xr:uid="{9F3CB872-FA2E-4A3B-B799-E73D575322CC}"/>
+    <hyperlink ref="C255" r:id="rId254" tooltip="Abrir" xr:uid="{5F6661B7-8CED-48C5-8B4C-D6A4B8402D3F}"/>
+    <hyperlink ref="C256" r:id="rId255" tooltip="Abrir" xr:uid="{97ED9DF7-C855-40ED-A365-748CDE3F05D7}"/>
+    <hyperlink ref="C257" r:id="rId256" tooltip="Abrir" xr:uid="{FD4678E3-4933-4629-BBE7-75B87730B578}"/>
+    <hyperlink ref="C258" r:id="rId257" tooltip="Abrir" xr:uid="{0192A509-E12B-485F-9D4E-509F58C28E7E}"/>
+    <hyperlink ref="C259" r:id="rId258" tooltip="Abrir" xr:uid="{3F89F624-8D1E-4389-8216-B0BFD0DAD461}"/>
+    <hyperlink ref="C260" r:id="rId259" tooltip="Abrir" xr:uid="{B8DE4BC5-DC25-4DC4-B716-51A3B9EB0148}"/>
+    <hyperlink ref="C261" r:id="rId260" tooltip="Abrir" xr:uid="{3CC8642A-4F53-4583-9AAA-40B251E5CACF}"/>
+    <hyperlink ref="C262" r:id="rId261" tooltip="Abrir" xr:uid="{ECCCA446-C345-494D-A7CD-DA6E28EBCE05}"/>
+    <hyperlink ref="C263" r:id="rId262" tooltip="Abrir" xr:uid="{5DF73127-2857-41ED-AC51-79C0138C5AFF}"/>
+    <hyperlink ref="C264" r:id="rId263" tooltip="Abrir" xr:uid="{C19642DB-E3E7-4D1F-B418-62AA6E477E10}"/>
+    <hyperlink ref="C265" r:id="rId264" tooltip="Abrir" xr:uid="{CDDEDF41-C066-45F2-B5CA-6BAAA0A452E0}"/>
+    <hyperlink ref="C266" r:id="rId265" tooltip="Abrir" xr:uid="{46905025-B2BC-40B7-918D-DA7BF39B500E}"/>
+    <hyperlink ref="C267" r:id="rId266" tooltip="Abrir" xr:uid="{20BC615D-2D1C-438B-84FD-89090BB8602F}"/>
+    <hyperlink ref="C268" r:id="rId267" tooltip="Abrir" xr:uid="{F7391345-5F61-4788-8555-C50E3AC07317}"/>
+    <hyperlink ref="C269" r:id="rId268" tooltip="Abrir" xr:uid="{A33E7635-A5A8-4086-9C7F-62C49BC64BF6}"/>
+    <hyperlink ref="C270" r:id="rId269" tooltip="Abrir" xr:uid="{00D010DB-C837-4116-95F7-05B718048B59}"/>
+    <hyperlink ref="C271" r:id="rId270" tooltip="Abrir" xr:uid="{B091EE06-B933-43BD-A477-EEA89240AA9B}"/>
+    <hyperlink ref="C272" r:id="rId271" tooltip="Abrir" xr:uid="{9D3A5322-FBE5-47E9-BB1D-54031CCD8531}"/>
+    <hyperlink ref="C273" r:id="rId272" tooltip="Abrir" xr:uid="{A0076736-3A5C-4CAB-B309-A155D6D24FA5}"/>
+    <hyperlink ref="C274" r:id="rId273" tooltip="Abrir" xr:uid="{E528B6CF-0366-40C9-B71E-AFAF415C26FA}"/>
+    <hyperlink ref="C275" r:id="rId274" tooltip="Abrir" xr:uid="{F50C86D3-51AB-49E1-AB17-7BA0CA05D261}"/>
+    <hyperlink ref="C276" r:id="rId275" tooltip="Abrir" xr:uid="{D6927397-BDF0-4A53-9422-E62926DF9425}"/>
+    <hyperlink ref="C277" r:id="rId276" tooltip="Abrir" xr:uid="{9F246806-FE96-4CD2-A88C-A8A216D092AC}"/>
+    <hyperlink ref="C278" r:id="rId277" tooltip="Abrir" xr:uid="{0470B392-E00B-45FB-A0DC-7017483C351F}"/>
+    <hyperlink ref="C279" r:id="rId278" tooltip="Abrir" xr:uid="{997F5ACE-3E87-4EED-B689-C72E11AB0AAC}"/>
+    <hyperlink ref="C280" r:id="rId279" tooltip="Abrir" xr:uid="{A549FDC2-4123-4287-95BB-D885831EEC19}"/>
+    <hyperlink ref="C281" r:id="rId280" tooltip="Abrir" xr:uid="{859B0056-7A25-4C4E-BCD0-38E7D5B454B7}"/>
+    <hyperlink ref="C282" r:id="rId281" tooltip="Abrir" xr:uid="{AA9BDA44-AAD0-411D-9C65-41370BA629CB}"/>
+    <hyperlink ref="C283" r:id="rId282" tooltip="Abrir" xr:uid="{DD098C42-5EA2-4215-88E4-2B00ACA4EEA6}"/>
+    <hyperlink ref="C284" r:id="rId283" tooltip="Abrir" xr:uid="{83801290-33FA-4B21-9D83-8A6063C715FB}"/>
+    <hyperlink ref="C285" r:id="rId284" tooltip="Abrir" xr:uid="{E6955148-A219-4254-A030-41EBCEC91E09}"/>
+    <hyperlink ref="C286" r:id="rId285" tooltip="Abrir" xr:uid="{70CF01EF-56C9-4C7E-AA9B-0AC388D2E606}"/>
+    <hyperlink ref="C287" r:id="rId286" tooltip="Abrir" xr:uid="{6F2F5A9D-A661-43B0-81D1-259316D78CDD}"/>
+    <hyperlink ref="C288" r:id="rId287" tooltip="Abrir" xr:uid="{851612C3-1858-4729-A173-04719B6EF4C0}"/>
+    <hyperlink ref="C289" r:id="rId288" tooltip="Abrir" xr:uid="{3309420C-506A-4B4C-BA7C-DC021D78CFAA}"/>
+    <hyperlink ref="C290" r:id="rId289" tooltip="Abrir" xr:uid="{BB58E4F8-BCA0-417F-A84B-ECCD8F53FEFE}"/>
+    <hyperlink ref="C291" r:id="rId290" tooltip="Abrir" xr:uid="{3770E030-D027-407F-85F5-C5284875C426}"/>
+    <hyperlink ref="C292" r:id="rId291" tooltip="Abrir" xr:uid="{F2DD9D0B-90BB-4A0B-AED1-9AAF73657CB6}"/>
+    <hyperlink ref="C293" r:id="rId292" tooltip="Abrir" xr:uid="{DF2CA785-2945-4B11-A0E3-E40821DC9880}"/>
+    <hyperlink ref="C294" r:id="rId293" tooltip="Abrir" xr:uid="{65B74930-B66D-433D-8B09-E5E7F4050B32}"/>
+    <hyperlink ref="C295" r:id="rId294" tooltip="Abrir" xr:uid="{9780112D-C8ED-4ED3-9278-9396B8BEF6E5}"/>
+    <hyperlink ref="C296" r:id="rId295" tooltip="Abrir" xr:uid="{B3A9E90A-3E79-4044-A436-23C0BF545948}"/>
+    <hyperlink ref="C297" r:id="rId296" tooltip="Abrir" xr:uid="{918EC3EE-E08E-44D2-98C7-8F6041607554}"/>
+    <hyperlink ref="C298" r:id="rId297" tooltip="Abrir" xr:uid="{A0C6909F-6654-4FAE-B3B5-965D5BD3328E}"/>
+    <hyperlink ref="C299" r:id="rId298" tooltip="Abrir" xr:uid="{FF8546F2-3D91-4A2B-BEFC-549DDE4ED609}"/>
+    <hyperlink ref="C300" r:id="rId299" tooltip="Abrir" xr:uid="{E4221E95-9D60-4AAD-9C06-65BAC01F47BB}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/vagas_gupy_inhire.xlsx
+++ b/vagas_gupy_inhire.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\busca-vagas-gupy-inhire-empregare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38D2F935-FA30-4E33-A148-E8785DC4039F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80BBFD1F-DEB0-45FE-B891-DA9BF9952350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D9ECBEF7-877E-4976-BCF7-3E4086BE0B02}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7B89FA0F-EF4E-4911-A5C4-77D29DB5884D}"/>
   </bookViews>
   <sheets>
     <sheet name="Vagas" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'InHire novas (fora da lista)'!$A$1:$C$300</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Presenca por Empresa'!$A$1:$F$251</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vagas!$A$1:$M$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vagas!$A$1:$N$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="684">
+  <si>
+    <t>Situação</t>
+  </si>
   <si>
     <t>Empresa</t>
   </si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t>Detectada em</t>
+  </si>
+  <si>
+    <t>Não Aplicada</t>
   </si>
   <si>
     <t>Bradesco</t>
@@ -2469,25 +2475,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80741ED5-37EE-444E-80DB-69DB0F3A1767}">
-  <dimension ref="A1:M47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B1E613-4CE6-444B-8C62-2BA4FD02DCE6}">
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="4" width="26.77734375" customWidth="1"/>
-    <col min="5" max="5" width="46.77734375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" customWidth="1"/>
-    <col min="8" max="8" width="42.77734375" customWidth="1"/>
-    <col min="9" max="9" width="22.77734375" customWidth="1"/>
-    <col min="10" max="11" width="12.77734375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="38.77734375" style="6" customWidth="1"/>
-    <col min="13" max="13" width="14.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
+    <col min="5" max="5" width="26.77734375" customWidth="1"/>
+    <col min="6" max="6" width="46.77734375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" customWidth="1"/>
+    <col min="9" max="9" width="42.77734375" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
+    <col min="11" max="12" width="12.77734375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="38.77734375" style="6" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2500,10 +2507,10 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -2515,1734 +2522,1880 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f04c4-0b85-7fc6-9ff3-e3913efb6dee","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1">
+        <v>46199</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f04c4-0b85-7fc6-9ff3-e3913efb6dee","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="F3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f61fe-9ebb-7da2-bfff-849044c53887","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="1">
+        <v>46217</v>
+      </c>
+      <c r="L3" s="1">
+        <v>46254</v>
+      </c>
+      <c r="N3" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f0450-997e-7321-8d0a-43f1e4904f73","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1">
         <v>46199</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L4" s="1">
         <v>46235</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <f>HYPERLINK("https://cadastra.gupy.io/job/eyJqb2JJZCI6MTE1ODgwNTUsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="1">
+        <v>46209</v>
+      </c>
+      <c r="L5" s="1">
+        <v>46269</v>
+      </c>
+      <c r="N5" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="2" t="str">
+        <f>HYPERLINK("https://azzasfashion.gupy.io/job/eyJqb2JJZCI6MTE3NDQ5NTIsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="1">
+        <v>46226</v>
+      </c>
+      <c r="L6" s="1">
+        <v>46265</v>
+      </c>
+      <c r="N6" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <f>HYPERLINK("https://contabilizei.inhire.app/vagas/fc71c615-507b-4b02-89d0-d7033b2e6b0e/contabilidade-analista-contabil-junior-crc-ativo","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="2" t="str">
+        <f>HYPERLINK("https://contabilizei.inhire.app/vagas/84646b9e-d831-43a2-9db0-a04434ea0206/expert-analista-de-operacoes-financeiras-junior-notas-fiscais-lp","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <f>HYPERLINK("https://contabilizei.inhire.app/vagas/dd76143f-464a-4d3c-8330-3c84ee76763c/expert-assistente-de-operacoes-financeiras-notas-fiscais","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="2" t="str">
+        <f>HYPERLINK("https://kpmg.inhire.app/vagas/c3466ef7-e680-4a1f-ab1a-a5934b46f5a6/consultor-junior-de-finance-transformation","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3111","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3023","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3157","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3145","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J14" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3155","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3125","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3120","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3133","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J18" t="s">
+        <v>73</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="2" t="str">
+        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3117","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v164426","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J20" t="s">
+        <v>77</v>
+      </c>
+      <c r="N20" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" t="s">
+        <v>81</v>
+      </c>
+      <c r="I21" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v169050","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J21" t="s">
+        <v>77</v>
+      </c>
+      <c r="N21" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v165398","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J22" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v169048","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J23" t="s">
+        <v>85</v>
+      </c>
+      <c r="N23" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" t="s">
+        <v>81</v>
+      </c>
+      <c r="I24" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v168595","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J24" t="s">
+        <v>85</v>
+      </c>
+      <c r="N24" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s">
+        <v>81</v>
+      </c>
+      <c r="I25" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v166320","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J25" t="s">
+        <v>87</v>
+      </c>
+      <c r="N25" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s">
+        <v>81</v>
+      </c>
+      <c r="I26" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v113757","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J26" t="s">
+        <v>89</v>
+      </c>
+      <c r="N26" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s">
+        <v>81</v>
+      </c>
+      <c r="I27" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v173041","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J27" t="s">
+        <v>91</v>
+      </c>
+      <c r="N27" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v169653","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J28" t="s">
+        <v>92</v>
+      </c>
+      <c r="N28" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" t="s">
+        <v>81</v>
+      </c>
+      <c r="I29" s="2" t="str">
+        <f>HYPERLINK("https://www.empregare.com/v171830","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J29" t="s">
+        <v>95</v>
+      </c>
+      <c r="N29" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f8f6b-6fa0-7757-9317-55bba394b4a2","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J30" t="s">
+        <v>97</v>
+      </c>
+      <c r="K30" s="1">
+        <v>46226</v>
+      </c>
+      <c r="L30" s="1">
+        <v>46252</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f392d-a65e-7b17-b749-1dacdc327e86","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J31" t="s">
+        <v>100</v>
+      </c>
+      <c r="K31" s="1">
+        <v>46209</v>
+      </c>
+      <c r="L31" s="1">
+        <v>46248</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N31" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G32" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f3c8f-8b57-70da-ac66-f889339cbc2c","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J32" t="s">
+        <v>100</v>
+      </c>
+      <c r="K32" s="1">
+        <v>46210</v>
+      </c>
+      <c r="L32" s="1">
+        <v>46248</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f391e-aa19-7a00-af4b-3dcbacec87eb","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J33" t="s">
+        <v>100</v>
+      </c>
+      <c r="K33" s="1">
+        <v>46209</v>
+      </c>
+      <c r="L33" s="1">
+        <v>46248</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f3902-d79d-7371-96e3-c2db2622cf05","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J34" t="s">
+        <v>100</v>
+      </c>
+      <c r="K34" s="1">
+        <v>46209</v>
+      </c>
+      <c r="L34" s="1">
+        <v>46248</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N34" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f3881-fc6b-745e-b3ce-70e58c958163","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J35" t="s">
+        <v>100</v>
+      </c>
+      <c r="K35" s="1">
+        <v>46209</v>
+      </c>
+      <c r="L35" s="1">
+        <v>46248</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f6101-e8af-7fca-8ac5-0591234d7c6a","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J36" t="s">
+        <v>107</v>
+      </c>
+      <c r="K36" s="1">
+        <v>46217</v>
+      </c>
+      <c r="L36" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N36" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" t="s">
+        <v>99</v>
+      </c>
+      <c r="H37" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019fa3df-0b51-7795-af50-cd2c042d9e4c","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K37" s="1">
+        <v>46230</v>
+      </c>
+      <c r="L37" s="1">
+        <v>46274</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f700a-0322-7e5a-b209-25d33b304523","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J38" t="s">
+        <v>109</v>
+      </c>
+      <c r="K38" s="1">
+        <v>46220</v>
+      </c>
+      <c r="L38" s="1">
+        <v>46274</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G39" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="1">
+      <c r="H39" t="s">
+        <v>115</v>
+      </c>
+      <c r="I39" s="2" t="str">
+        <f>HYPERLINK("https://app.eureca.me/vagas/019f226b-9654-76cc-94fb-f1cb74f39da2","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J39" t="s">
+        <v>113</v>
+      </c>
+      <c r="K39" s="1">
+        <v>46205</v>
+      </c>
+      <c r="L39" s="1">
+        <v>46241</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="N39" s="1">
         <v>46232</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f61fe-9ebb-7da2-bfff-849044c53887","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="1">
-        <v>46217</v>
-      </c>
-      <c r="K3" s="1">
-        <v>46254</v>
-      </c>
-      <c r="M3" s="1">
+      <c r="B40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" t="s">
+        <v>34</v>
+      </c>
+      <c r="I40" s="2" t="str">
+        <f>HYPERLINK("https://vagasconexaotalentos.gupy.io/job/eyJqb2JJZCI6MTE3ODM2NjIsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J40" t="s">
+        <v>117</v>
+      </c>
+      <c r="K40" s="1">
+        <v>46227</v>
+      </c>
+      <c r="L40" s="1">
+        <v>46241</v>
+      </c>
+      <c r="N40" s="1">
         <v>46232</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f0450-997e-7321-8d0a-43f1e4904f73","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="1">
-        <v>46199</v>
-      </c>
-      <c r="K4" s="1">
-        <v>46235</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="1">
+      <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" t="s">
+        <v>120</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G41" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" t="s">
+        <v>34</v>
+      </c>
+      <c r="I41" s="2" t="str">
+        <f>HYPERLINK("https://vagas-infnet.gupy.io/job/eyJqb2JJZCI6MTExMDY4MDksInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J41" t="s">
+        <v>119</v>
+      </c>
+      <c r="K41" s="1">
+        <v>46120</v>
+      </c>
+      <c r="L41" s="1">
+        <v>46290</v>
+      </c>
+      <c r="N41" s="1">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G42" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="2" t="str">
+        <f>HYPERLINK("https://estagio-e-trainee-infnet.gupy.io/job/eyJqb2JJZCI6MTEyMDcwODMsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J42" t="s">
+        <v>122</v>
+      </c>
+      <c r="K42" s="1">
+        <v>46140</v>
+      </c>
+      <c r="L42" s="1">
+        <v>46290</v>
+      </c>
+      <c r="N42" s="1">
         <v>46232</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6" t="s">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2" t="str">
-        <f>HYPERLINK("https://cadastra.gupy.io/job/eyJqb2JJZCI6MTE1ODgwNTUsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="D43" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G43" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="1">
-        <v>46209</v>
-      </c>
-      <c r="K5" s="1">
-        <v>46269</v>
-      </c>
-      <c r="M5" s="1">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="H43" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I43" s="2" t="str">
+        <f>HYPERLINK("https://conexaotalentos.gupy.io/job/eyJqb2JJZCI6MTE2MzU1OTYsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J43" t="s">
+        <v>124</v>
+      </c>
+      <c r="K43" s="1">
+        <v>46220</v>
+      </c>
+      <c r="L43" s="1">
+        <v>46251</v>
+      </c>
+      <c r="N43" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="2" t="str">
-        <f>HYPERLINK("https://azzasfashion.gupy.io/job/eyJqb2JJZCI6MTE3NDQ5NTIsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="1">
-        <v>46226</v>
-      </c>
-      <c r="K6" s="1">
-        <v>46265</v>
-      </c>
-      <c r="M6" s="1">
+      <c r="F44" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G44" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" t="s">
+        <v>129</v>
+      </c>
+      <c r="I44" s="2" t="str">
+        <f>HYPERLINK("https://magnumtires.gupy.io/job/eyJqb2JJZCI6MTE2MDUyODUsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J44" t="s">
+        <v>126</v>
+      </c>
+      <c r="K44" s="1">
+        <v>46227</v>
+      </c>
+      <c r="L44" s="1">
+        <v>46271</v>
+      </c>
+      <c r="N44" s="1">
         <v>46232</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="6" t="s">
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" t="s">
+        <v>132</v>
+      </c>
+      <c r="I45" s="2" t="str">
+        <f>HYPERLINK("https://redeamericas.gupy.io/job/eyJqb2JJZCI6MTE2NjY5MTUsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J45" t="s">
+        <v>130</v>
+      </c>
+      <c r="K45" s="1">
+        <v>46227</v>
+      </c>
+      <c r="L45" s="1">
+        <v>46279</v>
+      </c>
+      <c r="N45" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" t="s">
         <v>42</v>
       </c>
-      <c r="F7" t="s">
+      <c r="D46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" t="s">
         <v>43</v>
       </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="2" t="str">
-        <f>HYPERLINK("https://contabilizei.inhire.app/vagas/fc71c615-507b-4b02-89d0-d7033b2e6b0e/contabilidade-analista-contabil-junior-crc-ativo","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="1">
+      <c r="F46" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G46" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="2" t="str">
+        <f>HYPERLINK("https://gruposaga.inhire.app/vagas/835a22cd-2faa-4221-8ad6-b91f03f96e24/assistente-de-controladoria","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J46" t="s">
+        <v>133</v>
+      </c>
+      <c r="N46" s="1">
         <v>46232</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="6" t="s">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" t="s">
         <v>45</v>
       </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="2" t="str">
-        <f>HYPERLINK("https://contabilizei.inhire.app/vagas/84646b9e-d831-43a2-9db0-a04434ea0206/expert-analista-de-operacoes-financeiras-junior-notas-fiscais-lp","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="1">
+      <c r="H47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I47" s="2" t="str">
+        <f>HYPERLINK("https://nomadglobal.inhire.app/vagas/b457098d-6aee-49dd-bd00-d6469ade5b8d/analista-de-operacoes-i-cartao-de-credito","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+      <c r="J47" t="s">
+        <v>135</v>
+      </c>
+      <c r="N47" s="1">
         <v>46232</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="2" t="str">
-        <f>HYPERLINK("https://contabilizei.inhire.app/vagas/dd76143f-464a-4d3c-8330-3c84ee76763c/expert-assistente-de-operacoes-financeiras-notas-fiscais","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="2" t="str">
-        <f>HYPERLINK("https://kpmg.inhire.app/vagas/c3466ef7-e680-4a1f-ab1a-a5934b46f5a6/consultor-junior-de-finance-transformation","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3111","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3023","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3157","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I13" t="s">
-        <v>59</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3145","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I14" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M14" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3155","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M15" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3125","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M16" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" t="s">
-        <v>55</v>
-      </c>
-      <c r="H17" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3120","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I17" t="s">
-        <v>69</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M17" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>55</v>
-      </c>
-      <c r="H18" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3133","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I18" t="s">
-        <v>71</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M18" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="2" t="str">
-        <f>HYPERLINK("https://www.atsglobe.com/candidate-ui/#/login/candidacy-registration/3117","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M19" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v164426","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I20" t="s">
-        <v>75</v>
-      </c>
-      <c r="M20" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v169050","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I21" t="s">
-        <v>75</v>
-      </c>
-      <c r="M21" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v165398","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I22" t="s">
-        <v>81</v>
-      </c>
-      <c r="M22" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v169048","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I23" t="s">
-        <v>83</v>
-      </c>
-      <c r="M23" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v168595","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I24" t="s">
-        <v>83</v>
-      </c>
-      <c r="M24" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" t="s">
-        <v>79</v>
-      </c>
-      <c r="H25" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v166320","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I25" t="s">
-        <v>85</v>
-      </c>
-      <c r="M25" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v113757","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I26" t="s">
-        <v>87</v>
-      </c>
-      <c r="M26" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" t="s">
-        <v>79</v>
-      </c>
-      <c r="H27" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v173041","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I27" t="s">
-        <v>89</v>
-      </c>
-      <c r="M27" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" t="s">
-        <v>92</v>
-      </c>
-      <c r="H28" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v169653","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I28" t="s">
-        <v>90</v>
-      </c>
-      <c r="M28" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" t="s">
-        <v>79</v>
-      </c>
-      <c r="H29" s="2" t="str">
-        <f>HYPERLINK("https://www.empregare.com/v171830","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I29" t="s">
-        <v>93</v>
-      </c>
-      <c r="M29" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f8f6b-6fa0-7757-9317-55bba394b4a2","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I30" t="s">
-        <v>95</v>
-      </c>
-      <c r="J30" s="1">
-        <v>46226</v>
-      </c>
-      <c r="K30" s="1">
-        <v>46252</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M30" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F31" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f392d-a65e-7b17-b749-1dacdc327e86","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I31" t="s">
-        <v>98</v>
-      </c>
-      <c r="J31" s="1">
-        <v>46209</v>
-      </c>
-      <c r="K31" s="1">
-        <v>46248</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M31" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f3c8f-8b57-70da-ac66-f889339cbc2c","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I32" t="s">
-        <v>98</v>
-      </c>
-      <c r="J32" s="1">
-        <v>46210</v>
-      </c>
-      <c r="K32" s="1">
-        <v>46248</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f391e-aa19-7a00-af4b-3dcbacec87eb","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J33" s="1">
-        <v>46209</v>
-      </c>
-      <c r="K33" s="1">
-        <v>46248</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f3902-d79d-7371-96e3-c2db2622cf05","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I34" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" s="1">
-        <v>46209</v>
-      </c>
-      <c r="K34" s="1">
-        <v>46248</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M34" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F35" t="s">
-        <v>100</v>
-      </c>
-      <c r="G35" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f3881-fc6b-745e-b3ce-70e58c958163","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I35" t="s">
-        <v>98</v>
-      </c>
-      <c r="J35" s="1">
-        <v>46209</v>
-      </c>
-      <c r="K35" s="1">
-        <v>46248</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M35" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" t="s">
-        <v>100</v>
-      </c>
-      <c r="G36" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f6101-e8af-7fca-8ac5-0591234d7c6a","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I36" t="s">
-        <v>105</v>
-      </c>
-      <c r="J36" s="1">
-        <v>46217</v>
-      </c>
-      <c r="K36" s="1">
-        <v>46266</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M36" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>107</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G37" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019fa3df-0b51-7795-af50-cd2c042d9e4c","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I37" t="s">
-        <v>107</v>
-      </c>
-      <c r="J37" s="1">
-        <v>46230</v>
-      </c>
-      <c r="K37" s="1">
-        <v>46274</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M37" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" t="s">
-        <v>109</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F38" t="s">
-        <v>97</v>
-      </c>
-      <c r="G38" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f700a-0322-7e5a-b209-25d33b304523","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I38" t="s">
-        <v>107</v>
-      </c>
-      <c r="J38" s="1">
-        <v>46220</v>
-      </c>
-      <c r="K38" s="1">
-        <v>46274</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F39" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" t="s">
-        <v>113</v>
-      </c>
-      <c r="H39" s="2" t="str">
-        <f>HYPERLINK("https://app.eureca.me/vagas/019f226b-9654-76cc-94fb-f1cb74f39da2","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I39" t="s">
-        <v>111</v>
-      </c>
-      <c r="J39" s="1">
-        <v>46205</v>
-      </c>
-      <c r="K39" s="1">
-        <v>46241</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="M39" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" t="s">
-        <v>51</v>
-      </c>
-      <c r="D40" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-      <c r="G40" t="s">
-        <v>32</v>
-      </c>
-      <c r="H40" s="2" t="str">
-        <f>HYPERLINK("https://vagasconexaotalentos.gupy.io/job/eyJqb2JJZCI6MTE3ODM2NjIsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I40" t="s">
-        <v>115</v>
-      </c>
-      <c r="J40" s="1">
-        <v>46227</v>
-      </c>
-      <c r="K40" s="1">
-        <v>46241</v>
-      </c>
-      <c r="M40" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>117</v>
-      </c>
-      <c r="B41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" t="s">
-        <v>51</v>
-      </c>
-      <c r="D41" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F41" t="s">
-        <v>31</v>
-      </c>
-      <c r="G41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H41" s="2" t="str">
-        <f>HYPERLINK("https://vagas-infnet.gupy.io/job/eyJqb2JJZCI6MTExMDY4MDksInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I41" t="s">
-        <v>117</v>
-      </c>
-      <c r="J41" s="1">
-        <v>46120</v>
-      </c>
-      <c r="K41" s="1">
-        <v>46290</v>
-      </c>
-      <c r="M41" s="1">
-        <v>46219</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>120</v>
-      </c>
-      <c r="B42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" t="s">
-        <v>51</v>
-      </c>
-      <c r="D42" t="s">
-        <v>109</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F42" t="s">
-        <v>31</v>
-      </c>
-      <c r="G42" t="s">
-        <v>32</v>
-      </c>
-      <c r="H42" s="2" t="str">
-        <f>HYPERLINK("https://estagio-e-trainee-infnet.gupy.io/job/eyJqb2JJZCI6MTEyMDcwODMsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J42" s="1">
-        <v>46140</v>
-      </c>
-      <c r="K42" s="1">
-        <v>46290</v>
-      </c>
-      <c r="M42" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" t="s">
-        <v>41</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F43" t="s">
-        <v>31</v>
-      </c>
-      <c r="G43" t="s">
-        <v>32</v>
-      </c>
-      <c r="H43" s="2" t="str">
-        <f>HYPERLINK("https://conexaotalentos.gupy.io/job/eyJqb2JJZCI6MTE2MzU1OTYsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I43" t="s">
-        <v>122</v>
-      </c>
-      <c r="J43" s="1">
-        <v>46220</v>
-      </c>
-      <c r="K43" s="1">
-        <v>46251</v>
-      </c>
-      <c r="M43" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>124</v>
-      </c>
-      <c r="B44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F44" t="s">
-        <v>126</v>
-      </c>
-      <c r="G44" t="s">
-        <v>127</v>
-      </c>
-      <c r="H44" s="2" t="str">
-        <f>HYPERLINK("https://magnumtires.gupy.io/job/eyJqb2JJZCI6MTE2MDUyODUsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I44" t="s">
-        <v>124</v>
-      </c>
-      <c r="J44" s="1">
-        <v>46227</v>
-      </c>
-      <c r="K44" s="1">
-        <v>46271</v>
-      </c>
-      <c r="M44" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>128</v>
-      </c>
-      <c r="B45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" t="s">
-        <v>41</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G45" t="s">
-        <v>130</v>
-      </c>
-      <c r="H45" s="2" t="str">
-        <f>HYPERLINK("https://redeamericas.gupy.io/job/eyJqb2JJZCI6MTE2NjY5MTUsInNvdXJjZSI6Imd1cHlfcG9ydGFsIn0=?jobBoardSource=gupy_portal","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I45" t="s">
-        <v>128</v>
-      </c>
-      <c r="J45" s="1">
-        <v>46227</v>
-      </c>
-      <c r="K45" s="1">
-        <v>46279</v>
-      </c>
-      <c r="M45" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>131</v>
-      </c>
-      <c r="B46" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" t="s">
-        <v>51</v>
-      </c>
-      <c r="D46" t="s">
-        <v>41</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F46" t="s">
-        <v>43</v>
-      </c>
-      <c r="G46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H46" s="2" t="str">
-        <f>HYPERLINK("https://gruposaga.inhire.app/vagas/835a22cd-2faa-4221-8ad6-b91f03f96e24/assistente-de-controladoria","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I46" t="s">
-        <v>131</v>
-      </c>
-      <c r="M46" s="1">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" t="s">
-        <v>41</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F47" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" t="s">
-        <v>44</v>
-      </c>
-      <c r="H47" s="2" t="str">
-        <f>HYPERLINK("https://nomadglobal.inhire.app/vagas/b457098d-6aee-49dd-bd00-d6469ade5b8d/analista-de-operacoes-i-cartao-de-credito","Abrir")</f>
-        <v>Abrir</v>
-      </c>
-      <c r="I47" t="s">
-        <v>133</v>
-      </c>
-      <c r="M47" s="1">
-        <v>46232</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M47" xr:uid="{80741ED5-37EE-444E-80DB-69DB0F3A1767}"/>
+  <autoFilter ref="A1:N47" xr:uid="{65B1E613-4CE6-444B-8C62-2BA4FD02DCE6}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Situação inválida" error="Escolha uma das opções: Aplicada / Não Aplicada / Desenvolvendo currículo" sqref="A2:A47" xr:uid="{8DBE26DB-3E38-404D-A2A7-B548C0C19F2E}">
+      <formula1>"Aplicada,Não Aplicada,Desenvolvendo currículo"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99546847-F3FF-40DE-A671-68D37A1DA027}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D9CBEC-74A4-4930-A659-D7BD4FFB362E}">
   <dimension ref="A1:F251"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4256,30 +4409,30 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="str">
         <f>HYPERLINK("https://aarin.inhire.app/vagas","Abrir")</f>
@@ -4291,10 +4444,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>HYPERLINK("https://abaco.gupy.io/","Abrir")</f>
@@ -4303,10 +4456,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="str">
         <f>HYPERLINK("https://adyen.inhire.app/vagas","Abrir")</f>
@@ -4318,10 +4471,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="str">
         <f>HYPERLINK("https://afya.gupy.io/","Abrir")</f>
@@ -4330,10 +4483,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="str">
         <f>HYPERLINK("https://afya.gupy.io/","Abrir")</f>
@@ -4342,10 +4495,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="str">
         <f>HYPERLINK("https://agencia.gupy.io/","Abrir")</f>
@@ -4354,10 +4507,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="str">
         <f>HYPERLINK("https://agencia.gupy.io/","Abrir")</f>
@@ -4366,10 +4519,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="str">
         <f>HYPERLINK("https://eyxo.inhire.app/vagas","Abrir")</f>
@@ -4381,10 +4534,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="str">
         <f>HYPERLINK("https://agilize.gupy.io/","Abrir")</f>
@@ -4393,10 +4546,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2" t="str">
         <f>HYPERLINK("https://agriness.gupy.io/","Abrir")</f>
@@ -4405,10 +4558,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2" t="str">
         <f>HYPERLINK("https://akross.gupy.io/","Abrir")</f>
@@ -4417,10 +4570,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="str">
         <f>HYPERLINK("https://brasilparalelo.inhire.app/vagas","Abrir")</f>
@@ -4432,17 +4585,17 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2" t="str">
         <f>HYPERLINK("https://algar.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E14" s="2" t="str">
         <f>HYPERLINK("https://algar.inhire.app/vagas","Abrir")</f>
@@ -4454,10 +4607,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2" t="str">
         <f>HYPERLINK("https://alicerce.inhire.app/vagas","Abrir")</f>
@@ -4469,10 +4622,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>HYPERLINK("https://alpargatas.gupy.io/","Abrir")</f>
@@ -4481,10 +4634,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2" t="str">
         <f>HYPERLINK("https://alterdata.gupy.io/","Abrir")</f>
@@ -4493,10 +4646,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2" t="str">
         <f>HYPERLINK("https://alun.inhire.app/vagas","Abrir")</f>
@@ -4508,10 +4661,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="2" t="str">
         <f>HYPERLINK("https://amaro.inhire.app/vagas","Abrir")</f>
@@ -4523,10 +4676,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="str">
         <f>HYPERLINK("https://ambev.gupy.io/","Abrir")</f>
@@ -4535,10 +4688,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E21" s="2" t="str">
         <f>HYPERLINK("https://amcom.inhire.app/vagas","Abrir")</f>
@@ -4550,10 +4703,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2" t="str">
         <f>HYPERLINK("https://ame.gupy.io/","Abrir")</f>
@@ -4562,10 +4715,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2" t="str">
         <f>HYPERLINK("https://amparosaude.gupy.io/","Abrir")</f>
@@ -4574,10 +4727,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="2" t="str">
         <f>HYPERLINK("https://rpo-abinbev.inhire.app/vagas","Abrir")</f>
@@ -4589,10 +4742,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E25" s="2" t="str">
         <f>HYPERLINK("https://arquivei.inhire.app/vagas","Abrir")</f>
@@ -4604,10 +4757,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="str">
         <f>HYPERLINK("https://asaplog.gupy.io/","Abrir")</f>
@@ -4616,10 +4769,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="str">
         <f>HYPERLINK("https://atento.gupy.io/","Abrir")</f>
@@ -4628,10 +4781,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>HYPERLINK("https://ativa.gupy.io/","Abrir")</f>
@@ -4640,10 +4793,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E29" s="2" t="str">
         <f>HYPERLINK("https://auvotecnologia.inhire.app/vagas","Abrir")</f>
@@ -4655,10 +4808,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30" s="2" t="str">
         <f>HYPERLINK("https://avenue.inhire.app/vagas","Abrir")</f>
@@ -4670,10 +4823,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E31" s="2" t="str">
         <f>HYPERLINK("https://telavita.inhire.app/vagas","Abrir")</f>
@@ -4685,10 +4838,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32" s="2" t="str">
         <f>HYPERLINK("https://avivatec.inhire.app/vagas","Abrir")</f>
@@ -4700,10 +4853,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C33" s="2" t="str">
         <f>HYPERLINK("https://bancobmg.gupy.io/","Abrir")</f>
@@ -4712,10 +4865,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34" s="2" t="str">
         <f>HYPERLINK("https://votorantim.inhire.app/vagas","Abrir")</f>
@@ -4727,10 +4880,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="str">
         <f>HYPERLINK("https://bancodaycoval.gupy.io/","Abrir")</f>
@@ -4739,10 +4892,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C36" s="2" t="str">
         <f>HYPERLINK("https://original.gupy.io/","Abrir")</f>
@@ -4751,10 +4904,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E37" s="2" t="str">
         <f>HYPERLINK("https://bancopine.inhire.app/vagas","Abrir")</f>
@@ -4766,10 +4919,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C38" s="2" t="str">
         <f>HYPERLINK("https://bancosofisa.gupy.io/","Abrir")</f>
@@ -4778,10 +4931,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C39" s="2" t="str">
         <f>HYPERLINK("https://yamaha.gupy.io/","Abrir")</f>
@@ -4790,10 +4943,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="str">
         <f>HYPERLINK("https://bancorbras.gupy.io/","Abrir")</f>
@@ -4802,10 +4955,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E41" s="2" t="str">
         <f>HYPERLINK("https://cardapioweb.inhire.app/vagas","Abrir")</f>
@@ -4817,17 +4970,17 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C42" s="2" t="str">
         <f>HYPERLINK("https://bemobi.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E42" s="2" t="str">
         <f>HYPERLINK("https://bemobi.inhire.app/vagas","Abrir")</f>
@@ -4839,10 +4992,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E43" s="2" t="str">
         <f>HYPERLINK("https://bionexo.inhire.app/vagas","Abrir")</f>
@@ -4854,10 +5007,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="2" t="str">
         <f>HYPERLINK("https://boavista.gupy.io/","Abrir")</f>
@@ -4866,10 +5019,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E45" s="2" t="str">
         <f>HYPERLINK("https://bradesco.inhire.app/vagas","Abrir")</f>
@@ -4881,10 +5034,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C46" s="2" t="str">
         <f>HYPERLINK("https://brasilprev.gupy.io/","Abrir")</f>
@@ -4893,10 +5046,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E47" s="2" t="str">
         <f>HYPERLINK("https://brqdigitalsolutions.inhire.app/vagas","Abrir")</f>
@@ -4908,10 +5061,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C48" s="2" t="str">
         <f>HYPERLINK("https://burgerking.gupy.io/","Abrir")</f>
@@ -4920,10 +5073,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E49" s="2" t="str">
         <f>HYPERLINK("https://willbank.inhire.app/vagas","Abrir")</f>
@@ -4935,10 +5088,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C50" s="2" t="str">
         <f>HYPERLINK("https://cabonnet.gupy.io/","Abrir")</f>
@@ -4947,10 +5100,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C51" s="2" t="str">
         <f>HYPERLINK("https://cadastra.gupy.io/","Abrir")</f>
@@ -4959,10 +5112,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E52" s="2" t="str">
         <f>HYPERLINK("https://cadmus.inhire.app/vagas","Abrir")</f>
@@ -4974,10 +5127,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C53" s="2" t="str">
         <f>HYPERLINK("https://caju.gupy.io/","Abrir")</f>
@@ -4986,10 +5139,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E54" s="2" t="str">
         <f>HYPERLINK("https://cerc.inhire.app/vagas","Abrir")</f>
@@ -5001,10 +5154,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E55" s="2" t="str">
         <f>HYPERLINK("https://grupocentral.inhire.app/vagas","Abrir")</f>
@@ -5016,10 +5169,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C56" s="2" t="str">
         <f>HYPERLINK("https://cesar.gupy.io/","Abrir")</f>
@@ -5028,10 +5181,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C57" s="2" t="str">
         <f>HYPERLINK("https://ciahering.gupy.io/","Abrir")</f>
@@ -5040,10 +5193,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E58" s="2" t="str">
         <f>HYPERLINK("https://cielo.inhire.app/vagas","Abrir")</f>
@@ -5055,10 +5208,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C59" s="2" t="str">
         <f>HYPERLINK("https://clearsale.gupy.io/","Abrir")</f>
@@ -5067,10 +5220,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C60" s="2" t="str">
         <f>HYPERLINK("https://clearsale.gupy.io/","Abrir")</f>
@@ -5079,17 +5232,17 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C61" s="2" t="str">
         <f>HYPERLINK("https://clickbus.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E61" s="2" t="str">
         <f>HYPERLINK("https://clickbus.inhire.app/vagas","Abrir")</f>
@@ -5101,10 +5254,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E62" s="2" t="str">
         <f>HYPERLINK("https://cobli.inhire.app/vagas","Abrir")</f>
@@ -5116,17 +5269,17 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C63" s="2" t="str">
         <f>HYPERLINK("https://cogna.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E63" s="2" t="str">
         <f>HYPERLINK("https://cogna.inhire.app/vagas","Abrir")</f>
@@ -5138,10 +5291,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C64" s="2" t="str">
         <f>HYPERLINK("https://conductor.gupy.io/","Abrir")</f>
@@ -5150,10 +5303,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C65" s="2" t="str">
         <f>HYPERLINK("https://conexia.gupy.io/","Abrir")</f>
@@ -5162,10 +5315,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C66" s="2" t="str">
         <f>HYPERLINK("https://confitec.gupy.io/","Abrir")</f>
@@ -5174,10 +5327,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C67" s="2" t="str">
         <f>HYPERLINK("https://conquer.gupy.io/","Abrir")</f>
@@ -5186,10 +5339,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E68" s="2" t="str">
         <f>HYPERLINK("https://rpo-contasimples.inhire.app/vagas","Abrir")</f>
@@ -5201,10 +5354,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E69" s="2" t="str">
         <f>HYPERLINK("https://contabilizei.inhire.app/vagas","Abrir")</f>
@@ -5216,17 +5369,17 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C70" s="2" t="str">
         <f>HYPERLINK("https://convenia.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E70" s="2" t="str">
         <f>HYPERLINK("https://convenia.inhire.app/vagas","Abrir")</f>
@@ -5238,10 +5391,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E71" s="2" t="str">
         <f>HYPERLINK("https://cora.inhire.app/vagas","Abrir")</f>
@@ -5253,10 +5406,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C72" s="2" t="str">
         <f>HYPERLINK("https://corebiz.gupy.io/","Abrir")</f>
@@ -5265,10 +5418,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C73" s="2" t="str">
         <f>HYPERLINK("https://cortex.gupy.io/","Abrir")</f>
@@ -5277,17 +5430,17 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C74" s="2" t="str">
         <f>HYPERLINK("https://creditas.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E74" s="2" t="str">
         <f>HYPERLINK("https://creditas.inhire.app/vagas","Abrir")</f>
@@ -5299,10 +5452,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C75" s="2" t="str">
         <f>HYPERLINK("https://cruzeirodosuleducacional.gupy.io/","Abrir")</f>
@@ -5311,10 +5464,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E76" s="2" t="str">
         <f>HYPERLINK("https://csptecnologia.inhire.app/vagas","Abrir")</f>
@@ -5326,17 +5479,17 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C77" s="2" t="str">
         <f>HYPERLINK("https://csu.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E77" s="2" t="str">
         <f>HYPERLINK("https://csu.inhire.app/vagas","Abrir")</f>
@@ -5348,10 +5501,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E78" s="2" t="str">
         <f>HYPERLINK("https://cubos.inhire.app/vagas","Abrir")</f>
@@ -5363,10 +5516,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C79" s="2" t="str">
         <f>HYPERLINK("https://cvccorp.gupy.io/","Abrir")</f>
@@ -5375,17 +5528,17 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2" t="str">
         <f>HYPERLINK("https://dafiti.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E80" s="2" t="str">
         <f>HYPERLINK("https://dafiti.inhire.app/vagas","Abrir")</f>
@@ -5397,10 +5550,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E81" s="2" t="str">
         <f>HYPERLINK("https://db1.inhire.app/vagas","Abrir")</f>
@@ -5412,10 +5565,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E82" s="2" t="str">
         <f>HYPERLINK("https://deal.inhire.app/vagas","Abrir")</f>
@@ -5427,10 +5580,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E83" s="2" t="str">
         <f>HYPERLINK("https://frete.inhire.app/vagas","Abrir")</f>
@@ -5442,10 +5595,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C84" s="2" t="str">
         <f>HYPERLINK("https://deliverymuch.gupy.io/","Abrir")</f>
@@ -5454,10 +5607,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C85" s="2" t="str">
         <f>HYPERLINK("https://digio.gupy.io/","Abrir")</f>
@@ -5466,10 +5619,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E86" s="2" t="str">
         <f>HYPERLINK("https://digix.inhire.app/vagas","Abrir")</f>
@@ -5481,17 +5634,17 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C87" s="2" t="str">
         <f>HYPERLINK("https://dock.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E87" s="2" t="str">
         <f>HYPERLINK("https://dock.inhire.app/vagas","Abrir")</f>
@@ -5503,10 +5656,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C88" s="2" t="str">
         <f>HYPERLINK("https://docket.gupy.io/","Abrir")</f>
@@ -5515,10 +5668,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E89" s="2" t="str">
         <f>HYPERLINK("https://dotgroup.inhire.app/vagas","Abrir")</f>
@@ -5530,10 +5683,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C90" s="2" t="str">
         <f>HYPERLINK("https://dotz.gupy.io/","Abrir")</f>
@@ -5542,10 +5695,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E91" s="2" t="str">
         <f>HYPERLINK("https://dtidigital.inhire.app/vagas","Abrir")</f>
@@ -5557,10 +5710,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D92" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E92" s="2" t="str">
         <f>HYPERLINK("https://ecore.inhire.app/vagas","Abrir")</f>
@@ -5572,10 +5725,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E93" s="2" t="str">
         <f>HYPERLINK("https://ebanx.inhire.app/vagas","Abrir")</f>
@@ -5587,10 +5740,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C94" s="2" t="str">
         <f>HYPERLINK("https://econet.gupy.io/","Abrir")</f>
@@ -5599,10 +5752,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E95" s="2" t="str">
         <f>HYPERLINK("https://edenred.inhire.app/vagas","Abrir")</f>
@@ -5614,10 +5767,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E96" s="2" t="str">
         <f>HYPERLINK("https://elogroup.inhire.app/vagas","Abrir")</f>
@@ -5629,10 +5782,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D97" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E97" s="2" t="str">
         <f>HYPERLINK("https://enjoei.inhire.app/vagas","Abrir")</f>
@@ -5644,10 +5797,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E98" s="2" t="str">
         <f>HYPERLINK("https://tegra.inhire.app/vagas","Abrir")</f>
@@ -5659,10 +5812,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C99" s="2" t="str">
         <f>HYPERLINK("https://evino.gupy.io/","Abrir")</f>
@@ -5671,10 +5824,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E100" s="2" t="str">
         <f>HYPERLINK("https://exati.inhire.app/vagas","Abrir")</f>
@@ -5686,10 +5839,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E101" s="2" t="str">
         <f>HYPERLINK("https://extremegroup.inhire.app/vagas","Abrir")</f>
@@ -5701,10 +5854,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E102" s="2" t="str">
         <f>HYPERLINK("https://falconi.inhire.app/vagas","Abrir")</f>
@@ -5716,10 +5869,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C103" s="2" t="str">
         <f>HYPERLINK("https://fastshop.gupy.io/","Abrir")</f>
@@ -5728,10 +5881,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E104" s="2" t="str">
         <f>HYPERLINK("https://fbiz.inhire.app/vagas","Abrir")</f>
@@ -5743,17 +5896,17 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C105" s="2" t="str">
         <f>HYPERLINK("https://fcamara.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E105" s="2" t="str">
         <f>HYPERLINK("https://fcamara.inhire.app/vagas","Abrir")</f>
@@ -5765,10 +5918,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C106" s="2" t="str">
         <f>HYPERLINK("https://fitec.gupy.io/","Abrir")</f>
@@ -5777,10 +5930,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E107" s="2" t="str">
         <f>HYPERLINK("https://flash.inhire.app/vagas","Abrir")</f>
@@ -5792,10 +5945,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C108" s="2" t="str">
         <f>HYPERLINK("https://fortlev.gupy.io/","Abrir")</f>
@@ -5804,17 +5957,17 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C109" s="2" t="str">
         <f>HYPERLINK("https://gamersclub.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E109" s="2" t="str">
         <f>HYPERLINK("https://residclub.inhire.app/vagas","Abrir")</f>
@@ -5826,10 +5979,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E110" s="2" t="str">
         <f>HYPERLINK("https://gauge.inhire.app/vagas","Abrir")</f>
@@ -5841,10 +5994,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C111" s="2" t="str">
         <f>HYPERLINK("https://gavb.gupy.io/","Abrir")</f>
@@ -5853,10 +6006,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C112" s="2" t="str">
         <f>HYPERLINK("https://genial.gupy.io/","Abrir")</f>
@@ -5865,10 +6018,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E113" s="2" t="str">
         <f>HYPERLINK("https://gerdau.inhire.app/vagas","Abrir")</f>
@@ -5880,10 +6033,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C114" s="2" t="str">
         <f>HYPERLINK("https://globalhitss.gupy.io/","Abrir")</f>
@@ -5892,10 +6045,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C115" s="2" t="str">
         <f>HYPERLINK("https://gpa.gupy.io/","Abrir")</f>
@@ -5904,17 +6057,17 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C116" s="2" t="str">
         <f>HYPERLINK("https://grupoboticario.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E116" s="2" t="str">
         <f>HYPERLINK("https://grupoboticario.inhire.app/vagas","Abrir")</f>
@@ -5926,10 +6079,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C117" s="2" t="str">
         <f>HYPERLINK("https://fcamara.gupy.io/","Abrir")</f>
@@ -5938,10 +6091,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C118" s="2" t="str">
         <f>HYPERLINK("https://grupomag.gupy.io/","Abrir")</f>
@@ -5950,10 +6103,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D119" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E119" s="2" t="str">
         <f>HYPERLINK("https://harpia.inhire.app/vagas","Abrir")</f>
@@ -5965,10 +6118,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C120" s="2" t="str">
         <f>HYPERLINK("https://hbsis.gupy.io/","Abrir")</f>
@@ -5977,10 +6130,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C121" s="2" t="str">
         <f>HYPERLINK("https://hdiseguros.gupy.io/","Abrir")</f>
@@ -5989,10 +6142,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C122" s="2" t="str">
         <f>HYPERLINK("https://hering.gupy.io/","Abrir")</f>
@@ -6001,10 +6154,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D123" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E123" s="2" t="str">
         <f>HYPERLINK("https://platformbuilders.inhire.app/vagas","Abrir")</f>
@@ -6016,10 +6169,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E124" s="2" t="str">
         <f>HYPERLINK("https://sharepeoplehub.inhire.app/vagas","Abrir")</f>
@@ -6031,10 +6184,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E125" s="2" t="str">
         <f>HYPERLINK("https://icatuseguros.inhire.app/vagas","Abrir")</f>
@@ -6046,10 +6199,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D126" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E126" s="2" t="str">
         <f>HYPERLINK("https://idwall.inhire.app/vagas","Abrir")</f>
@@ -6061,10 +6214,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E127" s="2" t="str">
         <f>HYPERLINK("https://ifood.inhire.app/vagas","Abrir")</f>
@@ -6076,10 +6229,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D128" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E128" s="2" t="str">
         <f>HYPERLINK("https://impulsogov.inhire.app/vagas","Abrir")</f>
@@ -6091,10 +6244,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C129" s="2" t="str">
         <f>HYPERLINK("https://inmetrics.gupy.io/","Abrir")</f>
@@ -6103,10 +6256,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E130" s="2" t="str">
         <f>HYPERLINK("https://instacarro.inhire.app/vagas","Abrir")</f>
@@ -6118,10 +6271,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E131" s="2" t="str">
         <f>HYPERLINK("https://alana.inhire.app/vagas","Abrir")</f>
@@ -6133,10 +6286,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C132" s="2" t="str">
         <f>HYPERLINK("https://intelipost.gupy.io/","Abrir")</f>
@@ -6145,10 +6298,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D133" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E133" s="2" t="str">
         <f>HYPERLINK("https://intertechne.inhire.app/vagas","Abrir")</f>
@@ -6160,10 +6313,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C134" s="2" t="str">
         <f>HYPERLINK("https://invillia.gupy.io/","Abrir")</f>
@@ -6172,10 +6325,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D135" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E135" s="2" t="str">
         <f>HYPERLINK("https://involves.inhire.app/vagas","Abrir")</f>
@@ -6187,10 +6340,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C136" s="2" t="str">
         <f>HYPERLINK("https://ishtecnologia.gupy.io/","Abrir")</f>
@@ -6199,10 +6352,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D137" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E137" s="2" t="str">
         <f>HYPERLINK("https://prizmamidia.inhire.app/vagas","Abrir")</f>
@@ -6214,10 +6367,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E138" s="2" t="str">
         <f>HYPERLINK("https://iteris.inhire.app/vagas","Abrir")</f>
@@ -6229,10 +6382,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D139" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E139" s="2" t="str">
         <f>HYPERLINK("https://mediahero.inhire.app/vagas","Abrir")</f>
@@ -6244,10 +6397,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C140" s="2" t="str">
         <f>HYPERLINK("https://konecta.gupy.io/","Abrir")</f>
@@ -6256,10 +6409,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C141" s="2" t="str">
         <f>HYPERLINK("https://kovi.gupy.io/","Abrir")</f>
@@ -6268,10 +6421,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E142" s="2" t="str">
         <f>HYPERLINK("https://kpmg.inhire.app/vagas","Abrir")</f>
@@ -6283,10 +6436,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D143" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E143" s="2" t="str">
         <f>HYPERLINK("https://labisaude.inhire.app/vagas","Abrir")</f>
@@ -6298,10 +6451,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D144" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E144" s="2" t="str">
         <f>HYPERLINK("https://lastlink.inhire.app/vagas","Abrir")</f>
@@ -6313,10 +6466,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C145" s="2" t="str">
         <f>HYPERLINK("https://leega.gupy.io/","Abrir")</f>
@@ -6325,10 +6478,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D146" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E146" s="2" t="str">
         <f>HYPERLINK("https://hh-lello.inhire.app/vagas","Abrir")</f>
@@ -6340,10 +6493,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D147" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E147" s="2" t="str">
         <f>HYPERLINK("https://linx.inhire.app/vagas","Abrir")</f>
@@ -6355,10 +6508,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E148" s="2" t="str">
         <f>HYPERLINK("https://listo.inhire.app/vagas","Abrir")</f>
@@ -6370,10 +6523,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E149" s="2" t="str">
         <f>HYPERLINK("https://livelo.inhire.app/vagas","Abrir")</f>
@@ -6385,10 +6538,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C150" s="2" t="str">
         <f>HYPERLINK("https://localiza.gupy.io/","Abrir")</f>
@@ -6397,10 +6550,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E151" s="2" t="str">
         <f>HYPERLINK("https://loft.inhire.app/vagas","Abrir")</f>
@@ -6412,10 +6565,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E152" s="2" t="str">
         <f>HYPERLINK("https://loggi.inhire.app/vagas","Abrir")</f>
@@ -6427,10 +6580,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C153" s="2" t="str">
         <f>HYPERLINK("https://lojasrenner.gupy.io/","Abrir")</f>
@@ -6439,10 +6592,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C154" s="2" t="str">
         <f>HYPERLINK("https://looqbox.gupy.io/","Abrir")</f>
@@ -6451,10 +6604,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C155" s="2" t="str">
         <f>HYPERLINK("https://m4u.gupy.io/","Abrir")</f>
@@ -6463,10 +6616,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E156" s="2" t="str">
         <f>HYPERLINK("https://magazineluiza.inhire.app/vagas","Abrir")</f>
@@ -6478,10 +6631,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E157" s="2" t="str">
         <f>HYPERLINK("https://magnasearch.inhire.app/vagas","Abrir")</f>
@@ -6493,10 +6646,10 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C158" s="2" t="str">
         <f>HYPERLINK("https://mandae.gupy.io/","Abrir")</f>
@@ -6505,10 +6658,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E159" s="2" t="str">
         <f>HYPERLINK("https://matera.inhire.app/vagas","Abrir")</f>
@@ -6520,10 +6673,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E160" s="2" t="str">
         <f>HYPERLINK("https://mazzatech.inhire.app/vagas","Abrir")</f>
@@ -6535,17 +6688,17 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C161" s="2" t="str">
         <f>HYPERLINK("https://meliuz.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D161" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E161" s="2" t="str">
         <f>HYPERLINK("https://meliuz.inhire.app/vagas","Abrir")</f>
@@ -6557,10 +6710,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E162" s="2" t="str">
         <f>HYPERLINK("https://mb.inhire.app/vagas","Abrir")</f>
@@ -6572,10 +6725,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C163" s="2" t="str">
         <f>HYPERLINK("https://mlabs.gupy.io/","Abrir")</f>
@@ -6584,10 +6737,10 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C164" s="2" t="str">
         <f>HYPERLINK("https://mobit.gupy.io/","Abrir")</f>
@@ -6596,10 +6749,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C165" s="2" t="str">
         <f>HYPERLINK("https://montreal.gupy.io/","Abrir")</f>
@@ -6608,10 +6761,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C166" s="2" t="str">
         <f>HYPERLINK("https://movida.gupy.io/","Abrir")</f>
@@ -6620,17 +6773,17 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B167" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C167" s="2" t="str">
         <f>HYPERLINK("https://mundiale.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E167" s="2" t="str">
         <f>HYPERLINK("https://mundiale.inhire.app/vagas","Abrir")</f>
@@ -6642,10 +6795,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C168" s="2" t="str">
         <f>HYPERLINK("https://mundipagg.gupy.io/","Abrir")</f>
@@ -6654,10 +6807,10 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D169" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E169" s="2" t="str">
         <f>HYPERLINK("https://mutant.inhire.app/vagas","Abrir")</f>
@@ -6669,10 +6822,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D170" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E170" s="2" t="str">
         <f>HYPERLINK("https://neogrid.inhire.app/vagas","Abrir")</f>
@@ -6684,10 +6837,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D171" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E171" s="2" t="str">
         <f>HYPERLINK("https://neoway.inhire.app/vagas","Abrir")</f>
@@ -6699,10 +6852,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D172" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E172" s="2" t="str">
         <f>HYPERLINK("https://nexaas.inhire.app/vagas","Abrir")</f>
@@ -6714,10 +6867,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B173" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C173" s="2" t="str">
         <f>HYPERLINK("https://nexxera.gupy.io/","Abrir")</f>
@@ -6726,10 +6879,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D174" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E174" s="2" t="str">
         <f>HYPERLINK("https://nibo.inhire.app/vagas","Abrir")</f>
@@ -6741,10 +6894,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C175" s="2" t="str">
         <f>HYPERLINK("https://nodis.gupy.io/","Abrir")</f>
@@ -6753,17 +6906,17 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C176" s="2" t="str">
         <f>HYPERLINK("https://novaescola.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D176" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E176" s="2" t="str">
         <f>HYPERLINK("https://escoladnc.inhire.app/vagas","Abrir")</f>
@@ -6775,10 +6928,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D177" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E177" s="2" t="str">
         <f>HYPERLINK("https://nubank.inhire.app/vagas","Abrir")</f>
@@ -6790,10 +6943,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D178" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E178" s="2" t="str">
         <f>HYPERLINK("https://nuvemshop-tiendanube.inhire.app/vagas","Abrir")</f>
@@ -6805,10 +6958,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D179" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E179" s="2" t="str">
         <f>HYPERLINK("https://objective.inhire.app/vagas","Abrir")</f>
@@ -6820,10 +6973,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E180" s="2" t="str">
         <f>HYPERLINK("https://olist.inhire.app/vagas","Abrir")</f>
@@ -6835,10 +6988,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D181" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E181" s="2" t="str">
         <f>HYPERLINK("https://openlabs.inhire.app/vagas","Abrir")</f>
@@ -6850,10 +7003,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B182" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C182" s="2" t="str">
         <f>HYPERLINK("https://openlabs.gupy.io/","Abrir")</f>
@@ -6862,10 +7015,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D183" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E183" s="2" t="str">
         <f>HYPERLINK("https://wavin.inhire.app/vagas","Abrir")</f>
@@ -6877,17 +7030,17 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C184" s="2" t="str">
         <f>HYPERLINK("https://orizon.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D184" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E184" s="2" t="str">
         <f>HYPERLINK("https://orizon.inhire.app/vagas","Abrir")</f>
@@ -6899,10 +7052,10 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C185" s="2" t="str">
         <f>HYPERLINK("https://padtec.gupy.io/","Abrir")</f>
@@ -6911,10 +7064,10 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C186" s="2" t="str">
         <f>HYPERLINK("https://pagarme.gupy.io/","Abrir")</f>
@@ -6923,10 +7076,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C187" s="2" t="str">
         <f>HYPERLINK("https://pagseguro.gupy.io/","Abrir")</f>
@@ -6935,10 +7088,10 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D188" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E188" s="2" t="str">
         <f>HYPERLINK("https://paipe.inhire.app/vagas","Abrir")</f>
@@ -6950,10 +7103,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C189" s="2" t="str">
         <f>HYPERLINK("https://passeidireto.gupy.io/","Abrir")</f>
@@ -6962,10 +7115,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C190" s="2" t="str">
         <f>HYPERLINK("https://phoebus.gupy.io/","Abrir")</f>
@@ -6974,10 +7127,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D191" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E191" s="2" t="str">
         <f>HYPERLINK("https://pitang.inhire.app/vagas","Abrir")</f>
@@ -6989,10 +7142,10 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C192" s="2" t="str">
         <f>HYPERLINK("https://pitzi.gupy.io/","Abrir")</f>
@@ -7001,10 +7154,10 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C193" s="2" t="str">
         <f>HYPERLINK("https://porto.gupy.io/","Abrir")</f>
@@ -7013,10 +7166,10 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C194" s="2" t="str">
         <f>HYPERLINK("https://positivo.gupy.io/","Abrir")</f>
@@ -7025,10 +7178,10 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D195" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E195" s="2" t="str">
         <f>HYPERLINK("https://pravaler.inhire.app/vagas","Abrir")</f>
@@ -7040,10 +7193,10 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D196" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E196" s="2" t="str">
         <f>HYPERLINK("https://radix.inhire.app/vagas","Abrir")</f>
@@ -7055,10 +7208,10 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D197" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E197" s="2" t="str">
         <f>HYPERLINK("https://rarolabs.inhire.app/vagas","Abrir")</f>
@@ -7070,10 +7223,10 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D198" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E198" s="2" t="str">
         <f>HYPERLINK("https://reclameaqui.inhire.app/vagas","Abrir")</f>
@@ -7085,10 +7238,10 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D199" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E199" s="2" t="str">
         <f>HYPERLINK("https://rnp.inhire.app/vagas","Abrir")</f>
@@ -7100,10 +7253,10 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D200" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E200" s="2" t="str">
         <f>HYPERLINK("https://remessaonline.inhire.app/vagas","Abrir")</f>
@@ -7115,10 +7268,10 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C201" s="2" t="str">
         <f>HYPERLINK("https://repassa.gupy.io/","Abrir")</f>
@@ -7127,10 +7280,10 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C202" s="2" t="str">
         <f>HYPERLINK("https://rnp.gupy.io/","Abrir")</f>
@@ -7139,17 +7292,17 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C203" s="2" t="str">
         <f>HYPERLINK("https://samsungsds.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D203" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E203" s="2" t="str">
         <f>HYPERLINK("https://samsung.inhire.app/vagas","Abrir")</f>
@@ -7161,10 +7314,10 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C204" s="2" t="str">
         <f>HYPERLINK("https://sciensa.gupy.io/","Abrir")</f>
@@ -7173,10 +7326,10 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D205" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E205" s="2" t="str">
         <f>HYPERLINK("https://semantix.inhire.app/vagas","Abrir")</f>
@@ -7188,10 +7341,10 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C206" s="2" t="str">
         <f>HYPERLINK("https://sidi.gupy.io/","Abrir")</f>
@@ -7200,10 +7353,10 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D207" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E207" s="2" t="str">
         <f>HYPERLINK("https://sidia.inhire.app/vagas","Abrir")</f>
@@ -7215,10 +7368,10 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D208" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E208" s="2" t="str">
         <f>HYPERLINK("https://skyone.inhire.app/vagas","Abrir")</f>
@@ -7230,17 +7383,17 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B209" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C209" s="2" t="str">
         <f>HYPERLINK("https://smart.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D209" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E209" s="2" t="str">
         <f>HYPERLINK("https://fitenergia.inhire.app/vagas","Abrir")</f>
@@ -7252,10 +7405,10 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B210" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C210" s="2" t="str">
         <f>HYPERLINK("https://softplan.gupy.io/","Abrir")</f>
@@ -7264,10 +7417,10 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D211" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E211" s="2" t="str">
         <f>HYPERLINK("https://solutis.inhire.app/vagas","Abrir")</f>
@@ -7279,10 +7432,10 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C212" s="2" t="str">
         <f>HYPERLINK("https://spread.gupy.io/","Abrir")</f>
@@ -7291,10 +7444,10 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C213" s="2" t="str">
         <f>HYPERLINK("https://stefanini.gupy.io/","Abrir")</f>
@@ -7303,17 +7456,17 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C214" s="2" t="str">
         <f>HYPERLINK("https://stone.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D214" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E214" s="2" t="str">
         <f>HYPERLINK("https://stone.inhire.app/vagas","Abrir")</f>
@@ -7325,10 +7478,10 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D215" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E215" s="2" t="str">
         <f>HYPERLINK("https://superlogica.inhire.app/vagas","Abrir")</f>
@@ -7340,10 +7493,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D216" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E216" s="2" t="str">
         <f>HYPERLINK("https://grupotaking.inhire.app/vagas","Abrir")</f>
@@ -7355,10 +7508,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C217" s="2" t="str">
         <f>HYPERLINK("https://targetsistemas.gupy.io/","Abrir")</f>
@@ -7367,10 +7520,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B218" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C218" s="2" t="str">
         <f>HYPERLINK("https://tecban.gupy.io/","Abrir")</f>
@@ -7379,10 +7532,10 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D219" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E219" s="2" t="str">
         <f>HYPERLINK("https://techlead.inhire.app/vagas","Abrir")</f>
@@ -7394,10 +7547,10 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C220" s="2" t="str">
         <f>HYPERLINK("https://telemont.gupy.io/","Abrir")</f>
@@ -7406,10 +7559,10 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D221" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E221" s="2" t="str">
         <f>HYPERLINK("https://tembici.inhire.app/vagas","Abrir")</f>
@@ -7421,10 +7574,10 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D222" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E222" s="2" t="str">
         <f>HYPERLINK("https://tempest.inhire.app/vagas","Abrir")</f>
@@ -7436,10 +7589,10 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B223" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C223" s="2" t="str">
         <f>HYPERLINK("https://tempo.gupy.io/","Abrir")</f>
@@ -7448,10 +7601,10 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D224" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E224" s="2" t="str">
         <f>HYPERLINK("https://tinnova.inhire.app/vagas","Abrir")</f>
@@ -7463,10 +7616,10 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C225" s="2" t="str">
         <f>HYPERLINK("https://tokiomarine.gupy.io/","Abrir")</f>
@@ -7475,10 +7628,10 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D226" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E226" s="2" t="str">
         <f>HYPERLINK("https://totvs.inhire.app/vagas","Abrir")</f>
@@ -7490,10 +7643,10 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E227" s="2" t="str">
         <f>HYPERLINK("https://bancotoyota.inhire.app/vagas","Abrir")</f>
@@ -7505,10 +7658,10 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D228" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E228" s="2" t="str">
         <f>HYPERLINK("https://tqi.inhire.app/vagas","Abrir")</f>
@@ -7520,10 +7673,10 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D229" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E229" s="2" t="str">
         <f>HYPERLINK("https://tray.inhire.app/vagas","Abrir")</f>
@@ -7535,10 +7688,10 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D230" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E230" s="2" t="str">
         <f>HYPERLINK("https://trinca.inhire.app/vagas","Abrir")</f>
@@ -7550,10 +7703,10 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B231" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C231" s="2" t="str">
         <f>HYPERLINK("https://truckpad.gupy.io/","Abrir")</f>
@@ -7562,10 +7715,10 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D232" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E232" s="2" t="str">
         <f>HYPERLINK("https://turbi.inhire.app/vagas","Abrir")</f>
@@ -7577,17 +7730,17 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B233" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C233" s="2" t="str">
         <f>HYPERLINK("https://uello.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D233" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E233" s="2" t="str">
         <f>HYPERLINK("https://hh-uello.inhire.app/vagas","Abrir")</f>
@@ -7599,10 +7752,10 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D234" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E234" s="2" t="str">
         <f>HYPERLINK("https://unico.inhire.app/vagas","Abrir")</f>
@@ -7614,10 +7767,10 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B235" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C235" s="2" t="str">
         <f>HYPERLINK("https://uol.gupy.io/","Abrir")</f>
@@ -7626,10 +7779,10 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B236" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C236" s="2" t="str">
         <f>HYPERLINK("https://uol.gupy.io/","Abrir")</f>
@@ -7638,10 +7791,10 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D237" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E237" s="2" t="str">
         <f>HYPERLINK("https://vagasconfidenciais2.inhire.app/vagas","Abrir")</f>
@@ -7653,10 +7806,10 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D238" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E238" s="2" t="str">
         <f>HYPERLINK("https://venturus.inhire.app/vagas","Abrir")</f>
@@ -7668,10 +7821,10 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B239" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C239" s="2" t="str">
         <f>HYPERLINK("https://vertem.gupy.io/","Abrir")</f>
@@ -7680,10 +7833,10 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D240" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E240" s="2" t="str">
         <f>HYPERLINK("https://vhsys.inhire.app/vagas","Abrir")</f>
@@ -7695,10 +7848,10 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B241" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C241" s="2" t="str">
         <f>HYPERLINK("https://viasoft.gupy.io/","Abrir")</f>
@@ -7707,17 +7860,17 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C242" s="2" t="str">
         <f>HYPERLINK("https://vivo.gupy.io/","Abrir")</f>
         <v>Abrir</v>
       </c>
       <c r="D242" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E242" s="2" t="str">
         <f>HYPERLINK("https://vivopcd.inhire.app/vagas","Abrir")</f>
@@ -7729,10 +7882,10 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D243" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E243" s="2" t="str">
         <f>HYPERLINK("https://warren.inhire.app/vagas","Abrir")</f>
@@ -7744,10 +7897,10 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C244" s="2" t="str">
         <f>HYPERLINK("https://webjump.gupy.io/","Abrir")</f>
@@ -7756,10 +7909,10 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B245" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C245" s="2" t="str">
         <f>HYPERLINK("https://webmotors.gupy.io/","Abrir")</f>
@@ -7768,10 +7921,10 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D246" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E246" s="2" t="str">
         <f>HYPERLINK("https://winnin.inhire.app/vagas","Abrir")</f>
@@ -7783,10 +7936,10 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B247" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C247" s="2" t="str">
         <f>HYPERLINK("https://wiz.gupy.io/","Abrir")</f>
@@ -7795,10 +7948,10 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D248" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E248" s="2" t="str">
         <f>HYPERLINK("https://toroinvestimentos.inhire.app/vagas","Abrir")</f>
@@ -7810,10 +7963,10 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B249" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C249" s="2" t="str">
         <f>HYPERLINK("https://ztech.gupy.io/","Abrir")</f>
@@ -7822,10 +7975,10 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C250" s="2" t="str">
         <f>HYPERLINK("https://zeedog.gupy.io/","Abrir")</f>
@@ -7834,10 +7987,10 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D251" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E251" s="2" t="str">
         <f>HYPERLINK("https://zup.inhire.app/vagas","Abrir")</f>
@@ -7848,13 +8001,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F251" xr:uid="{99546847-F3FF-40DE-A671-68D37A1DA027}"/>
+  <autoFilter ref="A1:F251" xr:uid="{A9D9CBEC-74A4-4930-A659-D7BD4FFB362E}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289EF377-1059-4382-B848-913FAEFD6455}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7884C5-EE35-4997-88D0-31E7A24B608D}">
   <dimension ref="A1:C300"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7865,18 +8018,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B2">
         <v>971</v>
@@ -7888,7 +8041,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B3">
         <v>356</v>
@@ -7900,7 +8053,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B4">
         <v>272</v>
@@ -7912,7 +8065,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B5">
         <v>267</v>
@@ -7924,7 +8077,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B6">
         <v>246</v>
@@ -7936,7 +8089,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B7">
         <v>229</v>
@@ -7948,7 +8101,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B8">
         <v>208</v>
@@ -7960,7 +8113,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B9">
         <v>205</v>
@@ -7972,7 +8125,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B10">
         <v>193</v>
@@ -7984,7 +8137,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B11">
         <v>180</v>
@@ -7996,7 +8149,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B12">
         <v>107</v>
@@ -8008,7 +8161,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B13">
         <v>89</v>
@@ -8020,7 +8173,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B14">
         <v>66</v>
@@ -8032,7 +8185,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B15">
         <v>66</v>
@@ -8044,7 +8197,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B16">
         <v>65</v>
@@ -8056,7 +8209,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B17">
         <v>65</v>
@@ -8068,7 +8221,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B18">
         <v>60</v>
@@ -8080,7 +8233,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B19">
         <v>52</v>
@@ -8092,7 +8245,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B20">
         <v>51</v>
@@ -8104,7 +8257,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B21">
         <v>47</v>
@@ -8116,7 +8269,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B22">
         <v>46</v>
@@ -8128,7 +8281,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B23">
         <v>46</v>
@@ -8140,7 +8293,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B24">
         <v>45</v>
@@ -8152,7 +8305,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B25">
         <v>43</v>
@@ -8164,7 +8317,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B26">
         <v>41</v>
@@ -8176,7 +8329,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B27">
         <v>39</v>
@@ -8188,7 +8341,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B28">
         <v>39</v>
@@ -8200,7 +8353,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B29">
         <v>37</v>
@@ -8212,7 +8365,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B30">
         <v>36</v>
@@ -8224,7 +8377,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B31">
         <v>36</v>
@@ -8236,7 +8389,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B32">
         <v>35</v>
@@ -8248,7 +8401,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B33">
         <v>35</v>
@@ -8260,7 +8413,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B34">
         <v>34</v>
@@ -8272,7 +8425,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -8284,7 +8437,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B36">
         <v>32</v>
@@ -8296,7 +8449,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B37">
         <v>32</v>
@@ -8308,7 +8461,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B38">
         <v>32</v>
@@ -8320,7 +8473,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B39">
         <v>31</v>
@@ -8332,7 +8485,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B40">
         <v>31</v>
@@ -8344,7 +8497,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B41">
         <v>31</v>
@@ -8356,7 +8509,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B42">
         <v>30</v>
@@ -8368,7 +8521,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B43">
         <v>30</v>
@@ -8380,7 +8533,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B44">
         <v>29</v>
@@ -8392,7 +8545,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B45">
         <v>29</v>
@@ -8404,7 +8557,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B46">
         <v>28</v>
@@ -8416,7 +8569,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B47">
         <v>28</v>
@@ -8428,7 +8581,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B48">
         <v>28</v>
@@ -8440,7 +8593,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B49">
         <v>27</v>
@@ -8452,7 +8605,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B50">
         <v>27</v>
@@ -8464,7 +8617,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B51">
         <v>26</v>
@@ -8476,7 +8629,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B52">
         <v>26</v>
@@ -8488,7 +8641,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B53">
         <v>26</v>
@@ -8500,7 +8653,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B54">
         <v>25</v>
@@ -8512,7 +8665,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B55">
         <v>25</v>
@@ -8524,7 +8677,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B56">
         <v>24</v>
@@ -8536,7 +8689,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B57">
         <v>24</v>
@@ -8548,7 +8701,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B58">
         <v>24</v>
@@ -8560,7 +8713,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B59">
         <v>23</v>
@@ -8572,7 +8725,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B60">
         <v>23</v>
@@ -8584,7 +8737,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B61">
         <v>22</v>
@@ -8596,7 +8749,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B62">
         <v>21</v>
@@ -8608,7 +8761,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B63">
         <v>21</v>
@@ -8620,7 +8773,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B64">
         <v>20</v>
@@ -8632,7 +8785,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B65">
         <v>20</v>
@@ -8644,7 +8797,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B66">
         <v>20</v>
@@ -8656,7 +8809,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B67">
         <v>20</v>
@@ -8668,7 +8821,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B68">
         <v>19</v>
@@ -8680,7 +8833,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B69">
         <v>19</v>
@@ -8692,7 +8845,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B70">
         <v>19</v>
@@ -8704,7 +8857,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B71">
         <v>18</v>
@@ -8716,7 +8869,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B72">
         <v>18</v>
@@ -8728,7 +8881,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B73">
         <v>17</v>
@@ -8740,7 +8893,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B74">
         <v>17</v>
@@ -8752,7 +8905,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B75">
         <v>17</v>
@@ -8764,7 +8917,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B76">
         <v>17</v>
@@ -8776,7 +8929,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B77">
         <v>17</v>
@@ -8788,7 +8941,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B78">
         <v>17</v>
@@ -8800,7 +8953,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B79">
         <v>17</v>
@@ -8812,7 +8965,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B80">
         <v>17</v>
@@ -8824,7 +8977,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B81">
         <v>16</v>
@@ -8836,7 +8989,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B82">
         <v>16</v>
@@ -8848,7 +9001,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B83">
         <v>16</v>
@@ -8860,7 +9013,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B84">
         <v>16</v>
@@ -8872,7 +9025,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B85">
         <v>16</v>
@@ -8884,7 +9037,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B86">
         <v>16</v>
@@ -8896,7 +9049,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B87">
         <v>16</v>
@@ -8908,7 +9061,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B88">
         <v>15</v>
@@ -8920,7 +9073,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B89">
         <v>15</v>
@@ -8932,7 +9085,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B90">
         <v>15</v>
@@ -8944,7 +9097,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B91">
         <v>15</v>
@@ -8956,7 +9109,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B92">
         <v>15</v>
@@ -8968,7 +9121,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B93">
         <v>15</v>
@@ -8980,7 +9133,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B94">
         <v>15</v>
@@ -8992,7 +9145,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B95">
         <v>14</v>
@@ -9004,7 +9157,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B96">
         <v>14</v>
@@ -9016,7 +9169,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B97">
         <v>14</v>
@@ -9028,7 +9181,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B98">
         <v>14</v>
@@ -9040,7 +9193,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B99">
         <v>14</v>
@@ -9052,7 +9205,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B100">
         <v>14</v>
@@ -9064,7 +9217,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B101">
         <v>14</v>
@@ -9076,7 +9229,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B102">
         <v>14</v>
@@ -9088,7 +9241,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B103">
         <v>13</v>
@@ -9100,7 +9253,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B104">
         <v>13</v>
@@ -9112,7 +9265,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B105">
         <v>13</v>
@@ -9124,7 +9277,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B106">
         <v>12</v>
@@ -9136,7 +9289,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B107">
         <v>12</v>
@@ -9148,7 +9301,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B108">
         <v>12</v>
@@ -9160,7 +9313,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B109">
         <v>12</v>
@@ -9172,7 +9325,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B110">
         <v>12</v>
@@ -9184,7 +9337,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B111">
         <v>12</v>
@@ -9196,7 +9349,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B112">
         <v>11</v>
@@ -9208,7 +9361,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B113">
         <v>11</v>
@@ -9220,7 +9373,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B114">
         <v>11</v>
@@ -9232,7 +9385,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B115">
         <v>11</v>
@@ -9244,7 +9397,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B116">
         <v>11</v>
@@ -9256,7 +9409,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B117">
         <v>11</v>
@@ -9268,7 +9421,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B118">
         <v>11</v>
@@ -9280,7 +9433,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B119">
         <v>11</v>
@@ -9292,7 +9445,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B120">
         <v>10</v>
@@ -9304,7 +9457,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B121">
         <v>10</v>
@@ -9316,7 +9469,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B122">
         <v>10</v>
@@ -9328,7 +9481,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B123">
         <v>10</v>
@@ -9340,7 +9493,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B124">
         <v>10</v>
@@ -9352,7 +9505,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B125">
         <v>10</v>
@@ -9364,7 +9517,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B126">
         <v>9</v>
@@ -9376,7 +9529,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B127">
         <v>9</v>
@@ -9388,7 +9541,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B128">
         <v>9</v>
@@ -9400,7 +9553,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B129">
         <v>9</v>
@@ -9412,7 +9565,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B130">
         <v>9</v>
@@ -9424,7 +9577,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B131">
         <v>9</v>
@@ -9436,7 +9589,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B132">
         <v>9</v>
@@ -9448,7 +9601,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B133">
         <v>9</v>
@@ -9460,7 +9613,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B134">
         <v>9</v>
@@ -9472,7 +9625,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B135">
         <v>9</v>
@@ -9484,7 +9637,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B136">
         <v>9</v>
@@ -9496,7 +9649,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B137">
         <v>9</v>
@@ -9508,7 +9661,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B138">
         <v>9</v>
@@ -9520,7 +9673,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B139">
         <v>9</v>
@@ -9532,7 +9685,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B140">
         <v>9</v>
@@ -9544,7 +9697,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B141">
         <v>9</v>
@@ -9556,7 +9709,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B142">
         <v>8</v>
@@ -9568,7 +9721,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B143">
         <v>8</v>
@@ -9580,7 +9733,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B144">
         <v>8</v>
@@ -9592,7 +9745,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B145">
         <v>8</v>
@@ -9604,7 +9757,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B146">
         <v>8</v>
@@ -9616,7 +9769,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B147">
         <v>8</v>
@@ -9628,7 +9781,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B148">
         <v>8</v>
@@ -9640,7 +9793,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B149">
         <v>8</v>
@@ -9652,7 +9805,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B150">
         <v>8</v>
@@ -9664,7 +9817,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B151">
         <v>8</v>
@@ -9676,7 +9829,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B152">
         <v>8</v>
@@ -9688,7 +9841,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B153">
         <v>8</v>
@@ -9700,7 +9853,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B154">
         <v>8</v>
@@ -9712,7 +9865,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B155">
         <v>8</v>
@@ -9724,7 +9877,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B156">
         <v>8</v>
@@ -9736,7 +9889,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B157">
         <v>8</v>
@@ -9748,7 +9901,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B158">
         <v>8</v>
@@ -9760,7 +9913,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B159">
         <v>8</v>
@@ -9772,7 +9925,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B160">
         <v>8</v>
@@ -9784,7 +9937,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B161">
         <v>8</v>
@@ -9796,7 +9949,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B162">
         <v>7</v>
@@ -9808,7 +9961,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B163">
         <v>7</v>
@@ -9820,7 +9973,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B164">
         <v>7</v>
@@ -9832,7 +9985,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B165">
         <v>7</v>
@@ -9844,7 +9997,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B166">
         <v>7</v>
@@ -9856,7 +10009,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B167">
         <v>7</v>
@@ -9868,7 +10021,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B168">
         <v>7</v>
@@ -9880,7 +10033,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B169">
         <v>7</v>
@@ -9892,7 +10045,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B170">
         <v>7</v>
@@ -9904,7 +10057,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B171">
         <v>7</v>
@@ -9916,7 +10069,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B172">
         <v>7</v>
@@ -9928,7 +10081,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B173">
         <v>7</v>
@@ -9940,7 +10093,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B174">
         <v>7</v>
@@ -9952,7 +10105,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B175">
         <v>7</v>
@@ -9964,7 +10117,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B176">
         <v>7</v>
@@ -9976,7 +10129,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B177">
         <v>7</v>
@@ -9988,7 +10141,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B178">
         <v>7</v>
@@ -10000,7 +10153,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B179">
         <v>7</v>
@@ -10012,7 +10165,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B180">
         <v>7</v>
@@ -10024,7 +10177,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B181">
         <v>7</v>
@@ -10036,7 +10189,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B182">
         <v>7</v>
@@ -10048,7 +10201,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B183">
         <v>7</v>
@@ -10060,7 +10213,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B184">
         <v>7</v>
@@ -10072,7 +10225,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B185">
         <v>7</v>
@@ -10084,7 +10237,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B186">
         <v>7</v>
@@ -10096,7 +10249,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B187">
         <v>6</v>
@@ -10108,7 +10261,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B188">
         <v>6</v>
@@ -10120,7 +10273,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B189">
         <v>6</v>
@@ -10132,7 +10285,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B190">
         <v>6</v>
@@ -10144,7 +10297,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B191">
         <v>6</v>
@@ -10156,7 +10309,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B192">
         <v>6</v>
@@ -10168,7 +10321,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B193">
         <v>6</v>
@@ -10180,7 +10333,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B194">
         <v>6</v>
@@ -10192,7 +10345,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B195">
         <v>6</v>
@@ -10204,7 +10357,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B196">
         <v>6</v>
@@ -10216,7 +10369,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B197">
         <v>6</v>
@@ -10228,7 +10381,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B198">
         <v>6</v>
@@ -10240,7 +10393,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B199">
         <v>5</v>
@@ -10252,7 +10405,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B200">
         <v>5</v>
@@ -10264,7 +10417,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B201">
         <v>5</v>
@@ -10276,7 +10429,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B202">
         <v>5</v>
@@ -10288,7 +10441,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B203">
         <v>5</v>
@@ -10300,7 +10453,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B204">
         <v>5</v>
@@ -10312,7 +10465,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B205">
         <v>5</v>
@@ -10324,7 +10477,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B206">
         <v>5</v>
@@ -10336,7 +10489,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B207">
         <v>5</v>
@@ -10348,7 +10501,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B208">
         <v>5</v>
@@ -10360,7 +10513,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B209">
         <v>5</v>
@@ -10372,7 +10525,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B210">
         <v>5</v>
@@ -10384,7 +10537,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B211">
         <v>5</v>
@@ -10396,7 +10549,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B212">
         <v>5</v>
@@ -10408,7 +10561,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B213">
         <v>5</v>
@@ -10420,7 +10573,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B214">
         <v>5</v>
@@ -10432,7 +10585,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B215">
         <v>4</v>
@@ -10444,7 +10597,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B216">
         <v>4</v>
@@ -10456,7 +10609,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B217">
         <v>4</v>
@@ -10468,7 +10621,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B218">
         <v>4</v>
@@ -10480,7 +10633,7 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B219">
         <v>4</v>
@@ -10492,7 +10645,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B220">
         <v>4</v>
@@ -10504,7 +10657,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B221">
         <v>4</v>
@@ -10516,7 +10669,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B222">
         <v>4</v>
@@ -10528,7 +10681,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B223">
         <v>4</v>
@@ -10540,7 +10693,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B224">
         <v>4</v>
@@ -10552,7 +10705,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B225">
         <v>4</v>
@@ -10564,7 +10717,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B226">
         <v>4</v>
@@ -10576,7 +10729,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B227">
         <v>4</v>
@@ -10588,7 +10741,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B228">
         <v>4</v>
@@ -10600,7 +10753,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B229">
         <v>4</v>
@@ -10612,7 +10765,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B230">
         <v>4</v>
@@ -10624,7 +10777,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B231">
         <v>3</v>
@@ -10636,7 +10789,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B232">
         <v>3</v>
@@ -10648,7 +10801,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B233">
         <v>3</v>
@@ -10660,7 +10813,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B234">
         <v>3</v>
@@ -10672,7 +10825,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B235">
         <v>3</v>
@@ -10684,7 +10837,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B236">
         <v>3</v>
@@ -10696,7 +10849,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B237">
         <v>3</v>
@@ -10708,7 +10861,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B238">
         <v>3</v>
@@ -10720,7 +10873,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B239">
         <v>3</v>
@@ -10732,7 +10885,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B240">
         <v>3</v>
@@ -10744,7 +10897,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B241">
         <v>3</v>
@@ -10756,7 +10909,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B242">
         <v>3</v>
@@ -10768,7 +10921,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B243">
         <v>3</v>
@@ -10780,7 +10933,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B244">
         <v>3</v>
@@ -10792,7 +10945,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B245">
         <v>3</v>
@@ -10804,7 +10957,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B246">
         <v>3</v>
@@ -10816,7 +10969,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B247">
         <v>3</v>
@@ -10828,7 +10981,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B248">
         <v>3</v>
@@ -10840,7 +10993,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B249">
         <v>2</v>
@@ -10852,7 +11005,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B250">
         <v>2</v>
@@ -10864,7 +11017,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B251">
         <v>2</v>
@@ -10876,7 +11029,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B252">
         <v>2</v>
@@ -10888,7 +11041,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B253">
         <v>2</v>
@@ -10900,7 +11053,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B254">
         <v>2</v>
@@ -10912,7 +11065,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B255">
         <v>2</v>
@@ -10924,7 +11077,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B256">
         <v>2</v>
@@ -10936,7 +11089,7 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B257">
         <v>2</v>
@@ -10948,7 +11101,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B258">
         <v>2</v>
@@ -10960,7 +11113,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B259">
         <v>2</v>
@@ -10972,7 +11125,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B260">
         <v>2</v>
@@ -10984,7 +11137,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B261">
         <v>2</v>
@@ -10996,7 +11149,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B262">
         <v>2</v>
@@ -11008,7 +11161,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B263">
         <v>2</v>
@@ -11020,7 +11173,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B264">
         <v>2</v>
@@ -11032,7 +11185,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B265">
         <v>2</v>
@@ -11044,7 +11197,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B266">
         <v>2</v>
@@ -11056,7 +11209,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B267">
         <v>2</v>
@@ -11068,7 +11221,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B268">
         <v>2</v>
@@ -11080,7 +11233,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B269">
         <v>2</v>
@@ -11092,7 +11245,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B270">
         <v>2</v>
@@ -11104,7 +11257,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B271">
         <v>2</v>
@@ -11116,7 +11269,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B272">
         <v>2</v>
@@ -11128,7 +11281,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B273">
         <v>2</v>
@@ -11140,7 +11293,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B274">
         <v>2</v>
@@ -11152,7 +11305,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -11164,7 +11317,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -11176,7 +11329,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -11188,7 +11341,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -11200,7 +11353,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -11212,7 +11365,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -11224,7 +11377,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -11236,7 +11389,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -11248,7 +11401,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -11260,7 +11413,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -11272,7 +11425,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -11284,7 +11437,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -11296,7 +11449,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -11308,7 +11461,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -11320,7 +11473,7 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -11332,7 +11485,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -11344,7 +11497,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -11356,7 +11509,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -11368,7 +11521,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -11380,7 +11533,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -11392,7 +11545,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -11404,7 +11557,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -11416,7 +11569,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -11428,7 +11581,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -11440,7 +11593,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -11452,7 +11605,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B300">
         <v>1</v>
@@ -11463,7 +11616,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C300" xr:uid="{289EF377-1059-4382-B848-913FAEFD6455}"/>
+  <autoFilter ref="A1:C300" xr:uid="{BC7884C5-EE35-4997-88D0-31E7A24B608D}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>